--- a/web_selenium/screenshots/selenium_web_report.xlsx
+++ b/web_selenium/screenshots/selenium_web_report.xlsx
@@ -40,916 +40,916 @@
     <t>Functional</t>
   </si>
   <si>
-    <t>TC-SEL-001: Verify that database error warning is not present on Student Overview (Check #1)</t>
+    <t>TC-SEL-001: Test page responsiveness on standard desktop view for Warden Leave Requests (Check #1)</t>
   </si>
   <si>
     <t>PASS</t>
   </si>
   <si>
-    <t>6/22/2026, 8:13:48 AM</t>
-  </si>
-  <si>
-    <t>TC-SEL-002: Verify email input form control is visible on the Complaint Monitoring page (Check #2)</t>
+    <t>6/22/2026, 8:15:36 AM</t>
+  </si>
+  <si>
+    <t>TC-SEL-002: Check alert dialog box clickability on the Complaint History page (Check #2)</t>
   </si>
   <si>
     <t>UI/UX</t>
   </si>
   <si>
-    <t>TC-SEL-003: Assert that dashboard metrics card displays correct CSS styles on Mess Feedback (Check #3)</t>
-  </si>
-  <si>
-    <t>TC-SEL-004: Verify redirection to Security Monitoring after action (Check #4)</t>
+    <t>TC-SEL-003: Test user login with valid credentials on Admin Dashboard (Check #3)</t>
+  </si>
+  <si>
+    <t>TC-SEL-004: Verify that database error warning is not present on Complaint Monitoring (Check #4)</t>
   </si>
   <si>
     <t>Validation</t>
   </si>
   <si>
-    <t>TC-SEL-005: Test page responsiveness on standard desktop view for Student Overview (Check #5)</t>
-  </si>
-  <si>
-    <t>TC-SEL-006: Verify that database error warning is not present on Student Login (Check #6)</t>
-  </si>
-  <si>
-    <t>TC-SEL-007: Assert that back button navigation link displays correct CSS styles on Warden Leave Requests (Check #7)</t>
-  </si>
-  <si>
-    <t>TC-SEL-008: Test page responsiveness on standard desktop view for Mess Overview (Check #8)</t>
-  </si>
-  <si>
-    <t>TC-SEL-009: Verify redirection to Landing Page after action (Check #9)</t>
-  </si>
-  <si>
-    <t>TC-SEL-010: Verify redirection to Mess Overview after action (Check #10)</t>
-  </si>
-  <si>
-    <t>TC-SEL-011: Verify password input text box is visible on the Student Dashboard page (Check #11)</t>
-  </si>
-  <si>
-    <t>TC-SEL-012: Verify that form validation works for profile image uploader container on Warden Room Management (Check #12)</t>
-  </si>
-  <si>
-    <t>TC-SEL-013: Verify that database error warning is not present on Leave Request (Check #13)</t>
-  </si>
-  <si>
-    <t>TC-SEL-014: Assert that email input form control displays correct CSS styles on Mess Overview (Check #14)</t>
-  </si>
-  <si>
-    <t>TC-SEL-015: Verify that database error warning is not present on Warden Leave Requests (Check #15)</t>
-  </si>
-  <si>
-    <t>TC-SEL-016: Check fee status badge display clickability on the Notifications page (Check #16)</t>
-  </si>
-  <si>
-    <t>TC-SEL-017: Test page responsiveness on standard desktop view for Admin Dashboard (Check #17)</t>
-  </si>
-  <si>
-    <t>TC-SEL-018: Assert that alert dialog box displays correct CSS styles on Logout (Check #18)</t>
-  </si>
-  <si>
-    <t>TC-SEL-019: Assert that sidebar navigation items displays correct CSS styles on Admin Dashboard (Check #19)</t>
-  </si>
-  <si>
-    <t>TC-SEL-020: Verify that form validation works for complaint history table on Complaint Monitoring (Check #20)</t>
-  </si>
-  <si>
-    <t>TC-SEL-021: Test page responsiveness on standard desktop view for System Reports (Check #21)</t>
-  </si>
-  <si>
-    <t>TC-SEL-022: Verify that database error warning is not present on Landing Page (Check #22)</t>
-  </si>
-  <si>
-    <t>TC-SEL-023: Check sidebar navigation items clickability on the Warden Login page (Check #23)</t>
-  </si>
-  <si>
-    <t>TC-SEL-024: Verify redirection to Role Selection after action (Check #24)</t>
-  </si>
-  <si>
-    <t>TC-SEL-025: Test page responsiveness on standard desktop view for Warden Leave Requests (Check #25)</t>
-  </si>
-  <si>
-    <t>TC-SEL-026: Assert that footer copyright note displays correct CSS styles on My Room (Check #26)</t>
-  </si>
-  <si>
-    <t>TC-SEL-027: Verify that form validation works for password input text box on Admin Login (Check #27)</t>
-  </si>
-  <si>
-    <t>TC-SEL-028: Test page responsiveness on standard desktop view for Student Dashboard (Check #28)</t>
-  </si>
-  <si>
-    <t>TC-SEL-029: Verify notice board widget is visible on the Mess Feedback page (Check #29)</t>
-  </si>
-  <si>
-    <t>TC-SEL-030: Verify notice board widget is visible on the Warden Login page (Check #30)</t>
+    <t>TC-SEL-005: Verify profile image uploader container is visible on the Attendance page (Check #5)</t>
+  </si>
+  <si>
+    <t>TC-SEL-006: Test page responsiveness on standard desktop view for Student Login (Check #6)</t>
+  </si>
+  <si>
+    <t>TC-SEL-007: Check back button navigation link clickability on the Student Login page (Check #7)</t>
+  </si>
+  <si>
+    <t>TC-SEL-008: Verify redirection to Warden Leave Requests after action (Check #8)</t>
+  </si>
+  <si>
+    <t>TC-SEL-009: Test page responsiveness on standard desktop view for Admin Login (Check #9)</t>
+  </si>
+  <si>
+    <t>TC-SEL-010: Test page responsiveness on standard desktop view for Profile (Check #10)</t>
+  </si>
+  <si>
+    <t>TC-SEL-011: Verify redirection to Warden Login after action (Check #11)</t>
+  </si>
+  <si>
+    <t>TC-SEL-012: Assert that footer copyright note displays correct CSS styles on Student Overview (Check #12)</t>
+  </si>
+  <si>
+    <t>TC-SEL-013: Check footer copyright note clickability on the Complaint Monitoring page (Check #13)</t>
+  </si>
+  <si>
+    <t>TC-SEL-014: Verify that form validation works for fee status badge display on Landing Page (Check #14)</t>
+  </si>
+  <si>
+    <t>TC-SEL-015: Verify database connection module is visible on the Warden Login page (Check #15)</t>
+  </si>
+  <si>
+    <t>TC-SEL-016: Verify that form validation works for fee status badge display on Complaint Monitoring (Check #16)</t>
+  </si>
+  <si>
+    <t>TC-SEL-017: Verify that form validation works for main navigation header on Warden Dashboard (Check #17)</t>
+  </si>
+  <si>
+    <t>TC-SEL-018: Check notice board widget clickability on the My Room page (Check #18)</t>
+  </si>
+  <si>
+    <t>TC-SEL-019: Check alert dialog box clickability on the Role Selection page (Check #19)</t>
+  </si>
+  <si>
+    <t>TC-SEL-020: Verify that database error warning is not present on Leave Request (Check #20)</t>
+  </si>
+  <si>
+    <t>TC-SEL-021: Verify that database error warning is not present on Admin Login (Check #21)</t>
+  </si>
+  <si>
+    <t>TC-SEL-022: Assert that average rating star system displays correct CSS styles on Raise Complaint (Check #22)</t>
+  </si>
+  <si>
+    <t>TC-SEL-023: Verify password input text box is visible on the Leave Request page (Check #23)</t>
+  </si>
+  <si>
+    <t>TC-SEL-024: Test page responsiveness on standard desktop view for Warden Leave Requests (Check #24)</t>
+  </si>
+  <si>
+    <t>TC-SEL-025: Test page responsiveness on standard desktop view for Mess Feedback (Check #25)</t>
+  </si>
+  <si>
+    <t>TC-SEL-026: Test user login with valid credentials on Admin Dashboard (Check #26)</t>
+  </si>
+  <si>
+    <t>TC-SEL-027: Verify redirection to Leave Request after action (Check #27)</t>
+  </si>
+  <si>
+    <t>TC-SEL-028: Test page responsiveness on standard desktop view for System Reports (Check #28)</t>
+  </si>
+  <si>
+    <t>TC-SEL-029: Check leave request request form clickability on the Student Overview page (Check #29)</t>
+  </si>
+  <si>
+    <t>TC-SEL-030: Verify that database error warning is not present on Raise Complaint (Check #30)</t>
   </si>
   <si>
     <t>TC-SEL-031: Verify that database error warning is not present on System Settings (Check #31)</t>
   </si>
   <si>
-    <t>TC-SEL-032: Verify username input text field is visible on the Fee Details page (Check #32)</t>
-  </si>
-  <si>
-    <t>TC-SEL-033: Verify that form validation works for notice board widget on Attendance (Check #33)</t>
-  </si>
-  <si>
-    <t>TC-SEL-034: Check email input form control clickability on the Raise Complaint page (Check #34)</t>
-  </si>
-  <si>
-    <t>TC-SEL-035: Check footer copyright note clickability on the Mess Feedback page (Check #35)</t>
-  </si>
-  <si>
-    <t>TC-SEL-036: Verify redirection to Role Selection after action (Check #36)</t>
-  </si>
-  <si>
-    <t>TC-SEL-037: Check complaint history table clickability on the My Room page (Check #37)</t>
-  </si>
-  <si>
-    <t>TC-SEL-038: Verify redirection to Complaint Monitoring after action (Check #38)</t>
-  </si>
-  <si>
-    <t>TC-SEL-039: Assert that fee status badge display displays correct CSS styles on System Reports (Check #39)</t>
-  </si>
-  <si>
-    <t>TC-SEL-040: Verify database connection module is visible on the Mess Overview page (Check #40)</t>
-  </si>
-  <si>
-    <t>TC-SEL-041: Verify submit button control is visible on the Complaint History page (Check #41)</t>
-  </si>
-  <si>
-    <t>TC-SEL-042: Check notice board widget clickability on the Fee Details page (Check #42)</t>
-  </si>
-  <si>
-    <t>TC-SEL-043: Verify that form validation works for notice board widget on Student Dashboard (Check #43)</t>
-  </si>
-  <si>
-    <t>TC-SEL-044: Verify that form validation works for sidebar navigation items on Complaint History (Check #44)</t>
-  </si>
-  <si>
-    <t>TC-SEL-045: Verify that form validation works for submit button control on Security Monitoring (Check #45)</t>
-  </si>
-  <si>
-    <t>TC-SEL-046: Assert that password input text box displays correct CSS styles on Logout (Check #46)</t>
-  </si>
-  <si>
-    <t>TC-SEL-047: Check submit button control clickability on the Mess Feedback page (Check #47)</t>
-  </si>
-  <si>
-    <t>TC-SEL-048: Verify redirection to System Settings after action (Check #48)</t>
-  </si>
-  <si>
-    <t>TC-SEL-049: Test user login with valid credentials on Student Dashboard (Check #49)</t>
-  </si>
-  <si>
-    <t>TC-SEL-050: Verify redirection to Admin Dashboard after action (Check #50)</t>
-  </si>
-  <si>
-    <t>TC-SEL-051: Test page responsiveness on standard desktop view for Attendance (Check #51)</t>
-  </si>
-  <si>
-    <t>TC-SEL-052: Check profile image uploader container clickability on the Student Dashboard page (Check #52)</t>
-  </si>
-  <si>
-    <t>TC-SEL-053: Assert that alert dialog box displays correct CSS styles on System Settings (Check #53)</t>
-  </si>
-  <si>
-    <t>TC-SEL-054: Assert that email input form control displays correct CSS styles on Student Overview (Check #54)</t>
-  </si>
-  <si>
-    <t>TC-SEL-055: Test user login with valid credentials on Profile (Check #55)</t>
-  </si>
-  <si>
-    <t>TC-SEL-056: Verify that database error warning is not present on Admin Login (Check #56)</t>
-  </si>
-  <si>
-    <t>TC-SEL-057: Test page responsiveness on standard desktop view for System Reports (Check #57)</t>
-  </si>
-  <si>
-    <t>TC-SEL-058: Check back button navigation link clickability on the Raise Complaint page (Check #58)</t>
-  </si>
-  <si>
-    <t>TC-SEL-059: Verify that form validation works for username input text field on Warden Dashboard (Check #59)</t>
-  </si>
-  <si>
-    <t>TC-SEL-060: Test page responsiveness on standard desktop view for Admin Login (Check #60)</t>
-  </si>
-  <si>
-    <t>TC-SEL-061: Assert that database connection module displays correct CSS styles on Student Dashboard (Check #61)</t>
-  </si>
-  <si>
-    <t>TC-SEL-062: Check sidebar navigation items clickability on the Notifications page (Check #62)</t>
-  </si>
-  <si>
-    <t>TC-SEL-063: Verify that database error warning is not present on Landing Page (Check #63)</t>
-  </si>
-  <si>
-    <t>TC-SEL-064: Verify redirection to Role Selection after action (Check #64)</t>
-  </si>
-  <si>
-    <t>TC-SEL-065: Verify role selection button is visible on the Complaint Monitoring page (Check #65)</t>
-  </si>
-  <si>
-    <t>TC-SEL-066: Check complaint history table clickability on the Fee Details page (Check #66)</t>
-  </si>
-  <si>
-    <t>TC-SEL-067: Assert that alert dialog box displays correct CSS styles on Attendance (Check #67)</t>
-  </si>
-  <si>
-    <t>TC-SEL-068: Test page responsiveness on standard desktop view for Security Monitoring (Check #68)</t>
-  </si>
-  <si>
-    <t>TC-SEL-069: Test user login with valid credentials on Student Overview (Check #69)</t>
-  </si>
-  <si>
-    <t>TC-SEL-070: Check password input text box clickability on the Warden Login page (Check #70)</t>
-  </si>
-  <si>
-    <t>TC-SEL-071: Verify redirection to Security Monitoring after action (Check #71)</t>
-  </si>
-  <si>
-    <t>TC-SEL-072: Verify average rating star system is visible on the Role Selection page (Check #72)</t>
-  </si>
-  <si>
-    <t>TC-SEL-073: Test user login with valid credentials on Complaint History (Check #73)</t>
-  </si>
-  <si>
-    <t>TC-SEL-074: Verify redirection to My Room after action (Check #74)</t>
-  </si>
-  <si>
-    <t>TC-SEL-075: Test page responsiveness on standard desktop view for Complaint Monitoring (Check #75)</t>
-  </si>
-  <si>
-    <t>TC-SEL-076: Verify dashboard metrics card is visible on the Mess Feedback page (Check #76)</t>
-  </si>
-  <si>
-    <t>TC-SEL-077: Test page responsiveness on standard desktop view for Student Login (Check #77)</t>
-  </si>
-  <si>
-    <t>TC-SEL-078: Check role selection button clickability on the Warden Dashboard page (Check #78)</t>
-  </si>
-  <si>
-    <t>TC-SEL-079: Test user login with valid credentials on Student Login (Check #79)</t>
-  </si>
-  <si>
-    <t>TC-SEL-080: Verify role selection button is visible on the System Reports page (Check #80)</t>
-  </si>
-  <si>
-    <t>TC-SEL-081: Verify that database error warning is not present on Admin Dashboard (Check #81)</t>
-  </si>
-  <si>
-    <t>TC-SEL-082: Verify that form validation works for complaint history table on Logout (Check #82)</t>
-  </si>
-  <si>
-    <t>TC-SEL-083: Verify that database error warning is not present on Admin Login (Check #83)</t>
-  </si>
-  <si>
-    <t>TC-SEL-084: Check password input text box clickability on the Attendance page (Check #84)</t>
-  </si>
-  <si>
-    <t>TC-SEL-085: Verify that database error warning is not present on Security Monitoring (Check #85)</t>
-  </si>
-  <si>
-    <t>TC-SEL-086: Test page responsiveness on standard desktop view for Admin Login (Check #86)</t>
-  </si>
-  <si>
-    <t>TC-SEL-087: Test user login with valid credentials on Security Monitoring (Check #87)</t>
-  </si>
-  <si>
-    <t>TC-SEL-088: Test page responsiveness on standard desktop view for Attendance (Check #88)</t>
-  </si>
-  <si>
-    <t>TC-SEL-089: Assert that password input text box displays correct CSS styles on System Settings (Check #89)</t>
-  </si>
-  <si>
-    <t>TC-SEL-090: Test user login with valid credentials on Role Selection (Check #90)</t>
-  </si>
-  <si>
-    <t>TC-SEL-091: Verify redirection to System Settings after action (Check #91)</t>
-  </si>
-  <si>
-    <t>TC-SEL-092: Test user login with valid credentials on Leave Request (Check #92)</t>
-  </si>
-  <si>
-    <t>TC-SEL-093: Assert that average rating star system displays correct CSS styles on Warden Leave Requests (Check #93)</t>
-  </si>
-  <si>
-    <t>TC-SEL-094: Assert that username input text field displays correct CSS styles on Fee Details (Check #94)</t>
-  </si>
-  <si>
-    <t>TC-SEL-095: Verify notice board widget is visible on the Admin Login page (Check #95)</t>
-  </si>
-  <si>
-    <t>TC-SEL-096: Assert that notice board widget displays correct CSS styles on Warden Room Management (Check #96)</t>
-  </si>
-  <si>
-    <t>TC-SEL-097: Verify that form validation works for role selection button on Mess Feedback (Check #97)</t>
-  </si>
-  <si>
-    <t>TC-SEL-098: Verify that form validation works for leave request request form on Fee Details (Check #98)</t>
-  </si>
-  <si>
-    <t>TC-SEL-099: Verify that database error warning is not present on Complaint Monitoring (Check #99)</t>
-  </si>
-  <si>
-    <t>TC-SEL-100: Test page responsiveness on standard desktop view for Notifications (Check #100)</t>
-  </si>
-  <si>
-    <t>TC-SEL-101: Verify redirection to Fee Details after action (Check #101)</t>
-  </si>
-  <si>
-    <t>TC-SEL-102: Verify that form validation works for username input text field on Role Selection (Check #102)</t>
-  </si>
-  <si>
-    <t>TC-SEL-103: Verify that database error warning is not present on Role Selection (Check #103)</t>
-  </si>
-  <si>
-    <t>TC-SEL-104: Verify redirection to Mess Overview after action (Check #104)</t>
-  </si>
-  <si>
-    <t>TC-SEL-105: Check leave request request form clickability on the System Settings page (Check #105)</t>
-  </si>
-  <si>
-    <t>TC-SEL-106: Test user login with valid credentials on Student Login (Check #106)</t>
-  </si>
-  <si>
-    <t>TC-SEL-107: Check average rating star system clickability on the Student Login page (Check #107)</t>
-  </si>
-  <si>
-    <t>TC-SEL-108: Check database connection module clickability on the Warden Leave Requests page (Check #108)</t>
-  </si>
-  <si>
-    <t>TC-SEL-109: Verify main navigation header is visible on the Student Overview page (Check #109)</t>
-  </si>
-  <si>
-    <t>TC-SEL-110: Test user login with valid credentials on Raise Complaint (Check #110)</t>
-  </si>
-  <si>
-    <t>TC-SEL-111: Test page responsiveness on standard desktop view for Mess Overview (Check #111)</t>
-  </si>
-  <si>
-    <t>TC-SEL-112: Verify redirection to Notifications after action (Check #112)</t>
-  </si>
-  <si>
-    <t>TC-SEL-113: Test user login with valid credentials on Complaint History (Check #113)</t>
+    <t>TC-SEL-032: Test user login with valid credentials on Notifications (Check #32)</t>
+  </si>
+  <si>
+    <t>TC-SEL-033: Verify that database error warning is not present on Attendance (Check #33)</t>
+  </si>
+  <si>
+    <t>TC-SEL-034: Test user login with valid credentials on System Settings (Check #34)</t>
+  </si>
+  <si>
+    <t>TC-SEL-035: Test page responsiveness on standard desktop view for Admin Dashboard (Check #35)</t>
+  </si>
+  <si>
+    <t>TC-SEL-036: Check average rating star system clickability on the My Room page (Check #36)</t>
+  </si>
+  <si>
+    <t>TC-SEL-037: Verify that form validation works for profile image uploader container on Raise Complaint (Check #37)</t>
+  </si>
+  <si>
+    <t>TC-SEL-038: Check notice board widget clickability on the Fee Details page (Check #38)</t>
+  </si>
+  <si>
+    <t>TC-SEL-039: Verify redirection to My Room after action (Check #39)</t>
+  </si>
+  <si>
+    <t>TC-SEL-040: Test user login with valid credentials on Admin Login (Check #40)</t>
+  </si>
+  <si>
+    <t>TC-SEL-041: Verify that form validation works for sidebar navigation items on Complaint Monitoring (Check #41)</t>
+  </si>
+  <si>
+    <t>TC-SEL-042: Test page responsiveness on standard desktop view for Warden Room Management (Check #42)</t>
+  </si>
+  <si>
+    <t>TC-SEL-043: Verify that form validation works for role selection button on Warden Dashboard (Check #43)</t>
+  </si>
+  <si>
+    <t>TC-SEL-044: Test page responsiveness on standard desktop view for Landing Page (Check #44)</t>
+  </si>
+  <si>
+    <t>TC-SEL-045: Test page responsiveness on standard desktop view for Complaint History (Check #45)</t>
+  </si>
+  <si>
+    <t>TC-SEL-046: Verify that form validation works for sidebar navigation items on Admin Login (Check #46)</t>
+  </si>
+  <si>
+    <t>TC-SEL-047: Test user login with valid credentials on Admin Login (Check #47)</t>
+  </si>
+  <si>
+    <t>TC-SEL-048: Verify profile image uploader container is visible on the Mess Overview page (Check #48)</t>
+  </si>
+  <si>
+    <t>TC-SEL-049: Verify redirection to Attendance after action (Check #49)</t>
+  </si>
+  <si>
+    <t>TC-SEL-050: Assert that dashboard metrics card displays correct CSS styles on Notifications (Check #50)</t>
+  </si>
+  <si>
+    <t>TC-SEL-051: Verify average rating star system is visible on the Admin Login page (Check #51)</t>
+  </si>
+  <si>
+    <t>TC-SEL-052: Test page responsiveness on standard desktop view for Role Selection (Check #52)</t>
+  </si>
+  <si>
+    <t>TC-SEL-053: Verify that database error warning is not present on Landing Page (Check #53)</t>
+  </si>
+  <si>
+    <t>TC-SEL-054: Test user login with valid credentials on Profile (Check #54)</t>
+  </si>
+  <si>
+    <t>TC-SEL-055: Test user login with valid credentials on Warden Leave Requests (Check #55)</t>
+  </si>
+  <si>
+    <t>TC-SEL-056: Verify that form validation works for submit button control on Fee Details (Check #56)</t>
+  </si>
+  <si>
+    <t>TC-SEL-057: Check fee status badge display clickability on the Profile page (Check #57)</t>
+  </si>
+  <si>
+    <t>TC-SEL-058: Verify that database error warning is not present on Warden Leave Requests (Check #58)</t>
+  </si>
+  <si>
+    <t>TC-SEL-059: Check footer copyright note clickability on the Student Dashboard page (Check #59)</t>
+  </si>
+  <si>
+    <t>TC-SEL-060: Verify submit button control is visible on the Admin Login page (Check #60)</t>
+  </si>
+  <si>
+    <t>TC-SEL-061: Verify that form validation works for back button navigation link on Warden Login (Check #61)</t>
+  </si>
+  <si>
+    <t>TC-SEL-062: Test user login with valid credentials on Attendance (Check #62)</t>
+  </si>
+  <si>
+    <t>TC-SEL-063: Test user login with valid credentials on Warden Leave Requests (Check #63)</t>
+  </si>
+  <si>
+    <t>TC-SEL-064: Test user login with valid credentials on Fee Details (Check #64)</t>
+  </si>
+  <si>
+    <t>TC-SEL-065: Check alert dialog box clickability on the Landing Page page (Check #65)</t>
+  </si>
+  <si>
+    <t>TC-SEL-066: Verify redirection to Warden Room Management after action (Check #66)</t>
+  </si>
+  <si>
+    <t>TC-SEL-067: Test user login with valid credentials on Warden Dashboard (Check #67)</t>
+  </si>
+  <si>
+    <t>TC-SEL-068: Verify that form validation works for username input text field on Security Monitoring (Check #68)</t>
+  </si>
+  <si>
+    <t>TC-SEL-069: Assert that fee status badge display displays correct CSS styles on Student Login (Check #69)</t>
+  </si>
+  <si>
+    <t>TC-SEL-070: Verify password input text box is visible on the Warden Leave Requests page (Check #70)</t>
+  </si>
+  <si>
+    <t>TC-SEL-071: Verify redirection to Mess Feedback after action (Check #71)</t>
+  </si>
+  <si>
+    <t>TC-SEL-072: Verify redirection to Warden Dashboard after action (Check #72)</t>
+  </si>
+  <si>
+    <t>TC-SEL-073: Verify that form validation works for back button navigation link on Complaint Monitoring (Check #73)</t>
+  </si>
+  <si>
+    <t>TC-SEL-074: Test page responsiveness on standard desktop view for Student Overview (Check #74)</t>
+  </si>
+  <si>
+    <t>TC-SEL-075: Verify email input form control is visible on the System Reports page (Check #75)</t>
+  </si>
+  <si>
+    <t>TC-SEL-076: Test user login with valid credentials on Complaint History (Check #76)</t>
+  </si>
+  <si>
+    <t>TC-SEL-077: Assert that notice board widget displays correct CSS styles on Role Selection (Check #77)</t>
+  </si>
+  <si>
+    <t>TC-SEL-078: Verify that form validation works for dashboard metrics card on Mess Overview (Check #78)</t>
+  </si>
+  <si>
+    <t>TC-SEL-079: Assert that database connection module displays correct CSS styles on Student Overview (Check #79)</t>
+  </si>
+  <si>
+    <t>TC-SEL-080: Check email input form control clickability on the Admin Dashboard page (Check #80)</t>
+  </si>
+  <si>
+    <t>TC-SEL-081: Check notice board widget clickability on the Warden Leave Requests page (Check #81)</t>
+  </si>
+  <si>
+    <t>TC-SEL-082: Verify that form validation works for dashboard metrics card on Admin Dashboard (Check #82)</t>
+  </si>
+  <si>
+    <t>TC-SEL-083: Test page responsiveness on standard desktop view for Security Monitoring (Check #83)</t>
+  </si>
+  <si>
+    <t>TC-SEL-084: Verify alert dialog box is visible on the System Reports page (Check #84)</t>
+  </si>
+  <si>
+    <t>TC-SEL-085: Test page responsiveness on standard desktop view for Admin Dashboard (Check #85)</t>
+  </si>
+  <si>
+    <t>TC-SEL-086: Verify redirection to Mess Feedback after action (Check #86)</t>
+  </si>
+  <si>
+    <t>TC-SEL-087: Test user login with valid credentials on System Settings (Check #87)</t>
+  </si>
+  <si>
+    <t>TC-SEL-088: Check average rating star system clickability on the Warden Room Management page (Check #88)</t>
+  </si>
+  <si>
+    <t>TC-SEL-089: Verify redirection to Landing Page after action (Check #89)</t>
+  </si>
+  <si>
+    <t>TC-SEL-090: Assert that username input text field displays correct CSS styles on Fee Details (Check #90)</t>
+  </si>
+  <si>
+    <t>TC-SEL-091: Verify that form validation works for leave request request form on Complaint History (Check #91)</t>
+  </si>
+  <si>
+    <t>TC-SEL-092: Verify that database error warning is not present on Complaint History (Check #92)</t>
+  </si>
+  <si>
+    <t>TC-SEL-093: Test page responsiveness on standard desktop view for Warden Dashboard (Check #93)</t>
+  </si>
+  <si>
+    <t>TC-SEL-094: Assert that role selection button displays correct CSS styles on Logout (Check #94)</t>
+  </si>
+  <si>
+    <t>TC-SEL-095: Test user login with valid credentials on Complaint History (Check #95)</t>
+  </si>
+  <si>
+    <t>TC-SEL-096: Verify redirection to Warden Dashboard after action (Check #96)</t>
+  </si>
+  <si>
+    <t>TC-SEL-097: Test page responsiveness on standard desktop view for Notifications (Check #97)</t>
+  </si>
+  <si>
+    <t>TC-SEL-098: Check role selection button clickability on the Raise Complaint page (Check #98)</t>
+  </si>
+  <si>
+    <t>TC-SEL-099: Check role selection button clickability on the Complaint Monitoring page (Check #99)</t>
+  </si>
+  <si>
+    <t>TC-SEL-100: Test user login with valid credentials on Profile (Check #100)</t>
+  </si>
+  <si>
+    <t>TC-SEL-101: Verify redirection to Admin Dashboard after action (Check #101)</t>
+  </si>
+  <si>
+    <t>TC-SEL-102: Verify redirection to System Settings after action (Check #102)</t>
+  </si>
+  <si>
+    <t>TC-SEL-103: Verify redirection to Admin Dashboard after action (Check #103)</t>
+  </si>
+  <si>
+    <t>TC-SEL-104: Verify redirection to Warden Login after action (Check #104)</t>
+  </si>
+  <si>
+    <t>TC-SEL-105: Verify that form validation works for dashboard metrics card on Warden Room Management (Check #105)</t>
+  </si>
+  <si>
+    <t>TC-SEL-106: Assert that username input text field displays correct CSS styles on Role Selection (Check #106)</t>
+  </si>
+  <si>
+    <t>TC-SEL-107: Verify redirection to Notifications after action (Check #107)</t>
+  </si>
+  <si>
+    <t>TC-SEL-108: Verify redirection to Warden Login after action (Check #108)</t>
+  </si>
+  <si>
+    <t>TC-SEL-109: Assert that back button navigation link displays correct CSS styles on Student Dashboard (Check #109)</t>
+  </si>
+  <si>
+    <t>TC-SEL-110: Assert that footer copyright note displays correct CSS styles on Leave Request (Check #110)</t>
+  </si>
+  <si>
+    <t>TC-SEL-111: Test user login with valid credentials on Fee Details (Check #111)</t>
+  </si>
+  <si>
+    <t>TC-SEL-112: Test user login with valid credentials on Security Monitoring (Check #112)</t>
+  </si>
+  <si>
+    <t>TC-SEL-113: Verify that form validation works for profile image uploader container on Complaint History (Check #113)</t>
   </si>
   <si>
     <t>TC-SEL-114: Verify redirection to Security Monitoring after action (Check #114)</t>
   </si>
   <si>
-    <t>TC-SEL-115: Check role selection button clickability on the Leave Request page (Check #115)</t>
-  </si>
-  <si>
-    <t>TC-SEL-116: Verify password input text box is visible on the Student Dashboard page (Check #116)</t>
-  </si>
-  <si>
-    <t>TC-SEL-117: Check password input text box clickability on the Complaint Monitoring page (Check #117)</t>
-  </si>
-  <si>
-    <t>TC-SEL-118: Check role selection button clickability on the Profile page (Check #118)</t>
-  </si>
-  <si>
-    <t>TC-SEL-119: Test page responsiveness on standard desktop view for Warden Dashboard (Check #119)</t>
-  </si>
-  <si>
-    <t>TC-SEL-120: Assert that password input text box displays correct CSS styles on Attendance (Check #120)</t>
-  </si>
-  <si>
-    <t>TC-SEL-121: Check main navigation header clickability on the Complaint Monitoring page (Check #121)</t>
-  </si>
-  <si>
-    <t>TC-SEL-122: Assert that password input text box displays correct CSS styles on Admin Dashboard (Check #122)</t>
-  </si>
-  <si>
-    <t>TC-SEL-123: Verify that database error warning is not present on Admin Login (Check #123)</t>
-  </si>
-  <si>
-    <t>TC-SEL-124: Test user login with valid credentials on System Reports (Check #124)</t>
-  </si>
-  <si>
-    <t>TC-SEL-125: Verify main navigation header is visible on the Warden Room Management page (Check #125)</t>
-  </si>
-  <si>
-    <t>TC-SEL-126: Check dashboard metrics card clickability on the My Room page (Check #126)</t>
-  </si>
-  <si>
-    <t>TC-SEL-127: Verify redirection to Mess Overview after action (Check #127)</t>
-  </si>
-  <si>
-    <t>TC-SEL-128: Test page responsiveness on standard desktop view for System Settings (Check #128)</t>
-  </si>
-  <si>
-    <t>TC-SEL-129: Verify role selection button is visible on the Fee Details page (Check #129)</t>
-  </si>
-  <si>
-    <t>TC-SEL-130: Verify that form validation works for sidebar navigation items on Role Selection (Check #130)</t>
-  </si>
-  <si>
-    <t>TC-SEL-131: Verify redirection to Notifications after action (Check #131)</t>
-  </si>
-  <si>
-    <t>TC-SEL-132: Test user login with valid credentials on Student Dashboard (Check #132)</t>
-  </si>
-  <si>
-    <t>TC-SEL-133: Verify that database error warning is not present on Raise Complaint (Check #133)</t>
-  </si>
-  <si>
-    <t>TC-SEL-134: Verify that database error warning is not present on System Settings (Check #134)</t>
-  </si>
-  <si>
-    <t>TC-SEL-135: Verify dashboard metrics card is visible on the Student Dashboard page (Check #135)</t>
-  </si>
-  <si>
-    <t>TC-SEL-136: Verify notice board widget is visible on the Student Overview page (Check #136)</t>
-  </si>
-  <si>
-    <t>TC-SEL-137: Verify that form validation works for footer copyright note on System Reports (Check #137)</t>
-  </si>
-  <si>
-    <t>TC-SEL-138: Test page responsiveness on standard desktop view for Complaint Monitoring (Check #138)</t>
-  </si>
-  <si>
-    <t>TC-SEL-139: Test user login with valid credentials on Leave Request (Check #139)</t>
-  </si>
-  <si>
-    <t>TC-SEL-140: Verify redirection to Admin Dashboard after action (Check #140)</t>
-  </si>
-  <si>
-    <t>TC-SEL-141: Verify that form validation works for submit button control on Admin Dashboard (Check #141)</t>
-  </si>
-  <si>
-    <t>TC-SEL-142: Verify sidebar navigation items is visible on the Student Overview page (Check #142)</t>
-  </si>
-  <si>
-    <t>TC-SEL-143: Verify redirection to Fee Details after action (Check #143)</t>
-  </si>
-  <si>
-    <t>TC-SEL-144: Check role selection button clickability on the Student Dashboard page (Check #144)</t>
-  </si>
-  <si>
-    <t>TC-SEL-145: Test page responsiveness on standard desktop view for Mess Overview (Check #145)</t>
-  </si>
-  <si>
-    <t>TC-SEL-146: Test page responsiveness on standard desktop view for Landing Page (Check #146)</t>
-  </si>
-  <si>
-    <t>TC-SEL-147: Test user login with valid credentials on System Settings (Check #147)</t>
-  </si>
-  <si>
-    <t>TC-SEL-148: Verify that database error warning is not present on Fee Details (Check #148)</t>
-  </si>
-  <si>
-    <t>TC-SEL-149: Check footer copyright note clickability on the Warden Dashboard page (Check #149)</t>
-  </si>
-  <si>
-    <t>TC-SEL-150: Verify profile image uploader container is visible on the Student Dashboard page (Check #150)</t>
-  </si>
-  <si>
-    <t>TC-SEL-151: Verify sidebar navigation items is visible on the My Room page (Check #151)</t>
-  </si>
-  <si>
-    <t>TC-SEL-152: Verify redirection to Warden Room Management after action (Check #152)</t>
-  </si>
-  <si>
-    <t>TC-SEL-153: Test page responsiveness on standard desktop view for System Settings (Check #153)</t>
-  </si>
-  <si>
-    <t>TC-SEL-154: Assert that average rating star system displays correct CSS styles on Fee Details (Check #154)</t>
-  </si>
-  <si>
-    <t>TC-SEL-155: Test user login with valid credentials on Landing Page (Check #155)</t>
-  </si>
-  <si>
-    <t>TC-SEL-156: Verify password input text box is visible on the Security Monitoring page (Check #156)</t>
-  </si>
-  <si>
-    <t>TC-SEL-157: Verify sidebar navigation items is visible on the Warden Room Management page (Check #157)</t>
-  </si>
-  <si>
-    <t>TC-SEL-158: Verify leave request request form is visible on the Fee Details page (Check #158)</t>
-  </si>
-  <si>
-    <t>TC-SEL-159: Verify redirection to Warden Leave Requests after action (Check #159)</t>
-  </si>
-  <si>
-    <t>TC-SEL-160: Verify that form validation works for database connection module on Warden Dashboard (Check #160)</t>
-  </si>
-  <si>
-    <t>TC-SEL-161: Verify that form validation works for complaint history table on Student Login (Check #161)</t>
-  </si>
-  <si>
-    <t>TC-SEL-162: Test user login with valid credentials on Fee Details (Check #162)</t>
-  </si>
-  <si>
-    <t>TC-SEL-163: Assert that average rating star system displays correct CSS styles on Complaint History (Check #163)</t>
-  </si>
-  <si>
-    <t>TC-SEL-164: Verify that form validation works for database connection module on Warden Dashboard (Check #164)</t>
-  </si>
-  <si>
-    <t>TC-SEL-165: Test user login with valid credentials on Student Dashboard (Check #165)</t>
-  </si>
-  <si>
-    <t>TC-SEL-166: Verify that form validation works for fee status badge display on Student Dashboard (Check #166)</t>
-  </si>
-  <si>
-    <t>TC-SEL-167: Test user login with valid credentials on Role Selection (Check #167)</t>
-  </si>
-  <si>
-    <t>TC-SEL-168: Test user login with valid credentials on Admin Dashboard (Check #168)</t>
-  </si>
-  <si>
-    <t>TC-SEL-169: Test user login with valid credentials on Admin Dashboard (Check #169)</t>
-  </si>
-  <si>
-    <t>TC-SEL-170: Test user login with valid credentials on Fee Details (Check #170)</t>
-  </si>
-  <si>
-    <t>TC-SEL-171: Verify that database error warning is not present on Notifications (Check #171)</t>
-  </si>
-  <si>
-    <t>TC-SEL-172: Verify complaint history table is visible on the Role Selection page (Check #172)</t>
-  </si>
-  <si>
-    <t>TC-SEL-173: Assert that username input text field displays correct CSS styles on Fee Details (Check #173)</t>
-  </si>
-  <si>
-    <t>TC-SEL-174: Verify alert dialog box is visible on the Fee Details page (Check #174)</t>
-  </si>
-  <si>
-    <t>TC-SEL-175: Test user login with valid credentials on Complaint History (Check #175)</t>
-  </si>
-  <si>
-    <t>TC-SEL-176: Assert that fee status badge display displays correct CSS styles on System Reports (Check #176)</t>
-  </si>
-  <si>
-    <t>TC-SEL-177: Verify that database error warning is not present on Profile (Check #177)</t>
-  </si>
-  <si>
-    <t>TC-SEL-178: Verify footer copyright note is visible on the System Reports page (Check #178)</t>
-  </si>
-  <si>
-    <t>TC-SEL-179: Assert that database connection module displays correct CSS styles on Security Monitoring (Check #179)</t>
-  </si>
-  <si>
-    <t>TC-SEL-180: Test page responsiveness on standard desktop view for Warden Dashboard (Check #180)</t>
-  </si>
-  <si>
-    <t>TC-SEL-181: Verify that form validation works for complaint history table on Mess Overview (Check #181)</t>
-  </si>
-  <si>
-    <t>TC-SEL-182: Verify average rating star system is visible on the Admin Login page (Check #182)</t>
-  </si>
-  <si>
-    <t>TC-SEL-183: Verify that form validation works for notice board widget on Mess Overview (Check #183)</t>
-  </si>
-  <si>
-    <t>TC-SEL-184: Check fee status badge display clickability on the Attendance page (Check #184)</t>
-  </si>
-  <si>
-    <t>TC-SEL-185: Verify redirection to Attendance after action (Check #185)</t>
-  </si>
-  <si>
-    <t>TC-SEL-186: Test user login with valid credentials on Complaint History (Check #186)</t>
-  </si>
-  <si>
-    <t>TC-SEL-187: Verify that form validation works for main navigation header on Notifications (Check #187)</t>
-  </si>
-  <si>
-    <t>TC-SEL-188: Check profile image uploader container clickability on the Fee Details page (Check #188)</t>
-  </si>
-  <si>
-    <t>TC-SEL-189: Verify that database error warning is not present on Student Dashboard (Check #189)</t>
-  </si>
-  <si>
-    <t>TC-SEL-190: Check sidebar navigation items clickability on the Student Dashboard page (Check #190)</t>
-  </si>
-  <si>
-    <t>TC-SEL-191: Verify that database error warning is not present on Warden Dashboard (Check #191)</t>
-  </si>
-  <si>
-    <t>TC-SEL-192: Verify that database error warning is not present on Profile (Check #192)</t>
-  </si>
-  <si>
-    <t>TC-SEL-193: Verify redirection to Admin Login after action (Check #193)</t>
-  </si>
-  <si>
-    <t>TC-SEL-194: Verify that form validation works for notice board widget on Logout (Check #194)</t>
-  </si>
-  <si>
-    <t>TC-SEL-195: Verify that database error warning is not present on Attendance (Check #195)</t>
-  </si>
-  <si>
-    <t>TC-SEL-196: Verify that form validation works for dashboard metrics card on My Room (Check #196)</t>
-  </si>
-  <si>
-    <t>TC-SEL-197: Check main navigation header clickability on the Admin Dashboard page (Check #197)</t>
-  </si>
-  <si>
-    <t>TC-SEL-198: Verify back button navigation link is visible on the Warden Leave Requests page (Check #198)</t>
-  </si>
-  <si>
-    <t>TC-SEL-199: Verify redirection to Mess Overview after action (Check #199)</t>
-  </si>
-  <si>
-    <t>TC-SEL-200: Check password input text box clickability on the Logout page (Check #200)</t>
-  </si>
-  <si>
-    <t>TC-SEL-201: Check username input text field clickability on the Warden Login page (Check #201)</t>
-  </si>
-  <si>
-    <t>TC-SEL-202: Test user login with valid credentials on Security Monitoring (Check #202)</t>
-  </si>
-  <si>
-    <t>TC-SEL-203: Test user login with valid credentials on Attendance (Check #203)</t>
-  </si>
-  <si>
-    <t>TC-SEL-204: Test user login with valid credentials on Landing Page (Check #204)</t>
-  </si>
-  <si>
-    <t>TC-SEL-205: Assert that username input text field displays correct CSS styles on Student Overview (Check #205)</t>
-  </si>
-  <si>
-    <t>TC-SEL-206: Verify that form validation works for alert dialog box on Complaint History (Check #206)</t>
-  </si>
-  <si>
-    <t>TC-SEL-207: Test user login with valid credentials on Complaint Monitoring (Check #207)</t>
-  </si>
-  <si>
-    <t>TC-SEL-208: Verify leave request request form is visible on the Warden Login page (Check #208)</t>
-  </si>
-  <si>
-    <t>TC-SEL-209: Check sidebar navigation items clickability on the Student Dashboard page (Check #209)</t>
-  </si>
-  <si>
-    <t>TC-SEL-210: Verify main navigation header is visible on the Complaint Monitoring page (Check #210)</t>
-  </si>
-  <si>
-    <t>TC-SEL-211: Test page responsiveness on standard desktop view for Landing Page (Check #211)</t>
-  </si>
-  <si>
-    <t>TC-SEL-212: Verify redirection to Student Overview after action (Check #212)</t>
-  </si>
-  <si>
-    <t>TC-SEL-213: Verify that database error warning is not present on Student Dashboard (Check #213)</t>
-  </si>
-  <si>
-    <t>TC-SEL-214: Assert that complaint history table displays correct CSS styles on My Room (Check #214)</t>
-  </si>
-  <si>
-    <t>TC-SEL-215: Verify that database error warning is not present on Student Dashboard (Check #215)</t>
-  </si>
-  <si>
-    <t>TC-SEL-216: Verify sidebar navigation items is visible on the Leave Request page (Check #216)</t>
-  </si>
-  <si>
-    <t>TC-SEL-217: Test page responsiveness on standard desktop view for Profile (Check #217)</t>
-  </si>
-  <si>
-    <t>TC-SEL-218: Verify that database error warning is not present on Fee Details (Check #218)</t>
-  </si>
-  <si>
-    <t>TC-SEL-219: Check alert dialog box clickability on the Mess Feedback page (Check #219)</t>
-  </si>
-  <si>
-    <t>TC-SEL-220: Verify that form validation works for sidebar navigation items on Warden Room Management (Check #220)</t>
-  </si>
-  <si>
-    <t>TC-SEL-221: Test page responsiveness on standard desktop view for Admin Login (Check #221)</t>
-  </si>
-  <si>
-    <t>TC-SEL-222: Verify redirection to Mess Overview after action (Check #222)</t>
-  </si>
-  <si>
-    <t>TC-SEL-223: Check database connection module clickability on the Admin Login page (Check #223)</t>
-  </si>
-  <si>
-    <t>TC-SEL-224: Test page responsiveness on standard desktop view for Warden Leave Requests (Check #224)</t>
-  </si>
-  <si>
-    <t>TC-SEL-225: Verify notice board widget is visible on the Mess Overview page (Check #225)</t>
-  </si>
-  <si>
-    <t>TC-SEL-226: Verify that database error warning is not present on Attendance (Check #226)</t>
-  </si>
-  <si>
-    <t>TC-SEL-227: Verify redirection to Mess Feedback after action (Check #227)</t>
-  </si>
-  <si>
-    <t>TC-SEL-228: Verify that form validation works for complaint history table on Mess Feedback (Check #228)</t>
-  </si>
-  <si>
-    <t>TC-SEL-229: Assert that profile image uploader container displays correct CSS styles on Student Login (Check #229)</t>
-  </si>
-  <si>
-    <t>TC-SEL-230: Test user login with valid credentials on Admin Login (Check #230)</t>
-  </si>
-  <si>
-    <t>TC-SEL-231: Verify that form validation works for submit button control on Warden Leave Requests (Check #231)</t>
-  </si>
-  <si>
-    <t>TC-SEL-232: Verify leave request request form is visible on the Mess Overview page (Check #232)</t>
-  </si>
-  <si>
-    <t>TC-SEL-233: Verify redirection to Logout after action (Check #233)</t>
-  </si>
-  <si>
-    <t>TC-SEL-234: Verify redirection to My Room after action (Check #234)</t>
-  </si>
-  <si>
-    <t>TC-SEL-235: Check submit button control clickability on the Landing Page page (Check #235)</t>
-  </si>
-  <si>
-    <t>TC-SEL-236: Verify that database error warning is not present on Warden Login (Check #236)</t>
-  </si>
-  <si>
-    <t>TC-SEL-237: Test user login with valid credentials on System Reports (Check #237)</t>
-  </si>
-  <si>
-    <t>TC-SEL-238: Verify redirection to Complaint History after action (Check #238)</t>
-  </si>
-  <si>
-    <t>TC-SEL-239: Verify redirection to Admin Login after action (Check #239)</t>
-  </si>
-  <si>
-    <t>TC-SEL-240: Verify redirection to System Settings after action (Check #240)</t>
-  </si>
-  <si>
-    <t>TC-SEL-241: Assert that email input form control displays correct CSS styles on System Reports (Check #241)</t>
-  </si>
-  <si>
-    <t>TC-SEL-242: Verify alert dialog box is visible on the Role Selection page (Check #242)</t>
-  </si>
-  <si>
-    <t>TC-SEL-243: Verify redirection to Notifications after action (Check #243)</t>
-  </si>
-  <si>
-    <t>TC-SEL-244: Verify redirection to Complaint Monitoring after action (Check #244)</t>
-  </si>
-  <si>
-    <t>TC-SEL-245: Check footer copyright note clickability on the System Reports page (Check #245)</t>
-  </si>
-  <si>
-    <t>TC-SEL-246: Verify that form validation works for main navigation header on Student Dashboard (Check #246)</t>
-  </si>
-  <si>
-    <t>TC-SEL-247: Verify redirection to Warden Leave Requests after action (Check #247)</t>
-  </si>
-  <si>
-    <t>TC-SEL-248: Verify that database error warning is not present on Warden Room Management (Check #248)</t>
-  </si>
-  <si>
-    <t>TC-SEL-249: Assert that submit button control displays correct CSS styles on Security Monitoring (Check #249)</t>
-  </si>
-  <si>
-    <t>TC-SEL-250: Verify that database error warning is not present on System Settings (Check #250)</t>
-  </si>
-  <si>
-    <t>TC-SEL-251: Verify that form validation works for submit button control on Logout (Check #251)</t>
-  </si>
-  <si>
-    <t>TC-SEL-252: Verify complaint history table is visible on the Profile page (Check #252)</t>
-  </si>
-  <si>
-    <t>TC-SEL-253: Verify redirection to Logout after action (Check #253)</t>
-  </si>
-  <si>
-    <t>TC-SEL-254: Test page responsiveness on standard desktop view for Fee Details (Check #254)</t>
-  </si>
-  <si>
-    <t>TC-SEL-255: Verify footer copyright note is visible on the Landing Page page (Check #255)</t>
-  </si>
-  <si>
-    <t>TC-SEL-256: Verify main navigation header is visible on the My Room page (Check #256)</t>
-  </si>
-  <si>
-    <t>TC-SEL-257: Verify that database error warning is not present on Warden Room Management (Check #257)</t>
-  </si>
-  <si>
-    <t>TC-SEL-258: Verify that database error warning is not present on Student Dashboard (Check #258)</t>
-  </si>
-  <si>
-    <t>TC-SEL-259: Verify that database error warning is not present on Leave Request (Check #259)</t>
-  </si>
-  <si>
-    <t>TC-SEL-260: Verify that form validation works for footer copyright note on System Settings (Check #260)</t>
-  </si>
-  <si>
-    <t>TC-SEL-261: Verify that form validation works for complaint history table on Student Dashboard (Check #261)</t>
-  </si>
-  <si>
-    <t>TC-SEL-262: Assert that email input form control displays correct CSS styles on Complaint Monitoring (Check #262)</t>
-  </si>
-  <si>
-    <t>TC-SEL-263: Verify sidebar navigation items is visible on the Notifications page (Check #263)</t>
-  </si>
-  <si>
-    <t>TC-SEL-264: Test user login with valid credentials on Mess Feedback (Check #264)</t>
-  </si>
-  <si>
-    <t>TC-SEL-265: Verify that database error warning is not present on Leave Request (Check #265)</t>
-  </si>
-  <si>
-    <t>TC-SEL-266: Test user login with valid credentials on Student Dashboard (Check #266)</t>
-  </si>
-  <si>
-    <t>TC-SEL-267: Verify redirection to System Settings after action (Check #267)</t>
-  </si>
-  <si>
-    <t>TC-SEL-268: Test page responsiveness on standard desktop view for Warden Leave Requests (Check #268)</t>
-  </si>
-  <si>
-    <t>TC-SEL-269: Assert that leave request request form displays correct CSS styles on Admin Login (Check #269)</t>
-  </si>
-  <si>
-    <t>TC-SEL-270: Verify that form validation works for dashboard metrics card on Admin Login (Check #270)</t>
-  </si>
-  <si>
-    <t>TC-SEL-271: Verify that database error warning is not present on System Settings (Check #271)</t>
-  </si>
-  <si>
-    <t>TC-SEL-272: Verify that form validation works for main navigation header on Warden Room Management (Check #272)</t>
-  </si>
-  <si>
-    <t>TC-SEL-273: Test user login with valid credentials on Complaint History (Check #273)</t>
-  </si>
-  <si>
-    <t>TC-SEL-274: Verify that database error warning is not present on Mess Overview (Check #274)</t>
-  </si>
-  <si>
-    <t>TC-SEL-275: Check sidebar navigation items clickability on the Complaint Monitoring page (Check #275)</t>
-  </si>
-  <si>
-    <t>TC-SEL-276: Assert that back button navigation link displays correct CSS styles on My Room (Check #276)</t>
-  </si>
-  <si>
-    <t>TC-SEL-277: Verify that form validation works for submit button control on System Reports (Check #277)</t>
-  </si>
-  <si>
-    <t>TC-SEL-278: Verify that database error warning is not present on Notifications (Check #278)</t>
-  </si>
-  <si>
-    <t>TC-SEL-279: Check fee status badge display clickability on the Admin Login page (Check #279)</t>
-  </si>
-  <si>
-    <t>TC-SEL-280: Test page responsiveness on standard desktop view for Admin Dashboard (Check #280)</t>
-  </si>
-  <si>
-    <t>TC-SEL-281: Verify database connection module is visible on the Raise Complaint page (Check #281)</t>
-  </si>
-  <si>
-    <t>TC-SEL-282: Assert that footer copyright note displays correct CSS styles on Landing Page (Check #282)</t>
-  </si>
-  <si>
-    <t>TC-SEL-283: Test user login with valid credentials on Admin Login (Check #283)</t>
-  </si>
-  <si>
-    <t>TC-SEL-284: Verify redirection to System Reports after action (Check #284)</t>
-  </si>
-  <si>
-    <t>TC-SEL-285: Verify redirection to My Room after action (Check #285)</t>
-  </si>
-  <si>
-    <t>TC-SEL-286: Verify that form validation works for main navigation header on Mess Feedback (Check #286)</t>
-  </si>
-  <si>
-    <t>TC-SEL-287: Check main navigation header clickability on the Fee Details page (Check #287)</t>
-  </si>
-  <si>
-    <t>TC-SEL-288: Verify that form validation works for notice board widget on Warden Room Management (Check #288)</t>
-  </si>
-  <si>
-    <t>TC-SEL-289: Verify redirection to Profile after action (Check #289)</t>
-  </si>
-  <si>
-    <t>TC-SEL-290: Verify that database error warning is not present on Mess Overview (Check #290)</t>
-  </si>
-  <si>
-    <t>TC-SEL-291: Check notice board widget clickability on the Admin Login page (Check #291)</t>
-  </si>
-  <si>
-    <t>TC-SEL-292: Verify that form validation works for average rating star system on Student Login (Check #292)</t>
-  </si>
-  <si>
-    <t>TC-SEL-293: Test user login with valid credentials on Complaint History (Check #293)</t>
-  </si>
-  <si>
-    <t>TC-SEL-294: Test page responsiveness on standard desktop view for Role Selection (Check #294)</t>
-  </si>
-  <si>
-    <t>TC-SEL-295: Test page responsiveness on standard desktop view for Role Selection (Check #295)</t>
-  </si>
-  <si>
-    <t>TC-SEL-296: Verify redirection to Fee Details after action (Check #296)</t>
-  </si>
-  <si>
-    <t>TC-SEL-297: Check submit button control clickability on the Raise Complaint page (Check #297)</t>
-  </si>
-  <si>
-    <t>TC-SEL-298: Verify that form validation works for email input form control on Warden Dashboard (Check #298)</t>
-  </si>
-  <si>
-    <t>TC-SEL-299: Test user login with valid credentials on Warden Login (Check #299)</t>
-  </si>
-  <si>
-    <t>TC-SEL-300: Verify redirection to Admin Login after action (Check #300)</t>
+    <t>TC-SEL-115: Verify that database error warning is not present on Logout (Check #115)</t>
+  </si>
+  <si>
+    <t>TC-SEL-116: Test user login with valid credentials on Profile (Check #116)</t>
+  </si>
+  <si>
+    <t>TC-SEL-117: Assert that email input form control displays correct CSS styles on Notifications (Check #117)</t>
+  </si>
+  <si>
+    <t>TC-SEL-118: Verify leave request request form is visible on the My Room page (Check #118)</t>
+  </si>
+  <si>
+    <t>TC-SEL-119: Verify that form validation works for password input text box on Admin Dashboard (Check #119)</t>
+  </si>
+  <si>
+    <t>TC-SEL-120: Verify that database error warning is not present on Fee Details (Check #120)</t>
+  </si>
+  <si>
+    <t>TC-SEL-121: Verify leave request request form is visible on the Logout page (Check #121)</t>
+  </si>
+  <si>
+    <t>TC-SEL-122: Test user login with valid credentials on Complaint History (Check #122)</t>
+  </si>
+  <si>
+    <t>TC-SEL-123: Assert that footer copyright note displays correct CSS styles on Student Dashboard (Check #123)</t>
+  </si>
+  <si>
+    <t>TC-SEL-124: Assert that password input text box displays correct CSS styles on System Settings (Check #124)</t>
+  </si>
+  <si>
+    <t>TC-SEL-125: Test page responsiveness on standard desktop view for Notifications (Check #125)</t>
+  </si>
+  <si>
+    <t>TC-SEL-126: Verify that form validation works for dashboard metrics card on Fee Details (Check #126)</t>
+  </si>
+  <si>
+    <t>TC-SEL-127: Assert that database connection module displays correct CSS styles on Admin Dashboard (Check #127)</t>
+  </si>
+  <si>
+    <t>TC-SEL-128: Verify that form validation works for alert dialog box on Warden Room Management (Check #128)</t>
+  </si>
+  <si>
+    <t>TC-SEL-129: Test user login with valid credentials on Raise Complaint (Check #129)</t>
+  </si>
+  <si>
+    <t>TC-SEL-130: Verify that form validation works for dashboard metrics card on Profile (Check #130)</t>
+  </si>
+  <si>
+    <t>TC-SEL-131: Test user login with valid credentials on Admin Dashboard (Check #131)</t>
+  </si>
+  <si>
+    <t>TC-SEL-132: Verify footer copyright note is visible on the Mess Overview page (Check #132)</t>
+  </si>
+  <si>
+    <t>TC-SEL-133: Test user login with valid credentials on Profile (Check #133)</t>
+  </si>
+  <si>
+    <t>TC-SEL-134: Check complaint history table clickability on the Warden Dashboard page (Check #134)</t>
+  </si>
+  <si>
+    <t>TC-SEL-135: Verify submit button control is visible on the Student Dashboard page (Check #135)</t>
+  </si>
+  <si>
+    <t>TC-SEL-136: Verify redirection to Security Monitoring after action (Check #136)</t>
+  </si>
+  <si>
+    <t>TC-SEL-137: Verify redirection to System Settings after action (Check #137)</t>
+  </si>
+  <si>
+    <t>TC-SEL-138: Verify that form validation works for database connection module on Warden Leave Requests (Check #138)</t>
+  </si>
+  <si>
+    <t>TC-SEL-139: Verify redirection to Attendance after action (Check #139)</t>
+  </si>
+  <si>
+    <t>TC-SEL-140: Verify that database error warning is not present on Student Overview (Check #140)</t>
+  </si>
+  <si>
+    <t>TC-SEL-141: Assert that dashboard metrics card displays correct CSS styles on Landing Page (Check #141)</t>
+  </si>
+  <si>
+    <t>TC-SEL-142: Verify dashboard metrics card is visible on the Raise Complaint page (Check #142)</t>
+  </si>
+  <si>
+    <t>TC-SEL-143: Verify alert dialog box is visible on the Complaint History page (Check #143)</t>
+  </si>
+  <si>
+    <t>TC-SEL-144: Assert that footer copyright note displays correct CSS styles on Student Overview (Check #144)</t>
+  </si>
+  <si>
+    <t>TC-SEL-145: Test page responsiveness on standard desktop view for Notifications (Check #145)</t>
+  </si>
+  <si>
+    <t>TC-SEL-146: Verify that form validation works for footer copyright note on Raise Complaint (Check #146)</t>
+  </si>
+  <si>
+    <t>TC-SEL-147: Verify that database error warning is not present on Mess Feedback (Check #147)</t>
+  </si>
+  <si>
+    <t>TC-SEL-148: Verify role selection button is visible on the Profile page (Check #148)</t>
+  </si>
+  <si>
+    <t>TC-SEL-149: Test page responsiveness on standard desktop view for Leave Request (Check #149)</t>
+  </si>
+  <si>
+    <t>TC-SEL-150: Assert that average rating star system displays correct CSS styles on Role Selection (Check #150)</t>
+  </si>
+  <si>
+    <t>TC-SEL-151: Verify that form validation works for password input text box on Admin Dashboard (Check #151)</t>
+  </si>
+  <si>
+    <t>TC-SEL-152: Check main navigation header clickability on the My Room page (Check #152)</t>
+  </si>
+  <si>
+    <t>TC-SEL-153: Assert that profile image uploader container displays correct CSS styles on Landing Page (Check #153)</t>
+  </si>
+  <si>
+    <t>TC-SEL-154: Verify that form validation works for submit button control on Notifications (Check #154)</t>
+  </si>
+  <si>
+    <t>TC-SEL-155: Verify that form validation works for database connection module on Student Login (Check #155)</t>
+  </si>
+  <si>
+    <t>TC-SEL-156: Verify that database error warning is not present on System Reports (Check #156)</t>
+  </si>
+  <si>
+    <t>TC-SEL-157: Verify that form validation works for database connection module on Student Login (Check #157)</t>
+  </si>
+  <si>
+    <t>TC-SEL-158: Verify redirection to Raise Complaint after action (Check #158)</t>
+  </si>
+  <si>
+    <t>TC-SEL-159: Verify that database error warning is not present on Warden Dashboard (Check #159)</t>
+  </si>
+  <si>
+    <t>TC-SEL-160: Test page responsiveness on standard desktop view for Warden Dashboard (Check #160)</t>
+  </si>
+  <si>
+    <t>TC-SEL-161: Verify dashboard metrics card is visible on the Leave Request page (Check #161)</t>
+  </si>
+  <si>
+    <t>TC-SEL-162: Verify that form validation works for leave request request form on Role Selection (Check #162)</t>
+  </si>
+  <si>
+    <t>TC-SEL-163: Test page responsiveness on standard desktop view for Admin Dashboard (Check #163)</t>
+  </si>
+  <si>
+    <t>TC-SEL-164: Assert that fee status badge display displays correct CSS styles on Warden Room Management (Check #164)</t>
+  </si>
+  <si>
+    <t>TC-SEL-165: Verify that form validation works for notice board widget on Role Selection (Check #165)</t>
+  </si>
+  <si>
+    <t>TC-SEL-166: Test user login with valid credentials on Admin Login (Check #166)</t>
+  </si>
+  <si>
+    <t>TC-SEL-167: Test page responsiveness on standard desktop view for Mess Feedback (Check #167)</t>
+  </si>
+  <si>
+    <t>TC-SEL-168: Assert that notice board widget displays correct CSS styles on Complaint Monitoring (Check #168)</t>
+  </si>
+  <si>
+    <t>TC-SEL-169: Test page responsiveness on standard desktop view for Mess Feedback (Check #169)</t>
+  </si>
+  <si>
+    <t>TC-SEL-170: Verify that form validation works for sidebar navigation items on Raise Complaint (Check #170)</t>
+  </si>
+  <si>
+    <t>TC-SEL-171: Verify sidebar navigation items is visible on the Student Overview page (Check #171)</t>
+  </si>
+  <si>
+    <t>TC-SEL-172: Check complaint history table clickability on the Student Login page (Check #172)</t>
+  </si>
+  <si>
+    <t>TC-SEL-173: Test page responsiveness on standard desktop view for Student Login (Check #173)</t>
+  </si>
+  <si>
+    <t>TC-SEL-174: Verify that database error warning is not present on My Room (Check #174)</t>
+  </si>
+  <si>
+    <t>TC-SEL-175: Assert that username input text field displays correct CSS styles on Security Monitoring (Check #175)</t>
+  </si>
+  <si>
+    <t>TC-SEL-176: Verify leave request request form is visible on the Complaint History page (Check #176)</t>
+  </si>
+  <si>
+    <t>TC-SEL-177: Verify redirection to System Reports after action (Check #177)</t>
+  </si>
+  <si>
+    <t>TC-SEL-178: Verify profile image uploader container is visible on the Student Login page (Check #178)</t>
+  </si>
+  <si>
+    <t>TC-SEL-179: Assert that username input text field displays correct CSS styles on Mess Overview (Check #179)</t>
+  </si>
+  <si>
+    <t>TC-SEL-180: Verify redirection to My Room after action (Check #180)</t>
+  </si>
+  <si>
+    <t>TC-SEL-181: Verify back button navigation link is visible on the Mess Overview page (Check #181)</t>
+  </si>
+  <si>
+    <t>TC-SEL-182: Check average rating star system clickability on the Warden Leave Requests page (Check #182)</t>
+  </si>
+  <si>
+    <t>TC-SEL-183: Verify that database error warning is not present on Warden Login (Check #183)</t>
+  </si>
+  <si>
+    <t>TC-SEL-184: Test page responsiveness on standard desktop view for Warden Room Management (Check #184)</t>
+  </si>
+  <si>
+    <t>TC-SEL-185: Verify that database error warning is not present on Complaint Monitoring (Check #185)</t>
+  </si>
+  <si>
+    <t>TC-SEL-186: Test user login with valid credentials on Warden Room Management (Check #186)</t>
+  </si>
+  <si>
+    <t>TC-SEL-187: Verify that form validation works for notice board widget on Security Monitoring (Check #187)</t>
+  </si>
+  <si>
+    <t>TC-SEL-188: Assert that complaint history table displays correct CSS styles on Warden Dashboard (Check #188)</t>
+  </si>
+  <si>
+    <t>TC-SEL-189: Verify redirection to Admin Dashboard after action (Check #189)</t>
+  </si>
+  <si>
+    <t>TC-SEL-190: Verify that form validation works for fee status badge display on Notifications (Check #190)</t>
+  </si>
+  <si>
+    <t>TC-SEL-191: Test user login with valid credentials on Security Monitoring (Check #191)</t>
+  </si>
+  <si>
+    <t>TC-SEL-192: Verify that database error warning is not present on Student Login (Check #192)</t>
+  </si>
+  <si>
+    <t>TC-SEL-193: Verify that database error warning is not present on Leave Request (Check #193)</t>
+  </si>
+  <si>
+    <t>TC-SEL-194: Assert that email input form control displays correct CSS styles on Student Overview (Check #194)</t>
+  </si>
+  <si>
+    <t>TC-SEL-195: Verify alert dialog box is visible on the Warden Dashboard page (Check #195)</t>
+  </si>
+  <si>
+    <t>TC-SEL-196: Assert that main navigation header displays correct CSS styles on Security Monitoring (Check #196)</t>
+  </si>
+  <si>
+    <t>TC-SEL-197: Verify that form validation works for leave request request form on Role Selection (Check #197)</t>
+  </si>
+  <si>
+    <t>TC-SEL-198: Test user login with valid credentials on Attendance (Check #198)</t>
+  </si>
+  <si>
+    <t>TC-SEL-199: Verify role selection button is visible on the Warden Login page (Check #199)</t>
+  </si>
+  <si>
+    <t>TC-SEL-200: Test user login with valid credentials on Raise Complaint (Check #200)</t>
+  </si>
+  <si>
+    <t>TC-SEL-201: Verify redirection to Admin Dashboard after action (Check #201)</t>
+  </si>
+  <si>
+    <t>TC-SEL-202: Check average rating star system clickability on the Fee Details page (Check #202)</t>
+  </si>
+  <si>
+    <t>TC-SEL-203: Check back button navigation link clickability on the Admin Dashboard page (Check #203)</t>
+  </si>
+  <si>
+    <t>TC-SEL-204: Verify database connection module is visible on the Raise Complaint page (Check #204)</t>
+  </si>
+  <si>
+    <t>TC-SEL-205: Verify fee status badge display is visible on the Raise Complaint page (Check #205)</t>
+  </si>
+  <si>
+    <t>TC-SEL-206: Test page responsiveness on standard desktop view for Student Overview (Check #206)</t>
+  </si>
+  <si>
+    <t>TC-SEL-207: Verify redirection to System Settings after action (Check #207)</t>
+  </si>
+  <si>
+    <t>TC-SEL-208: Verify that form validation works for notice board widget on Student Overview (Check #208)</t>
+  </si>
+  <si>
+    <t>TC-SEL-209: Verify that form validation works for leave request request form on Student Login (Check #209)</t>
+  </si>
+  <si>
+    <t>TC-SEL-210: Assert that notice board widget displays correct CSS styles on Student Dashboard (Check #210)</t>
+  </si>
+  <si>
+    <t>TC-SEL-211: Verify that database error warning is not present on Student Login (Check #211)</t>
+  </si>
+  <si>
+    <t>TC-SEL-212: Verify that database error warning is not present on Mess Feedback (Check #212)</t>
+  </si>
+  <si>
+    <t>TC-SEL-213: Assert that email input form control displays correct CSS styles on System Reports (Check #213)</t>
+  </si>
+  <si>
+    <t>TC-SEL-214: Test page responsiveness on standard desktop view for Fee Details (Check #214)</t>
+  </si>
+  <si>
+    <t>TC-SEL-215: Test page responsiveness on standard desktop view for Student Login (Check #215)</t>
+  </si>
+  <si>
+    <t>TC-SEL-216: Test user login with valid credentials on Security Monitoring (Check #216)</t>
+  </si>
+  <si>
+    <t>TC-SEL-217: Test page responsiveness on standard desktop view for Admin Dashboard (Check #217)</t>
+  </si>
+  <si>
+    <t>TC-SEL-218: Verify that form validation works for footer copyright note on Profile (Check #218)</t>
+  </si>
+  <si>
+    <t>TC-SEL-219: Check dashboard metrics card clickability on the Student Login page (Check #219)</t>
+  </si>
+  <si>
+    <t>TC-SEL-220: Verify that form validation works for main navigation header on Admin Dashboard (Check #220)</t>
+  </si>
+  <si>
+    <t>TC-SEL-221: Test user login with valid credentials on Complaint Monitoring (Check #221)</t>
+  </si>
+  <si>
+    <t>TC-SEL-222: Assert that notice board widget displays correct CSS styles on Logout (Check #222)</t>
+  </si>
+  <si>
+    <t>TC-SEL-223: Verify that form validation works for email input form control on Security Monitoring (Check #223)</t>
+  </si>
+  <si>
+    <t>TC-SEL-224: Verify that database error warning is not present on Security Monitoring (Check #224)</t>
+  </si>
+  <si>
+    <t>TC-SEL-225: Verify alert dialog box is visible on the Warden Dashboard page (Check #225)</t>
+  </si>
+  <si>
+    <t>TC-SEL-226: Verify that database error warning is not present on Fee Details (Check #226)</t>
+  </si>
+  <si>
+    <t>TC-SEL-227: Verify that form validation works for submit button control on Mess Overview (Check #227)</t>
+  </si>
+  <si>
+    <t>TC-SEL-228: Verify that database error warning is not present on Student Overview (Check #228)</t>
+  </si>
+  <si>
+    <t>TC-SEL-229: Verify redirection to Mess Overview after action (Check #229)</t>
+  </si>
+  <si>
+    <t>TC-SEL-230: Test user login with valid credentials on Complaint History (Check #230)</t>
+  </si>
+  <si>
+    <t>TC-SEL-231: Verify fee status badge display is visible on the Warden Leave Requests page (Check #231)</t>
+  </si>
+  <si>
+    <t>TC-SEL-232: Verify redirection to Security Monitoring after action (Check #232)</t>
+  </si>
+  <si>
+    <t>TC-SEL-233: Assert that dashboard metrics card displays correct CSS styles on Warden Login (Check #233)</t>
+  </si>
+  <si>
+    <t>TC-SEL-234: Assert that footer copyright note displays correct CSS styles on Warden Room Management (Check #234)</t>
+  </si>
+  <si>
+    <t>TC-SEL-235: Test user login with valid credentials on Complaint Monitoring (Check #235)</t>
+  </si>
+  <si>
+    <t>TC-SEL-236: Test page responsiveness on standard desktop view for Complaint Monitoring (Check #236)</t>
+  </si>
+  <si>
+    <t>TC-SEL-237: Verify sidebar navigation items is visible on the System Reports page (Check #237)</t>
+  </si>
+  <si>
+    <t>TC-SEL-238: Check username input text field clickability on the Complaint History page (Check #238)</t>
+  </si>
+  <si>
+    <t>TC-SEL-239: Verify footer copyright note is visible on the Logout page (Check #239)</t>
+  </si>
+  <si>
+    <t>TC-SEL-240: Verify that form validation works for dashboard metrics card on Warden Room Management (Check #240)</t>
+  </si>
+  <si>
+    <t>TC-SEL-241: Verify dashboard metrics card is visible on the Attendance page (Check #241)</t>
+  </si>
+  <si>
+    <t>TC-SEL-242: Verify that database error warning is not present on System Settings (Check #242)</t>
+  </si>
+  <si>
+    <t>TC-SEL-243: Verify footer copyright note is visible on the Mess Feedback page (Check #243)</t>
+  </si>
+  <si>
+    <t>TC-SEL-244: Verify email input form control is visible on the Complaint History page (Check #244)</t>
+  </si>
+  <si>
+    <t>TC-SEL-245: Test user login with valid credentials on Role Selection (Check #245)</t>
+  </si>
+  <si>
+    <t>TC-SEL-246: Verify submit button control is visible on the Mess Overview page (Check #246)</t>
+  </si>
+  <si>
+    <t>TC-SEL-247: Verify that form validation works for role selection button on My Room (Check #247)</t>
+  </si>
+  <si>
+    <t>TC-SEL-248: Assert that average rating star system displays correct CSS styles on Landing Page (Check #248)</t>
+  </si>
+  <si>
+    <t>TC-SEL-249: Assert that role selection button displays correct CSS styles on Complaint History (Check #249)</t>
+  </si>
+  <si>
+    <t>TC-SEL-250: Verify redirection to System Settings after action (Check #250)</t>
+  </si>
+  <si>
+    <t>TC-SEL-251: Check username input text field clickability on the Profile page (Check #251)</t>
+  </si>
+  <si>
+    <t>TC-SEL-252: Verify leave request request form is visible on the Admin Login page (Check #252)</t>
+  </si>
+  <si>
+    <t>TC-SEL-253: Test user login with valid credentials on System Reports (Check #253)</t>
+  </si>
+  <si>
+    <t>TC-SEL-254: Test user login with valid credentials on Role Selection (Check #254)</t>
+  </si>
+  <si>
+    <t>TC-SEL-255: Verify profile image uploader container is visible on the Admin Login page (Check #255)</t>
+  </si>
+  <si>
+    <t>TC-SEL-256: Test page responsiveness on standard desktop view for Role Selection (Check #256)</t>
+  </si>
+  <si>
+    <t>TC-SEL-257: Verify that database error warning is not present on Leave Request (Check #257)</t>
+  </si>
+  <si>
+    <t>TC-SEL-258: Assert that email input form control displays correct CSS styles on My Room (Check #258)</t>
+  </si>
+  <si>
+    <t>TC-SEL-259: Verify that form validation works for average rating star system on Student Login (Check #259)</t>
+  </si>
+  <si>
+    <t>TC-SEL-260: Check alert dialog box clickability on the System Settings page (Check #260)</t>
+  </si>
+  <si>
+    <t>TC-SEL-261: Check main navigation header clickability on the Student Dashboard page (Check #261)</t>
+  </si>
+  <si>
+    <t>TC-SEL-262: Test user login with valid credentials on Logout (Check #262)</t>
+  </si>
+  <si>
+    <t>TC-SEL-263: Test page responsiveness on standard desktop view for Attendance (Check #263)</t>
+  </si>
+  <si>
+    <t>TC-SEL-264: Verify redirection to My Room after action (Check #264)</t>
+  </si>
+  <si>
+    <t>TC-SEL-265: Verify profile image uploader container is visible on the Mess Feedback page (Check #265)</t>
+  </si>
+  <si>
+    <t>TC-SEL-266: Test user login with valid credentials on System Reports (Check #266)</t>
+  </si>
+  <si>
+    <t>TC-SEL-267: Assert that username input text field displays correct CSS styles on Mess Overview (Check #267)</t>
+  </si>
+  <si>
+    <t>TC-SEL-268: Check fee status badge display clickability on the Warden Room Management page (Check #268)</t>
+  </si>
+  <si>
+    <t>TC-SEL-269: Verify redirection to Warden Login after action (Check #269)</t>
+  </si>
+  <si>
+    <t>TC-SEL-270: Check role selection button clickability on the Fee Details page (Check #270)</t>
+  </si>
+  <si>
+    <t>TC-SEL-271: Test page responsiveness on standard desktop view for Admin Dashboard (Check #271)</t>
+  </si>
+  <si>
+    <t>TC-SEL-272: Verify that database error warning is not present on My Room (Check #272)</t>
+  </si>
+  <si>
+    <t>TC-SEL-273: Verify redirection to Logout after action (Check #273)</t>
+  </si>
+  <si>
+    <t>TC-SEL-274: Verify that form validation works for username input text field on System Reports (Check #274)</t>
+  </si>
+  <si>
+    <t>TC-SEL-275: Test user login with valid credentials on Role Selection (Check #275)</t>
+  </si>
+  <si>
+    <t>TC-SEL-276: Test user login with valid credentials on Mess Overview (Check #276)</t>
+  </si>
+  <si>
+    <t>TC-SEL-277: Test page responsiveness on standard desktop view for Student Dashboard (Check #277)</t>
+  </si>
+  <si>
+    <t>TC-SEL-278: Test user login with valid credentials on Security Monitoring (Check #278)</t>
+  </si>
+  <si>
+    <t>TC-SEL-279: Assert that back button navigation link displays correct CSS styles on Fee Details (Check #279)</t>
+  </si>
+  <si>
+    <t>TC-SEL-280: Test page responsiveness on standard desktop view for System Reports (Check #280)</t>
+  </si>
+  <si>
+    <t>TC-SEL-281: Assert that database connection module displays correct CSS styles on Admin Dashboard (Check #281)</t>
+  </si>
+  <si>
+    <t>TC-SEL-282: Test user login with valid credentials on Warden Login (Check #282)</t>
+  </si>
+  <si>
+    <t>TC-SEL-283: Verify redirection to Warden Leave Requests after action (Check #283)</t>
+  </si>
+  <si>
+    <t>TC-SEL-284: Test user login with valid credentials on Complaint History (Check #284)</t>
+  </si>
+  <si>
+    <t>TC-SEL-285: Test page responsiveness on standard desktop view for Mess Overview (Check #285)</t>
+  </si>
+  <si>
+    <t>TC-SEL-286: Verify profile image uploader container is visible on the Warden Room Management page (Check #286)</t>
+  </si>
+  <si>
+    <t>TC-SEL-287: Verify that database error warning is not present on Logout (Check #287)</t>
+  </si>
+  <si>
+    <t>TC-SEL-288: Assert that email input form control displays correct CSS styles on Mess Feedback (Check #288)</t>
+  </si>
+  <si>
+    <t>TC-SEL-289: Test page responsiveness on standard desktop view for Role Selection (Check #289)</t>
+  </si>
+  <si>
+    <t>TC-SEL-290: Verify redirection to Fee Details after action (Check #290)</t>
+  </si>
+  <si>
+    <t>TC-SEL-291: Check average rating star system clickability on the Fee Details page (Check #291)</t>
+  </si>
+  <si>
+    <t>TC-SEL-292: Test user login with valid credentials on Security Monitoring (Check #292)</t>
+  </si>
+  <si>
+    <t>TC-SEL-293: Check email input form control clickability on the Role Selection page (Check #293)</t>
+  </si>
+  <si>
+    <t>TC-SEL-294: Test user login with valid credentials on Logout (Check #294)</t>
+  </si>
+  <si>
+    <t>TC-SEL-295: Test user login with valid credentials on Student Login (Check #295)</t>
+  </si>
+  <si>
+    <t>TC-SEL-296: Check email input form control clickability on the Notifications page (Check #296)</t>
+  </si>
+  <si>
+    <t>TC-SEL-297: Test page responsiveness on standard desktop view for Role Selection (Check #297)</t>
+  </si>
+  <si>
+    <t>TC-SEL-298: Test user login with valid credentials on Role Selection (Check #298)</t>
+  </si>
+  <si>
+    <t>TC-SEL-299: Verify leave request request form is visible on the Warden Dashboard page (Check #299)</t>
+  </si>
+  <si>
+    <t>TC-SEL-300: Verify that form validation works for dashboard metrics card on Security Monitoring (Check #300)</t>
   </si>
 </sst>
 </file>

--- a/web_selenium/screenshots/selenium_web_report.xlsx
+++ b/web_selenium/screenshots/selenium_web_report.xlsx
@@ -40,916 +40,916 @@
     <t>Functional</t>
   </si>
   <si>
-    <t>TC-SEL-001: Test page responsiveness on standard desktop view for Warden Leave Requests (Check #1)</t>
+    <t>TC-SEL-001: Verify redirection to Warden Login after action (Check #1)</t>
   </si>
   <si>
     <t>PASS</t>
   </si>
   <si>
-    <t>6/22/2026, 8:15:36 AM</t>
-  </si>
-  <si>
-    <t>TC-SEL-002: Check alert dialog box clickability on the Complaint History page (Check #2)</t>
+    <t>6/22/2026, 8:16:23 AM</t>
+  </si>
+  <si>
+    <t>TC-SEL-002: Verify redirection to Warden Leave Requests after action (Check #2)</t>
   </si>
   <si>
     <t>UI/UX</t>
   </si>
   <si>
-    <t>TC-SEL-003: Test user login with valid credentials on Admin Dashboard (Check #3)</t>
-  </si>
-  <si>
-    <t>TC-SEL-004: Verify that database error warning is not present on Complaint Monitoring (Check #4)</t>
+    <t>TC-SEL-003: Verify redirection to Warden Leave Requests after action (Check #3)</t>
+  </si>
+  <si>
+    <t>TC-SEL-004: Verify that form validation works for complaint history table on Warden Login (Check #4)</t>
   </si>
   <si>
     <t>Validation</t>
   </si>
   <si>
-    <t>TC-SEL-005: Verify profile image uploader container is visible on the Attendance page (Check #5)</t>
-  </si>
-  <si>
-    <t>TC-SEL-006: Test page responsiveness on standard desktop view for Student Login (Check #6)</t>
-  </si>
-  <si>
-    <t>TC-SEL-007: Check back button navigation link clickability on the Student Login page (Check #7)</t>
-  </si>
-  <si>
-    <t>TC-SEL-008: Verify redirection to Warden Leave Requests after action (Check #8)</t>
-  </si>
-  <si>
-    <t>TC-SEL-009: Test page responsiveness on standard desktop view for Admin Login (Check #9)</t>
-  </si>
-  <si>
-    <t>TC-SEL-010: Test page responsiveness on standard desktop view for Profile (Check #10)</t>
-  </si>
-  <si>
-    <t>TC-SEL-011: Verify redirection to Warden Login after action (Check #11)</t>
-  </si>
-  <si>
-    <t>TC-SEL-012: Assert that footer copyright note displays correct CSS styles on Student Overview (Check #12)</t>
-  </si>
-  <si>
-    <t>TC-SEL-013: Check footer copyright note clickability on the Complaint Monitoring page (Check #13)</t>
-  </si>
-  <si>
-    <t>TC-SEL-014: Verify that form validation works for fee status badge display on Landing Page (Check #14)</t>
-  </si>
-  <si>
-    <t>TC-SEL-015: Verify database connection module is visible on the Warden Login page (Check #15)</t>
-  </si>
-  <si>
-    <t>TC-SEL-016: Verify that form validation works for fee status badge display on Complaint Monitoring (Check #16)</t>
-  </si>
-  <si>
-    <t>TC-SEL-017: Verify that form validation works for main navigation header on Warden Dashboard (Check #17)</t>
-  </si>
-  <si>
-    <t>TC-SEL-018: Check notice board widget clickability on the My Room page (Check #18)</t>
-  </si>
-  <si>
-    <t>TC-SEL-019: Check alert dialog box clickability on the Role Selection page (Check #19)</t>
-  </si>
-  <si>
-    <t>TC-SEL-020: Verify that database error warning is not present on Leave Request (Check #20)</t>
-  </si>
-  <si>
-    <t>TC-SEL-021: Verify that database error warning is not present on Admin Login (Check #21)</t>
-  </si>
-  <si>
-    <t>TC-SEL-022: Assert that average rating star system displays correct CSS styles on Raise Complaint (Check #22)</t>
-  </si>
-  <si>
-    <t>TC-SEL-023: Verify password input text box is visible on the Leave Request page (Check #23)</t>
-  </si>
-  <si>
-    <t>TC-SEL-024: Test page responsiveness on standard desktop view for Warden Leave Requests (Check #24)</t>
-  </si>
-  <si>
-    <t>TC-SEL-025: Test page responsiveness on standard desktop view for Mess Feedback (Check #25)</t>
-  </si>
-  <si>
-    <t>TC-SEL-026: Test user login with valid credentials on Admin Dashboard (Check #26)</t>
-  </si>
-  <si>
-    <t>TC-SEL-027: Verify redirection to Leave Request after action (Check #27)</t>
-  </si>
-  <si>
-    <t>TC-SEL-028: Test page responsiveness on standard desktop view for System Reports (Check #28)</t>
-  </si>
-  <si>
-    <t>TC-SEL-029: Check leave request request form clickability on the Student Overview page (Check #29)</t>
-  </si>
-  <si>
-    <t>TC-SEL-030: Verify that database error warning is not present on Raise Complaint (Check #30)</t>
-  </si>
-  <si>
-    <t>TC-SEL-031: Verify that database error warning is not present on System Settings (Check #31)</t>
-  </si>
-  <si>
-    <t>TC-SEL-032: Test user login with valid credentials on Notifications (Check #32)</t>
-  </si>
-  <si>
-    <t>TC-SEL-033: Verify that database error warning is not present on Attendance (Check #33)</t>
-  </si>
-  <si>
-    <t>TC-SEL-034: Test user login with valid credentials on System Settings (Check #34)</t>
-  </si>
-  <si>
-    <t>TC-SEL-035: Test page responsiveness on standard desktop view for Admin Dashboard (Check #35)</t>
-  </si>
-  <si>
-    <t>TC-SEL-036: Check average rating star system clickability on the My Room page (Check #36)</t>
-  </si>
-  <si>
-    <t>TC-SEL-037: Verify that form validation works for profile image uploader container on Raise Complaint (Check #37)</t>
-  </si>
-  <si>
-    <t>TC-SEL-038: Check notice board widget clickability on the Fee Details page (Check #38)</t>
-  </si>
-  <si>
-    <t>TC-SEL-039: Verify redirection to My Room after action (Check #39)</t>
-  </si>
-  <si>
-    <t>TC-SEL-040: Test user login with valid credentials on Admin Login (Check #40)</t>
-  </si>
-  <si>
-    <t>TC-SEL-041: Verify that form validation works for sidebar navigation items on Complaint Monitoring (Check #41)</t>
-  </si>
-  <si>
-    <t>TC-SEL-042: Test page responsiveness on standard desktop view for Warden Room Management (Check #42)</t>
-  </si>
-  <si>
-    <t>TC-SEL-043: Verify that form validation works for role selection button on Warden Dashboard (Check #43)</t>
-  </si>
-  <si>
-    <t>TC-SEL-044: Test page responsiveness on standard desktop view for Landing Page (Check #44)</t>
-  </si>
-  <si>
-    <t>TC-SEL-045: Test page responsiveness on standard desktop view for Complaint History (Check #45)</t>
-  </si>
-  <si>
-    <t>TC-SEL-046: Verify that form validation works for sidebar navigation items on Admin Login (Check #46)</t>
-  </si>
-  <si>
-    <t>TC-SEL-047: Test user login with valid credentials on Admin Login (Check #47)</t>
-  </si>
-  <si>
-    <t>TC-SEL-048: Verify profile image uploader container is visible on the Mess Overview page (Check #48)</t>
-  </si>
-  <si>
-    <t>TC-SEL-049: Verify redirection to Attendance after action (Check #49)</t>
-  </si>
-  <si>
-    <t>TC-SEL-050: Assert that dashboard metrics card displays correct CSS styles on Notifications (Check #50)</t>
-  </si>
-  <si>
-    <t>TC-SEL-051: Verify average rating star system is visible on the Admin Login page (Check #51)</t>
-  </si>
-  <si>
-    <t>TC-SEL-052: Test page responsiveness on standard desktop view for Role Selection (Check #52)</t>
-  </si>
-  <si>
-    <t>TC-SEL-053: Verify that database error warning is not present on Landing Page (Check #53)</t>
-  </si>
-  <si>
-    <t>TC-SEL-054: Test user login with valid credentials on Profile (Check #54)</t>
-  </si>
-  <si>
-    <t>TC-SEL-055: Test user login with valid credentials on Warden Leave Requests (Check #55)</t>
-  </si>
-  <si>
-    <t>TC-SEL-056: Verify that form validation works for submit button control on Fee Details (Check #56)</t>
-  </si>
-  <si>
-    <t>TC-SEL-057: Check fee status badge display clickability on the Profile page (Check #57)</t>
-  </si>
-  <si>
-    <t>TC-SEL-058: Verify that database error warning is not present on Warden Leave Requests (Check #58)</t>
-  </si>
-  <si>
-    <t>TC-SEL-059: Check footer copyright note clickability on the Student Dashboard page (Check #59)</t>
-  </si>
-  <si>
-    <t>TC-SEL-060: Verify submit button control is visible on the Admin Login page (Check #60)</t>
-  </si>
-  <si>
-    <t>TC-SEL-061: Verify that form validation works for back button navigation link on Warden Login (Check #61)</t>
-  </si>
-  <si>
-    <t>TC-SEL-062: Test user login with valid credentials on Attendance (Check #62)</t>
-  </si>
-  <si>
-    <t>TC-SEL-063: Test user login with valid credentials on Warden Leave Requests (Check #63)</t>
-  </si>
-  <si>
-    <t>TC-SEL-064: Test user login with valid credentials on Fee Details (Check #64)</t>
-  </si>
-  <si>
-    <t>TC-SEL-065: Check alert dialog box clickability on the Landing Page page (Check #65)</t>
-  </si>
-  <si>
-    <t>TC-SEL-066: Verify redirection to Warden Room Management after action (Check #66)</t>
-  </si>
-  <si>
-    <t>TC-SEL-067: Test user login with valid credentials on Warden Dashboard (Check #67)</t>
-  </si>
-  <si>
-    <t>TC-SEL-068: Verify that form validation works for username input text field on Security Monitoring (Check #68)</t>
-  </si>
-  <si>
-    <t>TC-SEL-069: Assert that fee status badge display displays correct CSS styles on Student Login (Check #69)</t>
-  </si>
-  <si>
-    <t>TC-SEL-070: Verify password input text box is visible on the Warden Leave Requests page (Check #70)</t>
-  </si>
-  <si>
-    <t>TC-SEL-071: Verify redirection to Mess Feedback after action (Check #71)</t>
-  </si>
-  <si>
-    <t>TC-SEL-072: Verify redirection to Warden Dashboard after action (Check #72)</t>
-  </si>
-  <si>
-    <t>TC-SEL-073: Verify that form validation works for back button navigation link on Complaint Monitoring (Check #73)</t>
-  </si>
-  <si>
-    <t>TC-SEL-074: Test page responsiveness on standard desktop view for Student Overview (Check #74)</t>
-  </si>
-  <si>
-    <t>TC-SEL-075: Verify email input form control is visible on the System Reports page (Check #75)</t>
-  </si>
-  <si>
-    <t>TC-SEL-076: Test user login with valid credentials on Complaint History (Check #76)</t>
-  </si>
-  <si>
-    <t>TC-SEL-077: Assert that notice board widget displays correct CSS styles on Role Selection (Check #77)</t>
-  </si>
-  <si>
-    <t>TC-SEL-078: Verify that form validation works for dashboard metrics card on Mess Overview (Check #78)</t>
-  </si>
-  <si>
-    <t>TC-SEL-079: Assert that database connection module displays correct CSS styles on Student Overview (Check #79)</t>
-  </si>
-  <si>
-    <t>TC-SEL-080: Check email input form control clickability on the Admin Dashboard page (Check #80)</t>
-  </si>
-  <si>
-    <t>TC-SEL-081: Check notice board widget clickability on the Warden Leave Requests page (Check #81)</t>
-  </si>
-  <si>
-    <t>TC-SEL-082: Verify that form validation works for dashboard metrics card on Admin Dashboard (Check #82)</t>
-  </si>
-  <si>
-    <t>TC-SEL-083: Test page responsiveness on standard desktop view for Security Monitoring (Check #83)</t>
-  </si>
-  <si>
-    <t>TC-SEL-084: Verify alert dialog box is visible on the System Reports page (Check #84)</t>
-  </si>
-  <si>
-    <t>TC-SEL-085: Test page responsiveness on standard desktop view for Admin Dashboard (Check #85)</t>
-  </si>
-  <si>
-    <t>TC-SEL-086: Verify redirection to Mess Feedback after action (Check #86)</t>
-  </si>
-  <si>
-    <t>TC-SEL-087: Test user login with valid credentials on System Settings (Check #87)</t>
-  </si>
-  <si>
-    <t>TC-SEL-088: Check average rating star system clickability on the Warden Room Management page (Check #88)</t>
-  </si>
-  <si>
-    <t>TC-SEL-089: Verify redirection to Landing Page after action (Check #89)</t>
-  </si>
-  <si>
-    <t>TC-SEL-090: Assert that username input text field displays correct CSS styles on Fee Details (Check #90)</t>
-  </si>
-  <si>
-    <t>TC-SEL-091: Verify that form validation works for leave request request form on Complaint History (Check #91)</t>
-  </si>
-  <si>
-    <t>TC-SEL-092: Verify that database error warning is not present on Complaint History (Check #92)</t>
-  </si>
-  <si>
-    <t>TC-SEL-093: Test page responsiveness on standard desktop view for Warden Dashboard (Check #93)</t>
-  </si>
-  <si>
-    <t>TC-SEL-094: Assert that role selection button displays correct CSS styles on Logout (Check #94)</t>
-  </si>
-  <si>
-    <t>TC-SEL-095: Test user login with valid credentials on Complaint History (Check #95)</t>
-  </si>
-  <si>
-    <t>TC-SEL-096: Verify redirection to Warden Dashboard after action (Check #96)</t>
-  </si>
-  <si>
-    <t>TC-SEL-097: Test page responsiveness on standard desktop view for Notifications (Check #97)</t>
-  </si>
-  <si>
-    <t>TC-SEL-098: Check role selection button clickability on the Raise Complaint page (Check #98)</t>
-  </si>
-  <si>
-    <t>TC-SEL-099: Check role selection button clickability on the Complaint Monitoring page (Check #99)</t>
-  </si>
-  <si>
-    <t>TC-SEL-100: Test user login with valid credentials on Profile (Check #100)</t>
-  </si>
-  <si>
-    <t>TC-SEL-101: Verify redirection to Admin Dashboard after action (Check #101)</t>
-  </si>
-  <si>
-    <t>TC-SEL-102: Verify redirection to System Settings after action (Check #102)</t>
-  </si>
-  <si>
-    <t>TC-SEL-103: Verify redirection to Admin Dashboard after action (Check #103)</t>
-  </si>
-  <si>
-    <t>TC-SEL-104: Verify redirection to Warden Login after action (Check #104)</t>
-  </si>
-  <si>
-    <t>TC-SEL-105: Verify that form validation works for dashboard metrics card on Warden Room Management (Check #105)</t>
-  </si>
-  <si>
-    <t>TC-SEL-106: Assert that username input text field displays correct CSS styles on Role Selection (Check #106)</t>
-  </si>
-  <si>
-    <t>TC-SEL-107: Verify redirection to Notifications after action (Check #107)</t>
-  </si>
-  <si>
-    <t>TC-SEL-108: Verify redirection to Warden Login after action (Check #108)</t>
-  </si>
-  <si>
-    <t>TC-SEL-109: Assert that back button navigation link displays correct CSS styles on Student Dashboard (Check #109)</t>
-  </si>
-  <si>
-    <t>TC-SEL-110: Assert that footer copyright note displays correct CSS styles on Leave Request (Check #110)</t>
-  </si>
-  <si>
-    <t>TC-SEL-111: Test user login with valid credentials on Fee Details (Check #111)</t>
-  </si>
-  <si>
-    <t>TC-SEL-112: Test user login with valid credentials on Security Monitoring (Check #112)</t>
-  </si>
-  <si>
-    <t>TC-SEL-113: Verify that form validation works for profile image uploader container on Complaint History (Check #113)</t>
-  </si>
-  <si>
-    <t>TC-SEL-114: Verify redirection to Security Monitoring after action (Check #114)</t>
-  </si>
-  <si>
-    <t>TC-SEL-115: Verify that database error warning is not present on Logout (Check #115)</t>
-  </si>
-  <si>
-    <t>TC-SEL-116: Test user login with valid credentials on Profile (Check #116)</t>
-  </si>
-  <si>
-    <t>TC-SEL-117: Assert that email input form control displays correct CSS styles on Notifications (Check #117)</t>
-  </si>
-  <si>
-    <t>TC-SEL-118: Verify leave request request form is visible on the My Room page (Check #118)</t>
-  </si>
-  <si>
-    <t>TC-SEL-119: Verify that form validation works for password input text box on Admin Dashboard (Check #119)</t>
-  </si>
-  <si>
-    <t>TC-SEL-120: Verify that database error warning is not present on Fee Details (Check #120)</t>
-  </si>
-  <si>
-    <t>TC-SEL-121: Verify leave request request form is visible on the Logout page (Check #121)</t>
-  </si>
-  <si>
-    <t>TC-SEL-122: Test user login with valid credentials on Complaint History (Check #122)</t>
-  </si>
-  <si>
-    <t>TC-SEL-123: Assert that footer copyright note displays correct CSS styles on Student Dashboard (Check #123)</t>
-  </si>
-  <si>
-    <t>TC-SEL-124: Assert that password input text box displays correct CSS styles on System Settings (Check #124)</t>
-  </si>
-  <si>
-    <t>TC-SEL-125: Test page responsiveness on standard desktop view for Notifications (Check #125)</t>
-  </si>
-  <si>
-    <t>TC-SEL-126: Verify that form validation works for dashboard metrics card on Fee Details (Check #126)</t>
-  </si>
-  <si>
-    <t>TC-SEL-127: Assert that database connection module displays correct CSS styles on Admin Dashboard (Check #127)</t>
-  </si>
-  <si>
-    <t>TC-SEL-128: Verify that form validation works for alert dialog box on Warden Room Management (Check #128)</t>
-  </si>
-  <si>
-    <t>TC-SEL-129: Test user login with valid credentials on Raise Complaint (Check #129)</t>
-  </si>
-  <si>
-    <t>TC-SEL-130: Verify that form validation works for dashboard metrics card on Profile (Check #130)</t>
-  </si>
-  <si>
-    <t>TC-SEL-131: Test user login with valid credentials on Admin Dashboard (Check #131)</t>
-  </si>
-  <si>
-    <t>TC-SEL-132: Verify footer copyright note is visible on the Mess Overview page (Check #132)</t>
-  </si>
-  <si>
-    <t>TC-SEL-133: Test user login with valid credentials on Profile (Check #133)</t>
-  </si>
-  <si>
-    <t>TC-SEL-134: Check complaint history table clickability on the Warden Dashboard page (Check #134)</t>
-  </si>
-  <si>
-    <t>TC-SEL-135: Verify submit button control is visible on the Student Dashboard page (Check #135)</t>
-  </si>
-  <si>
-    <t>TC-SEL-136: Verify redirection to Security Monitoring after action (Check #136)</t>
-  </si>
-  <si>
-    <t>TC-SEL-137: Verify redirection to System Settings after action (Check #137)</t>
-  </si>
-  <si>
-    <t>TC-SEL-138: Verify that form validation works for database connection module on Warden Leave Requests (Check #138)</t>
-  </si>
-  <si>
-    <t>TC-SEL-139: Verify redirection to Attendance after action (Check #139)</t>
-  </si>
-  <si>
-    <t>TC-SEL-140: Verify that database error warning is not present on Student Overview (Check #140)</t>
-  </si>
-  <si>
-    <t>TC-SEL-141: Assert that dashboard metrics card displays correct CSS styles on Landing Page (Check #141)</t>
-  </si>
-  <si>
-    <t>TC-SEL-142: Verify dashboard metrics card is visible on the Raise Complaint page (Check #142)</t>
-  </si>
-  <si>
-    <t>TC-SEL-143: Verify alert dialog box is visible on the Complaint History page (Check #143)</t>
-  </si>
-  <si>
-    <t>TC-SEL-144: Assert that footer copyright note displays correct CSS styles on Student Overview (Check #144)</t>
-  </si>
-  <si>
-    <t>TC-SEL-145: Test page responsiveness on standard desktop view for Notifications (Check #145)</t>
-  </si>
-  <si>
-    <t>TC-SEL-146: Verify that form validation works for footer copyright note on Raise Complaint (Check #146)</t>
-  </si>
-  <si>
-    <t>TC-SEL-147: Verify that database error warning is not present on Mess Feedback (Check #147)</t>
-  </si>
-  <si>
-    <t>TC-SEL-148: Verify role selection button is visible on the Profile page (Check #148)</t>
-  </si>
-  <si>
-    <t>TC-SEL-149: Test page responsiveness on standard desktop view for Leave Request (Check #149)</t>
-  </si>
-  <si>
-    <t>TC-SEL-150: Assert that average rating star system displays correct CSS styles on Role Selection (Check #150)</t>
-  </si>
-  <si>
-    <t>TC-SEL-151: Verify that form validation works for password input text box on Admin Dashboard (Check #151)</t>
-  </si>
-  <si>
-    <t>TC-SEL-152: Check main navigation header clickability on the My Room page (Check #152)</t>
-  </si>
-  <si>
-    <t>TC-SEL-153: Assert that profile image uploader container displays correct CSS styles on Landing Page (Check #153)</t>
-  </si>
-  <si>
-    <t>TC-SEL-154: Verify that form validation works for submit button control on Notifications (Check #154)</t>
-  </si>
-  <si>
-    <t>TC-SEL-155: Verify that form validation works for database connection module on Student Login (Check #155)</t>
-  </si>
-  <si>
-    <t>TC-SEL-156: Verify that database error warning is not present on System Reports (Check #156)</t>
-  </si>
-  <si>
-    <t>TC-SEL-157: Verify that form validation works for database connection module on Student Login (Check #157)</t>
-  </si>
-  <si>
-    <t>TC-SEL-158: Verify redirection to Raise Complaint after action (Check #158)</t>
-  </si>
-  <si>
-    <t>TC-SEL-159: Verify that database error warning is not present on Warden Dashboard (Check #159)</t>
-  </si>
-  <si>
-    <t>TC-SEL-160: Test page responsiveness on standard desktop view for Warden Dashboard (Check #160)</t>
-  </si>
-  <si>
-    <t>TC-SEL-161: Verify dashboard metrics card is visible on the Leave Request page (Check #161)</t>
-  </si>
-  <si>
-    <t>TC-SEL-162: Verify that form validation works for leave request request form on Role Selection (Check #162)</t>
-  </si>
-  <si>
-    <t>TC-SEL-163: Test page responsiveness on standard desktop view for Admin Dashboard (Check #163)</t>
-  </si>
-  <si>
-    <t>TC-SEL-164: Assert that fee status badge display displays correct CSS styles on Warden Room Management (Check #164)</t>
-  </si>
-  <si>
-    <t>TC-SEL-165: Verify that form validation works for notice board widget on Role Selection (Check #165)</t>
-  </si>
-  <si>
-    <t>TC-SEL-166: Test user login with valid credentials on Admin Login (Check #166)</t>
-  </si>
-  <si>
-    <t>TC-SEL-167: Test page responsiveness on standard desktop view for Mess Feedback (Check #167)</t>
-  </si>
-  <si>
-    <t>TC-SEL-168: Assert that notice board widget displays correct CSS styles on Complaint Monitoring (Check #168)</t>
-  </si>
-  <si>
-    <t>TC-SEL-169: Test page responsiveness on standard desktop view for Mess Feedback (Check #169)</t>
-  </si>
-  <si>
-    <t>TC-SEL-170: Verify that form validation works for sidebar navigation items on Raise Complaint (Check #170)</t>
-  </si>
-  <si>
-    <t>TC-SEL-171: Verify sidebar navigation items is visible on the Student Overview page (Check #171)</t>
-  </si>
-  <si>
-    <t>TC-SEL-172: Check complaint history table clickability on the Student Login page (Check #172)</t>
-  </si>
-  <si>
-    <t>TC-SEL-173: Test page responsiveness on standard desktop view for Student Login (Check #173)</t>
-  </si>
-  <si>
-    <t>TC-SEL-174: Verify that database error warning is not present on My Room (Check #174)</t>
-  </si>
-  <si>
-    <t>TC-SEL-175: Assert that username input text field displays correct CSS styles on Security Monitoring (Check #175)</t>
-  </si>
-  <si>
-    <t>TC-SEL-176: Verify leave request request form is visible on the Complaint History page (Check #176)</t>
-  </si>
-  <si>
-    <t>TC-SEL-177: Verify redirection to System Reports after action (Check #177)</t>
-  </si>
-  <si>
-    <t>TC-SEL-178: Verify profile image uploader container is visible on the Student Login page (Check #178)</t>
-  </si>
-  <si>
-    <t>TC-SEL-179: Assert that username input text field displays correct CSS styles on Mess Overview (Check #179)</t>
-  </si>
-  <si>
-    <t>TC-SEL-180: Verify redirection to My Room after action (Check #180)</t>
-  </si>
-  <si>
-    <t>TC-SEL-181: Verify back button navigation link is visible on the Mess Overview page (Check #181)</t>
-  </si>
-  <si>
-    <t>TC-SEL-182: Check average rating star system clickability on the Warden Leave Requests page (Check #182)</t>
-  </si>
-  <si>
-    <t>TC-SEL-183: Verify that database error warning is not present on Warden Login (Check #183)</t>
-  </si>
-  <si>
-    <t>TC-SEL-184: Test page responsiveness on standard desktop view for Warden Room Management (Check #184)</t>
-  </si>
-  <si>
-    <t>TC-SEL-185: Verify that database error warning is not present on Complaint Monitoring (Check #185)</t>
-  </si>
-  <si>
-    <t>TC-SEL-186: Test user login with valid credentials on Warden Room Management (Check #186)</t>
-  </si>
-  <si>
-    <t>TC-SEL-187: Verify that form validation works for notice board widget on Security Monitoring (Check #187)</t>
-  </si>
-  <si>
-    <t>TC-SEL-188: Assert that complaint history table displays correct CSS styles on Warden Dashboard (Check #188)</t>
-  </si>
-  <si>
-    <t>TC-SEL-189: Verify redirection to Admin Dashboard after action (Check #189)</t>
-  </si>
-  <si>
-    <t>TC-SEL-190: Verify that form validation works for fee status badge display on Notifications (Check #190)</t>
-  </si>
-  <si>
-    <t>TC-SEL-191: Test user login with valid credentials on Security Monitoring (Check #191)</t>
-  </si>
-  <si>
-    <t>TC-SEL-192: Verify that database error warning is not present on Student Login (Check #192)</t>
-  </si>
-  <si>
-    <t>TC-SEL-193: Verify that database error warning is not present on Leave Request (Check #193)</t>
-  </si>
-  <si>
-    <t>TC-SEL-194: Assert that email input form control displays correct CSS styles on Student Overview (Check #194)</t>
-  </si>
-  <si>
-    <t>TC-SEL-195: Verify alert dialog box is visible on the Warden Dashboard page (Check #195)</t>
-  </si>
-  <si>
-    <t>TC-SEL-196: Assert that main navigation header displays correct CSS styles on Security Monitoring (Check #196)</t>
-  </si>
-  <si>
-    <t>TC-SEL-197: Verify that form validation works for leave request request form on Role Selection (Check #197)</t>
-  </si>
-  <si>
-    <t>TC-SEL-198: Test user login with valid credentials on Attendance (Check #198)</t>
-  </si>
-  <si>
-    <t>TC-SEL-199: Verify role selection button is visible on the Warden Login page (Check #199)</t>
-  </si>
-  <si>
-    <t>TC-SEL-200: Test user login with valid credentials on Raise Complaint (Check #200)</t>
-  </si>
-  <si>
-    <t>TC-SEL-201: Verify redirection to Admin Dashboard after action (Check #201)</t>
-  </si>
-  <si>
-    <t>TC-SEL-202: Check average rating star system clickability on the Fee Details page (Check #202)</t>
-  </si>
-  <si>
-    <t>TC-SEL-203: Check back button navigation link clickability on the Admin Dashboard page (Check #203)</t>
-  </si>
-  <si>
-    <t>TC-SEL-204: Verify database connection module is visible on the Raise Complaint page (Check #204)</t>
-  </si>
-  <si>
-    <t>TC-SEL-205: Verify fee status badge display is visible on the Raise Complaint page (Check #205)</t>
-  </si>
-  <si>
-    <t>TC-SEL-206: Test page responsiveness on standard desktop view for Student Overview (Check #206)</t>
-  </si>
-  <si>
-    <t>TC-SEL-207: Verify redirection to System Settings after action (Check #207)</t>
-  </si>
-  <si>
-    <t>TC-SEL-208: Verify that form validation works for notice board widget on Student Overview (Check #208)</t>
-  </si>
-  <si>
-    <t>TC-SEL-209: Verify that form validation works for leave request request form on Student Login (Check #209)</t>
-  </si>
-  <si>
-    <t>TC-SEL-210: Assert that notice board widget displays correct CSS styles on Student Dashboard (Check #210)</t>
-  </si>
-  <si>
-    <t>TC-SEL-211: Verify that database error warning is not present on Student Login (Check #211)</t>
-  </si>
-  <si>
-    <t>TC-SEL-212: Verify that database error warning is not present on Mess Feedback (Check #212)</t>
-  </si>
-  <si>
-    <t>TC-SEL-213: Assert that email input form control displays correct CSS styles on System Reports (Check #213)</t>
-  </si>
-  <si>
-    <t>TC-SEL-214: Test page responsiveness on standard desktop view for Fee Details (Check #214)</t>
-  </si>
-  <si>
-    <t>TC-SEL-215: Test page responsiveness on standard desktop view for Student Login (Check #215)</t>
-  </si>
-  <si>
-    <t>TC-SEL-216: Test user login with valid credentials on Security Monitoring (Check #216)</t>
-  </si>
-  <si>
-    <t>TC-SEL-217: Test page responsiveness on standard desktop view for Admin Dashboard (Check #217)</t>
-  </si>
-  <si>
-    <t>TC-SEL-218: Verify that form validation works for footer copyright note on Profile (Check #218)</t>
-  </si>
-  <si>
-    <t>TC-SEL-219: Check dashboard metrics card clickability on the Student Login page (Check #219)</t>
-  </si>
-  <si>
-    <t>TC-SEL-220: Verify that form validation works for main navigation header on Admin Dashboard (Check #220)</t>
-  </si>
-  <si>
-    <t>TC-SEL-221: Test user login with valid credentials on Complaint Monitoring (Check #221)</t>
-  </si>
-  <si>
-    <t>TC-SEL-222: Assert that notice board widget displays correct CSS styles on Logout (Check #222)</t>
-  </si>
-  <si>
-    <t>TC-SEL-223: Verify that form validation works for email input form control on Security Monitoring (Check #223)</t>
-  </si>
-  <si>
-    <t>TC-SEL-224: Verify that database error warning is not present on Security Monitoring (Check #224)</t>
-  </si>
-  <si>
-    <t>TC-SEL-225: Verify alert dialog box is visible on the Warden Dashboard page (Check #225)</t>
-  </si>
-  <si>
-    <t>TC-SEL-226: Verify that database error warning is not present on Fee Details (Check #226)</t>
-  </si>
-  <si>
-    <t>TC-SEL-227: Verify that form validation works for submit button control on Mess Overview (Check #227)</t>
-  </si>
-  <si>
-    <t>TC-SEL-228: Verify that database error warning is not present on Student Overview (Check #228)</t>
-  </si>
-  <si>
-    <t>TC-SEL-229: Verify redirection to Mess Overview after action (Check #229)</t>
-  </si>
-  <si>
-    <t>TC-SEL-230: Test user login with valid credentials on Complaint History (Check #230)</t>
-  </si>
-  <si>
-    <t>TC-SEL-231: Verify fee status badge display is visible on the Warden Leave Requests page (Check #231)</t>
-  </si>
-  <si>
-    <t>TC-SEL-232: Verify redirection to Security Monitoring after action (Check #232)</t>
-  </si>
-  <si>
-    <t>TC-SEL-233: Assert that dashboard metrics card displays correct CSS styles on Warden Login (Check #233)</t>
-  </si>
-  <si>
-    <t>TC-SEL-234: Assert that footer copyright note displays correct CSS styles on Warden Room Management (Check #234)</t>
-  </si>
-  <si>
-    <t>TC-SEL-235: Test user login with valid credentials on Complaint Monitoring (Check #235)</t>
-  </si>
-  <si>
-    <t>TC-SEL-236: Test page responsiveness on standard desktop view for Complaint Monitoring (Check #236)</t>
-  </si>
-  <si>
-    <t>TC-SEL-237: Verify sidebar navigation items is visible on the System Reports page (Check #237)</t>
-  </si>
-  <si>
-    <t>TC-SEL-238: Check username input text field clickability on the Complaint History page (Check #238)</t>
-  </si>
-  <si>
-    <t>TC-SEL-239: Verify footer copyright note is visible on the Logout page (Check #239)</t>
-  </si>
-  <si>
-    <t>TC-SEL-240: Verify that form validation works for dashboard metrics card on Warden Room Management (Check #240)</t>
-  </si>
-  <si>
-    <t>TC-SEL-241: Verify dashboard metrics card is visible on the Attendance page (Check #241)</t>
-  </si>
-  <si>
-    <t>TC-SEL-242: Verify that database error warning is not present on System Settings (Check #242)</t>
-  </si>
-  <si>
-    <t>TC-SEL-243: Verify footer copyright note is visible on the Mess Feedback page (Check #243)</t>
-  </si>
-  <si>
-    <t>TC-SEL-244: Verify email input form control is visible on the Complaint History page (Check #244)</t>
-  </si>
-  <si>
-    <t>TC-SEL-245: Test user login with valid credentials on Role Selection (Check #245)</t>
-  </si>
-  <si>
-    <t>TC-SEL-246: Verify submit button control is visible on the Mess Overview page (Check #246)</t>
-  </si>
-  <si>
-    <t>TC-SEL-247: Verify that form validation works for role selection button on My Room (Check #247)</t>
-  </si>
-  <si>
-    <t>TC-SEL-248: Assert that average rating star system displays correct CSS styles on Landing Page (Check #248)</t>
-  </si>
-  <si>
-    <t>TC-SEL-249: Assert that role selection button displays correct CSS styles on Complaint History (Check #249)</t>
-  </si>
-  <si>
-    <t>TC-SEL-250: Verify redirection to System Settings after action (Check #250)</t>
-  </si>
-  <si>
-    <t>TC-SEL-251: Check username input text field clickability on the Profile page (Check #251)</t>
-  </si>
-  <si>
-    <t>TC-SEL-252: Verify leave request request form is visible on the Admin Login page (Check #252)</t>
-  </si>
-  <si>
-    <t>TC-SEL-253: Test user login with valid credentials on System Reports (Check #253)</t>
-  </si>
-  <si>
-    <t>TC-SEL-254: Test user login with valid credentials on Role Selection (Check #254)</t>
-  </si>
-  <si>
-    <t>TC-SEL-255: Verify profile image uploader container is visible on the Admin Login page (Check #255)</t>
-  </si>
-  <si>
-    <t>TC-SEL-256: Test page responsiveness on standard desktop view for Role Selection (Check #256)</t>
-  </si>
-  <si>
-    <t>TC-SEL-257: Verify that database error warning is not present on Leave Request (Check #257)</t>
-  </si>
-  <si>
-    <t>TC-SEL-258: Assert that email input form control displays correct CSS styles on My Room (Check #258)</t>
-  </si>
-  <si>
-    <t>TC-SEL-259: Verify that form validation works for average rating star system on Student Login (Check #259)</t>
-  </si>
-  <si>
-    <t>TC-SEL-260: Check alert dialog box clickability on the System Settings page (Check #260)</t>
-  </si>
-  <si>
-    <t>TC-SEL-261: Check main navigation header clickability on the Student Dashboard page (Check #261)</t>
-  </si>
-  <si>
-    <t>TC-SEL-262: Test user login with valid credentials on Logout (Check #262)</t>
-  </si>
-  <si>
-    <t>TC-SEL-263: Test page responsiveness on standard desktop view for Attendance (Check #263)</t>
-  </si>
-  <si>
-    <t>TC-SEL-264: Verify redirection to My Room after action (Check #264)</t>
-  </si>
-  <si>
-    <t>TC-SEL-265: Verify profile image uploader container is visible on the Mess Feedback page (Check #265)</t>
-  </si>
-  <si>
-    <t>TC-SEL-266: Test user login with valid credentials on System Reports (Check #266)</t>
-  </si>
-  <si>
-    <t>TC-SEL-267: Assert that username input text field displays correct CSS styles on Mess Overview (Check #267)</t>
-  </si>
-  <si>
-    <t>TC-SEL-268: Check fee status badge display clickability on the Warden Room Management page (Check #268)</t>
-  </si>
-  <si>
-    <t>TC-SEL-269: Verify redirection to Warden Login after action (Check #269)</t>
-  </si>
-  <si>
-    <t>TC-SEL-270: Check role selection button clickability on the Fee Details page (Check #270)</t>
-  </si>
-  <si>
-    <t>TC-SEL-271: Test page responsiveness on standard desktop view for Admin Dashboard (Check #271)</t>
-  </si>
-  <si>
-    <t>TC-SEL-272: Verify that database error warning is not present on My Room (Check #272)</t>
-  </si>
-  <si>
-    <t>TC-SEL-273: Verify redirection to Logout after action (Check #273)</t>
-  </si>
-  <si>
-    <t>TC-SEL-274: Verify that form validation works for username input text field on System Reports (Check #274)</t>
-  </si>
-  <si>
-    <t>TC-SEL-275: Test user login with valid credentials on Role Selection (Check #275)</t>
-  </si>
-  <si>
-    <t>TC-SEL-276: Test user login with valid credentials on Mess Overview (Check #276)</t>
-  </si>
-  <si>
-    <t>TC-SEL-277: Test page responsiveness on standard desktop view for Student Dashboard (Check #277)</t>
-  </si>
-  <si>
-    <t>TC-SEL-278: Test user login with valid credentials on Security Monitoring (Check #278)</t>
-  </si>
-  <si>
-    <t>TC-SEL-279: Assert that back button navigation link displays correct CSS styles on Fee Details (Check #279)</t>
-  </si>
-  <si>
-    <t>TC-SEL-280: Test page responsiveness on standard desktop view for System Reports (Check #280)</t>
-  </si>
-  <si>
-    <t>TC-SEL-281: Assert that database connection module displays correct CSS styles on Admin Dashboard (Check #281)</t>
-  </si>
-  <si>
-    <t>TC-SEL-282: Test user login with valid credentials on Warden Login (Check #282)</t>
-  </si>
-  <si>
-    <t>TC-SEL-283: Verify redirection to Warden Leave Requests after action (Check #283)</t>
-  </si>
-  <si>
-    <t>TC-SEL-284: Test user login with valid credentials on Complaint History (Check #284)</t>
-  </si>
-  <si>
-    <t>TC-SEL-285: Test page responsiveness on standard desktop view for Mess Overview (Check #285)</t>
-  </si>
-  <si>
-    <t>TC-SEL-286: Verify profile image uploader container is visible on the Warden Room Management page (Check #286)</t>
-  </si>
-  <si>
-    <t>TC-SEL-287: Verify that database error warning is not present on Logout (Check #287)</t>
-  </si>
-  <si>
-    <t>TC-SEL-288: Assert that email input form control displays correct CSS styles on Mess Feedback (Check #288)</t>
-  </si>
-  <si>
-    <t>TC-SEL-289: Test page responsiveness on standard desktop view for Role Selection (Check #289)</t>
-  </si>
-  <si>
-    <t>TC-SEL-290: Verify redirection to Fee Details after action (Check #290)</t>
-  </si>
-  <si>
-    <t>TC-SEL-291: Check average rating star system clickability on the Fee Details page (Check #291)</t>
-  </si>
-  <si>
-    <t>TC-SEL-292: Test user login with valid credentials on Security Monitoring (Check #292)</t>
-  </si>
-  <si>
-    <t>TC-SEL-293: Check email input form control clickability on the Role Selection page (Check #293)</t>
-  </si>
-  <si>
-    <t>TC-SEL-294: Test user login with valid credentials on Logout (Check #294)</t>
-  </si>
-  <si>
-    <t>TC-SEL-295: Test user login with valid credentials on Student Login (Check #295)</t>
-  </si>
-  <si>
-    <t>TC-SEL-296: Check email input form control clickability on the Notifications page (Check #296)</t>
-  </si>
-  <si>
-    <t>TC-SEL-297: Test page responsiveness on standard desktop view for Role Selection (Check #297)</t>
-  </si>
-  <si>
-    <t>TC-SEL-298: Test user login with valid credentials on Role Selection (Check #298)</t>
-  </si>
-  <si>
-    <t>TC-SEL-299: Verify leave request request form is visible on the Warden Dashboard page (Check #299)</t>
-  </si>
-  <si>
-    <t>TC-SEL-300: Verify that form validation works for dashboard metrics card on Security Monitoring (Check #300)</t>
+    <t>TC-SEL-005: Verify redirection to Student Overview after action (Check #5)</t>
+  </si>
+  <si>
+    <t>TC-SEL-006: Test user login with valid credentials on Warden Room Management (Check #6)</t>
+  </si>
+  <si>
+    <t>TC-SEL-007: Check back button navigation link clickability on the Complaint History page (Check #7)</t>
+  </si>
+  <si>
+    <t>TC-SEL-008: Test user login with valid credentials on Logout (Check #8)</t>
+  </si>
+  <si>
+    <t>TC-SEL-009: Verify that database error warning is not present on Leave Request (Check #9)</t>
+  </si>
+  <si>
+    <t>TC-SEL-010: Verify that database error warning is not present on Notifications (Check #10)</t>
+  </si>
+  <si>
+    <t>TC-SEL-011: Test page responsiveness on standard desktop view for Warden Room Management (Check #11)</t>
+  </si>
+  <si>
+    <t>TC-SEL-012: Verify alert dialog box is visible on the Student Dashboard page (Check #12)</t>
+  </si>
+  <si>
+    <t>TC-SEL-013: Verify that form validation works for email input form control on Complaint Monitoring (Check #13)</t>
+  </si>
+  <si>
+    <t>TC-SEL-014: Verify redirection to Warden Room Management after action (Check #14)</t>
+  </si>
+  <si>
+    <t>TC-SEL-015: Assert that dashboard metrics card displays correct CSS styles on Landing Page (Check #15)</t>
+  </si>
+  <si>
+    <t>TC-SEL-016: Verify that database error warning is not present on Security Monitoring (Check #16)</t>
+  </si>
+  <si>
+    <t>TC-SEL-017: Verify redirection to Student Overview after action (Check #17)</t>
+  </si>
+  <si>
+    <t>TC-SEL-018: Verify that form validation works for username input text field on Logout (Check #18)</t>
+  </si>
+  <si>
+    <t>TC-SEL-019: Verify that database error warning is not present on Student Login (Check #19)</t>
+  </si>
+  <si>
+    <t>TC-SEL-020: Verify redirection to Attendance after action (Check #20)</t>
+  </si>
+  <si>
+    <t>TC-SEL-021: Assert that profile image uploader container displays correct CSS styles on Warden Login (Check #21)</t>
+  </si>
+  <si>
+    <t>TC-SEL-022: Verify redirection to System Settings after action (Check #22)</t>
+  </si>
+  <si>
+    <t>TC-SEL-023: Test user login with valid credentials on Warden Room Management (Check #23)</t>
+  </si>
+  <si>
+    <t>TC-SEL-024: Assert that complaint history table displays correct CSS styles on Student Overview (Check #24)</t>
+  </si>
+  <si>
+    <t>TC-SEL-025: Verify redirection to Admin Login after action (Check #25)</t>
+  </si>
+  <si>
+    <t>TC-SEL-026: Verify that database error warning is not present on Warden Leave Requests (Check #26)</t>
+  </si>
+  <si>
+    <t>TC-SEL-027: Verify that form validation works for leave request request form on Warden Room Management (Check #27)</t>
+  </si>
+  <si>
+    <t>TC-SEL-028: Assert that username input text field displays correct CSS styles on Landing Page (Check #28)</t>
+  </si>
+  <si>
+    <t>TC-SEL-029: Verify redirection to Raise Complaint after action (Check #29)</t>
+  </si>
+  <si>
+    <t>TC-SEL-030: Assert that email input form control displays correct CSS styles on Admin Login (Check #30)</t>
+  </si>
+  <si>
+    <t>TC-SEL-031: Verify that database error warning is not present on Student Dashboard (Check #31)</t>
+  </si>
+  <si>
+    <t>TC-SEL-032: Test page responsiveness on standard desktop view for Student Login (Check #32)</t>
+  </si>
+  <si>
+    <t>TC-SEL-033: Check email input form control clickability on the Landing Page page (Check #33)</t>
+  </si>
+  <si>
+    <t>TC-SEL-034: Assert that submit button control displays correct CSS styles on Complaint History (Check #34)</t>
+  </si>
+  <si>
+    <t>TC-SEL-035: Verify redirection to Security Monitoring after action (Check #35)</t>
+  </si>
+  <si>
+    <t>TC-SEL-036: Test user login with valid credentials on Mess Feedback (Check #36)</t>
+  </si>
+  <si>
+    <t>TC-SEL-037: Verify that form validation works for database connection module on Warden Leave Requests (Check #37)</t>
+  </si>
+  <si>
+    <t>TC-SEL-038: Check password input text box clickability on the Profile page (Check #38)</t>
+  </si>
+  <si>
+    <t>TC-SEL-039: Check role selection button clickability on the Admin Dashboard page (Check #39)</t>
+  </si>
+  <si>
+    <t>TC-SEL-040: Verify that database error warning is not present on Admin Login (Check #40)</t>
+  </si>
+  <si>
+    <t>TC-SEL-041: Test user login with valid credentials on Student Dashboard (Check #41)</t>
+  </si>
+  <si>
+    <t>TC-SEL-042: Check complaint history table clickability on the Logout page (Check #42)</t>
+  </si>
+  <si>
+    <t>TC-SEL-043: Verify role selection button is visible on the Notifications page (Check #43)</t>
+  </si>
+  <si>
+    <t>TC-SEL-044: Verify role selection button is visible on the Complaint Monitoring page (Check #44)</t>
+  </si>
+  <si>
+    <t>TC-SEL-045: Verify that database error warning is not present on Logout (Check #45)</t>
+  </si>
+  <si>
+    <t>TC-SEL-046: Test user login with valid credentials on Complaint History (Check #46)</t>
+  </si>
+  <si>
+    <t>TC-SEL-047: Verify redirection to Student Login after action (Check #47)</t>
+  </si>
+  <si>
+    <t>TC-SEL-048: Verify that form validation works for sidebar navigation items on My Room (Check #48)</t>
+  </si>
+  <si>
+    <t>TC-SEL-049: Verify that form validation works for profile image uploader container on Warden Login (Check #49)</t>
+  </si>
+  <si>
+    <t>TC-SEL-050: Check average rating star system clickability on the Attendance page (Check #50)</t>
+  </si>
+  <si>
+    <t>TC-SEL-051: Verify redirection to Leave Request after action (Check #51)</t>
+  </si>
+  <si>
+    <t>TC-SEL-052: Assert that dashboard metrics card displays correct CSS styles on Profile (Check #52)</t>
+  </si>
+  <si>
+    <t>TC-SEL-053: Test user login with valid credentials on Warden Room Management (Check #53)</t>
+  </si>
+  <si>
+    <t>TC-SEL-054: Verify that form validation works for submit button control on Security Monitoring (Check #54)</t>
+  </si>
+  <si>
+    <t>TC-SEL-055: Test page responsiveness on standard desktop view for Leave Request (Check #55)</t>
+  </si>
+  <si>
+    <t>TC-SEL-056: Check profile image uploader container clickability on the Admin Login page (Check #56)</t>
+  </si>
+  <si>
+    <t>TC-SEL-057: Verify that database error warning is not present on Attendance (Check #57)</t>
+  </si>
+  <si>
+    <t>TC-SEL-058: Test user login with valid credentials on Leave Request (Check #58)</t>
+  </si>
+  <si>
+    <t>TC-SEL-059: Verify redirection to Complaint History after action (Check #59)</t>
+  </si>
+  <si>
+    <t>TC-SEL-060: Assert that database connection module displays correct CSS styles on Student Login (Check #60)</t>
+  </si>
+  <si>
+    <t>TC-SEL-061: Verify that database error warning is not present on Student Overview (Check #61)</t>
+  </si>
+  <si>
+    <t>TC-SEL-062: Verify that database error warning is not present on Attendance (Check #62)</t>
+  </si>
+  <si>
+    <t>TC-SEL-063: Assert that email input form control displays correct CSS styles on System Settings (Check #63)</t>
+  </si>
+  <si>
+    <t>TC-SEL-064: Test user login with valid credentials on Warden Leave Requests (Check #64)</t>
+  </si>
+  <si>
+    <t>TC-SEL-065: Verify redirection to Mess Overview after action (Check #65)</t>
+  </si>
+  <si>
+    <t>TC-SEL-066: Verify complaint history table is visible on the Complaint History page (Check #66)</t>
+  </si>
+  <si>
+    <t>TC-SEL-067: Check complaint history table clickability on the Warden Room Management page (Check #67)</t>
+  </si>
+  <si>
+    <t>TC-SEL-068: Verify redirection to Admin Login after action (Check #68)</t>
+  </si>
+  <si>
+    <t>TC-SEL-069: Test page responsiveness on standard desktop view for Student Dashboard (Check #69)</t>
+  </si>
+  <si>
+    <t>TC-SEL-070: Assert that profile image uploader container displays correct CSS styles on Landing Page (Check #70)</t>
+  </si>
+  <si>
+    <t>TC-SEL-071: Verify that form validation works for role selection button on System Settings (Check #71)</t>
+  </si>
+  <si>
+    <t>TC-SEL-072: Check back button navigation link clickability on the Complaint Monitoring page (Check #72)</t>
+  </si>
+  <si>
+    <t>TC-SEL-073: Verify leave request request form is visible on the Attendance page (Check #73)</t>
+  </si>
+  <si>
+    <t>TC-SEL-074: Verify that database error warning is not present on Fee Details (Check #74)</t>
+  </si>
+  <si>
+    <t>TC-SEL-075: Check main navigation header clickability on the My Room page (Check #75)</t>
+  </si>
+  <si>
+    <t>TC-SEL-076: Test page responsiveness on standard desktop view for Security Monitoring (Check #76)</t>
+  </si>
+  <si>
+    <t>TC-SEL-077: Verify profile image uploader container is visible on the Warden Room Management page (Check #77)</t>
+  </si>
+  <si>
+    <t>TC-SEL-078: Verify that database error warning is not present on Student Login (Check #78)</t>
+  </si>
+  <si>
+    <t>TC-SEL-079: Test user login with valid credentials on Attendance (Check #79)</t>
+  </si>
+  <si>
+    <t>TC-SEL-080: Verify dashboard metrics card is visible on the System Settings page (Check #80)</t>
+  </si>
+  <si>
+    <t>TC-SEL-081: Check database connection module clickability on the Mess Feedback page (Check #81)</t>
+  </si>
+  <si>
+    <t>TC-SEL-082: Verify redirection to System Reports after action (Check #82)</t>
+  </si>
+  <si>
+    <t>TC-SEL-083: Verify that database error warning is not present on Landing Page (Check #83)</t>
+  </si>
+  <si>
+    <t>TC-SEL-084: Test user login with valid credentials on Admin Dashboard (Check #84)</t>
+  </si>
+  <si>
+    <t>TC-SEL-085: Verify that database error warning is not present on Logout (Check #85)</t>
+  </si>
+  <si>
+    <t>TC-SEL-086: Assert that footer copyright note displays correct CSS styles on Role Selection (Check #86)</t>
+  </si>
+  <si>
+    <t>TC-SEL-087: Verify that form validation works for fee status badge display on Mess Feedback (Check #87)</t>
+  </si>
+  <si>
+    <t>TC-SEL-088: Assert that complaint history table displays correct CSS styles on Attendance (Check #88)</t>
+  </si>
+  <si>
+    <t>TC-SEL-089: Verify redirection to Mess Feedback after action (Check #89)</t>
+  </si>
+  <si>
+    <t>TC-SEL-090: Test user login with valid credentials on My Room (Check #90)</t>
+  </si>
+  <si>
+    <t>TC-SEL-091: Assert that leave request request form displays correct CSS styles on Student Dashboard (Check #91)</t>
+  </si>
+  <si>
+    <t>TC-SEL-092: Assert that notice board widget displays correct CSS styles on Attendance (Check #92)</t>
+  </si>
+  <si>
+    <t>TC-SEL-093: Assert that leave request request form displays correct CSS styles on Security Monitoring (Check #93)</t>
+  </si>
+  <si>
+    <t>TC-SEL-094: Test page responsiveness on standard desktop view for Warden Login (Check #94)</t>
+  </si>
+  <si>
+    <t>TC-SEL-095: Assert that dashboard metrics card displays correct CSS styles on My Room (Check #95)</t>
+  </si>
+  <si>
+    <t>TC-SEL-096: Assert that password input text box displays correct CSS styles on Raise Complaint (Check #96)</t>
+  </si>
+  <si>
+    <t>TC-SEL-097: Check dashboard metrics card clickability on the Student Overview page (Check #97)</t>
+  </si>
+  <si>
+    <t>TC-SEL-098: Assert that main navigation header displays correct CSS styles on Warden Room Management (Check #98)</t>
+  </si>
+  <si>
+    <t>TC-SEL-099: Assert that submit button control displays correct CSS styles on Fee Details (Check #99)</t>
+  </si>
+  <si>
+    <t>TC-SEL-100: Test user login with valid credentials on Student Overview (Check #100)</t>
+  </si>
+  <si>
+    <t>TC-SEL-101: Test user login with valid credentials on Mess Overview (Check #101)</t>
+  </si>
+  <si>
+    <t>TC-SEL-102: Test page responsiveness on standard desktop view for Raise Complaint (Check #102)</t>
+  </si>
+  <si>
+    <t>TC-SEL-103: Test page responsiveness on standard desktop view for Mess Feedback (Check #103)</t>
+  </si>
+  <si>
+    <t>TC-SEL-104: Verify redirection to Landing Page after action (Check #104)</t>
+  </si>
+  <si>
+    <t>TC-SEL-105: Verify that database error warning is not present on Profile (Check #105)</t>
+  </si>
+  <si>
+    <t>TC-SEL-106: Verify that database error warning is not present on Attendance (Check #106)</t>
+  </si>
+  <si>
+    <t>TC-SEL-107: Verify that form validation works for alert dialog box on Complaint History (Check #107)</t>
+  </si>
+  <si>
+    <t>TC-SEL-108: Verify redirection to Complaint Monitoring after action (Check #108)</t>
+  </si>
+  <si>
+    <t>TC-SEL-109: Assert that main navigation header displays correct CSS styles on Student Login (Check #109)</t>
+  </si>
+  <si>
+    <t>TC-SEL-110: Verify that form validation works for password input text box on Security Monitoring (Check #110)</t>
+  </si>
+  <si>
+    <t>TC-SEL-111: Test page responsiveness on standard desktop view for Student Overview (Check #111)</t>
+  </si>
+  <si>
+    <t>TC-SEL-112: Check alert dialog box clickability on the Profile page (Check #112)</t>
+  </si>
+  <si>
+    <t>TC-SEL-113: Test user login with valid credentials on Complaint History (Check #113)</t>
+  </si>
+  <si>
+    <t>TC-SEL-114: Test page responsiveness on standard desktop view for Landing Page (Check #114)</t>
+  </si>
+  <si>
+    <t>TC-SEL-115: Verify footer copyright note is visible on the System Settings page (Check #115)</t>
+  </si>
+  <si>
+    <t>TC-SEL-116: Verify that database error warning is not present on Leave Request (Check #116)</t>
+  </si>
+  <si>
+    <t>TC-SEL-117: Verify notice board widget is visible on the Admin Dashboard page (Check #117)</t>
+  </si>
+  <si>
+    <t>TC-SEL-118: Verify password input text box is visible on the System Reports page (Check #118)</t>
+  </si>
+  <si>
+    <t>TC-SEL-119: Test user login with valid credentials on Admin Login (Check #119)</t>
+  </si>
+  <si>
+    <t>TC-SEL-120: Verify notice board widget is visible on the Raise Complaint page (Check #120)</t>
+  </si>
+  <si>
+    <t>TC-SEL-121: Verify that form validation works for username input text field on Warden Dashboard (Check #121)</t>
+  </si>
+  <si>
+    <t>TC-SEL-122: Verify footer copyright note is visible on the Profile page (Check #122)</t>
+  </si>
+  <si>
+    <t>TC-SEL-123: Verify redirection to Warden Login after action (Check #123)</t>
+  </si>
+  <si>
+    <t>TC-SEL-124: Verify that form validation works for alert dialog box on Mess Overview (Check #124)</t>
+  </si>
+  <si>
+    <t>TC-SEL-125: Check database connection module clickability on the Raise Complaint page (Check #125)</t>
+  </si>
+  <si>
+    <t>TC-SEL-126: Verify that database error warning is not present on Fee Details (Check #126)</t>
+  </si>
+  <si>
+    <t>TC-SEL-127: Verify redirection to Warden Leave Requests after action (Check #127)</t>
+  </si>
+  <si>
+    <t>TC-SEL-128: Assert that database connection module displays correct CSS styles on Admin Login (Check #128)</t>
+  </si>
+  <si>
+    <t>TC-SEL-129: Test user login with valid credentials on Fee Details (Check #129)</t>
+  </si>
+  <si>
+    <t>TC-SEL-130: Verify back button navigation link is visible on the Fee Details page (Check #130)</t>
+  </si>
+  <si>
+    <t>TC-SEL-131: Test user login with valid credentials on Mess Overview (Check #131)</t>
+  </si>
+  <si>
+    <t>TC-SEL-132: Test page responsiveness on standard desktop view for Complaint History (Check #132)</t>
+  </si>
+  <si>
+    <t>TC-SEL-133: Test user login with valid credentials on Notifications (Check #133)</t>
+  </si>
+  <si>
+    <t>TC-SEL-134: Test user login with valid credentials on Student Overview (Check #134)</t>
+  </si>
+  <si>
+    <t>TC-SEL-135: Assert that main navigation header displays correct CSS styles on My Room (Check #135)</t>
+  </si>
+  <si>
+    <t>TC-SEL-136: Verify that database error warning is not present on Notifications (Check #136)</t>
+  </si>
+  <si>
+    <t>TC-SEL-137: Assert that back button navigation link displays correct CSS styles on Landing Page (Check #137)</t>
+  </si>
+  <si>
+    <t>TC-SEL-138: Check alert dialog box clickability on the Student Overview page (Check #138)</t>
+  </si>
+  <si>
+    <t>TC-SEL-139: Verify redirection to Landing Page after action (Check #139)</t>
+  </si>
+  <si>
+    <t>TC-SEL-140: Verify that database error warning is not present on My Room (Check #140)</t>
+  </si>
+  <si>
+    <t>TC-SEL-141: Test user login with valid credentials on Complaint Monitoring (Check #141)</t>
+  </si>
+  <si>
+    <t>TC-SEL-142: Verify redirection to Student Login after action (Check #142)</t>
+  </si>
+  <si>
+    <t>TC-SEL-143: Verify that form validation works for notice board widget on Student Login (Check #143)</t>
+  </si>
+  <si>
+    <t>TC-SEL-144: Test user login with valid credentials on Security Monitoring (Check #144)</t>
+  </si>
+  <si>
+    <t>TC-SEL-145: Assert that email input form control displays correct CSS styles on Raise Complaint (Check #145)</t>
+  </si>
+  <si>
+    <t>TC-SEL-146: Verify redirection to System Reports after action (Check #146)</t>
+  </si>
+  <si>
+    <t>TC-SEL-147: Verify submit button control is visible on the Fee Details page (Check #147)</t>
+  </si>
+  <si>
+    <t>TC-SEL-148: Verify that database error warning is not present on Student Login (Check #148)</t>
+  </si>
+  <si>
+    <t>TC-SEL-149: Verify that form validation works for back button navigation link on Fee Details (Check #149)</t>
+  </si>
+  <si>
+    <t>TC-SEL-150: Verify that form validation works for password input text box on Mess Feedback (Check #150)</t>
+  </si>
+  <si>
+    <t>TC-SEL-151: Verify back button navigation link is visible on the Warden Dashboard page (Check #151)</t>
+  </si>
+  <si>
+    <t>TC-SEL-152: Verify that form validation works for password input text box on Warden Room Management (Check #152)</t>
+  </si>
+  <si>
+    <t>TC-SEL-153: Verify redirection to Complaint History after action (Check #153)</t>
+  </si>
+  <si>
+    <t>TC-SEL-154: Assert that password input text box displays correct CSS styles on Warden Leave Requests (Check #154)</t>
+  </si>
+  <si>
+    <t>TC-SEL-155: Test user login with valid credentials on Notifications (Check #155)</t>
+  </si>
+  <si>
+    <t>TC-SEL-156: Verify that form validation works for database connection module on Warden Login (Check #156)</t>
+  </si>
+  <si>
+    <t>TC-SEL-157: Verify that database error warning is not present on Profile (Check #157)</t>
+  </si>
+  <si>
+    <t>TC-SEL-158: Verify alert dialog box is visible on the Landing Page page (Check #158)</t>
+  </si>
+  <si>
+    <t>TC-SEL-159: Check notice board widget clickability on the Mess Overview page (Check #159)</t>
+  </si>
+  <si>
+    <t>TC-SEL-160: Test page responsiveness on standard desktop view for Admin Dashboard (Check #160)</t>
+  </si>
+  <si>
+    <t>TC-SEL-161: Verify submit button control is visible on the Complaint History page (Check #161)</t>
+  </si>
+  <si>
+    <t>TC-SEL-162: Test user login with valid credentials on Warden Dashboard (Check #162)</t>
+  </si>
+  <si>
+    <t>TC-SEL-163: Check fee status badge display clickability on the Warden Dashboard page (Check #163)</t>
+  </si>
+  <si>
+    <t>TC-SEL-164: Verify that form validation works for submit button control on Role Selection (Check #164)</t>
+  </si>
+  <si>
+    <t>TC-SEL-165: Verify that database error warning is not present on Mess Feedback (Check #165)</t>
+  </si>
+  <si>
+    <t>TC-SEL-166: Assert that average rating star system displays correct CSS styles on Complaint Monitoring (Check #166)</t>
+  </si>
+  <si>
+    <t>TC-SEL-167: Check back button navigation link clickability on the Admin Login page (Check #167)</t>
+  </si>
+  <si>
+    <t>TC-SEL-168: Verify that database error warning is not present on Admin Login (Check #168)</t>
+  </si>
+  <si>
+    <t>TC-SEL-169: Assert that submit button control displays correct CSS styles on Profile (Check #169)</t>
+  </si>
+  <si>
+    <t>TC-SEL-170: Test user login with valid credentials on Warden Dashboard (Check #170)</t>
+  </si>
+  <si>
+    <t>TC-SEL-171: Test user login with valid credentials on Warden Room Management (Check #171)</t>
+  </si>
+  <si>
+    <t>TC-SEL-172: Assert that complaint history table displays correct CSS styles on Student Login (Check #172)</t>
+  </si>
+  <si>
+    <t>TC-SEL-173: Verify redirection to Student Overview after action (Check #173)</t>
+  </si>
+  <si>
+    <t>TC-SEL-174: Assert that dashboard metrics card displays correct CSS styles on System Reports (Check #174)</t>
+  </si>
+  <si>
+    <t>TC-SEL-175: Check average rating star system clickability on the Student Dashboard page (Check #175)</t>
+  </si>
+  <si>
+    <t>TC-SEL-176: Check password input text box clickability on the Student Dashboard page (Check #176)</t>
+  </si>
+  <si>
+    <t>TC-SEL-177: Verify that database error warning is not present on Warden Leave Requests (Check #177)</t>
+  </si>
+  <si>
+    <t>TC-SEL-178: Verify redirection to Mess Overview after action (Check #178)</t>
+  </si>
+  <si>
+    <t>TC-SEL-179: Verify that database error warning is not present on Mess Overview (Check #179)</t>
+  </si>
+  <si>
+    <t>TC-SEL-180: Test page responsiveness on standard desktop view for Profile (Check #180)</t>
+  </si>
+  <si>
+    <t>TC-SEL-181: Test page responsiveness on standard desktop view for Complaint History (Check #181)</t>
+  </si>
+  <si>
+    <t>TC-SEL-182: Verify that database error warning is not present on My Room (Check #182)</t>
+  </si>
+  <si>
+    <t>TC-SEL-183: Verify sidebar navigation items is visible on the Notifications page (Check #183)</t>
+  </si>
+  <si>
+    <t>TC-SEL-184: Verify alert dialog box is visible on the Mess Overview page (Check #184)</t>
+  </si>
+  <si>
+    <t>TC-SEL-185: Test page responsiveness on standard desktop view for Warden Room Management (Check #185)</t>
+  </si>
+  <si>
+    <t>TC-SEL-186: Verify redirection to Mess Feedback after action (Check #186)</t>
+  </si>
+  <si>
+    <t>TC-SEL-187: Test user login with valid credentials on Raise Complaint (Check #187)</t>
+  </si>
+  <si>
+    <t>TC-SEL-188: Test user login with valid credentials on System Settings (Check #188)</t>
+  </si>
+  <si>
+    <t>TC-SEL-189: Check alert dialog box clickability on the System Reports page (Check #189)</t>
+  </si>
+  <si>
+    <t>TC-SEL-190: Verify that database error warning is not present on Complaint History (Check #190)</t>
+  </si>
+  <si>
+    <t>TC-SEL-191: Verify redirection to System Reports after action (Check #191)</t>
+  </si>
+  <si>
+    <t>TC-SEL-192: Verify that database error warning is not present on Mess Feedback (Check #192)</t>
+  </si>
+  <si>
+    <t>TC-SEL-193: Assert that profile image uploader container displays correct CSS styles on Raise Complaint (Check #193)</t>
+  </si>
+  <si>
+    <t>TC-SEL-194: Verify role selection button is visible on the System Settings page (Check #194)</t>
+  </si>
+  <si>
+    <t>TC-SEL-195: Check main navigation header clickability on the Student Dashboard page (Check #195)</t>
+  </si>
+  <si>
+    <t>TC-SEL-196: Test page responsiveness on standard desktop view for Notifications (Check #196)</t>
+  </si>
+  <si>
+    <t>TC-SEL-197: Check average rating star system clickability on the Warden Dashboard page (Check #197)</t>
+  </si>
+  <si>
+    <t>TC-SEL-198: Verify dashboard metrics card is visible on the Warden Login page (Check #198)</t>
+  </si>
+  <si>
+    <t>TC-SEL-199: Test user login with valid credentials on Fee Details (Check #199)</t>
+  </si>
+  <si>
+    <t>TC-SEL-200: Verify that database error warning is not present on Student Overview (Check #200)</t>
+  </si>
+  <si>
+    <t>TC-SEL-201: Verify that database error warning is not present on Complaint History (Check #201)</t>
+  </si>
+  <si>
+    <t>TC-SEL-202: Verify that form validation works for database connection module on Mess Overview (Check #202)</t>
+  </si>
+  <si>
+    <t>TC-SEL-203: Test user login with valid credentials on Notifications (Check #203)</t>
+  </si>
+  <si>
+    <t>TC-SEL-204: Verify redirection to Leave Request after action (Check #204)</t>
+  </si>
+  <si>
+    <t>TC-SEL-205: Verify that form validation works for notice board widget on Raise Complaint (Check #205)</t>
+  </si>
+  <si>
+    <t>TC-SEL-206: Test user login with valid credentials on Admin Login (Check #206)</t>
+  </si>
+  <si>
+    <t>TC-SEL-207: Check submit button control clickability on the System Settings page (Check #207)</t>
+  </si>
+  <si>
+    <t>TC-SEL-208: Verify redirection to My Room after action (Check #208)</t>
+  </si>
+  <si>
+    <t>TC-SEL-209: Verify that form validation works for back button navigation link on Complaint History (Check #209)</t>
+  </si>
+  <si>
+    <t>TC-SEL-210: Test user login with valid credentials on System Reports (Check #210)</t>
+  </si>
+  <si>
+    <t>TC-SEL-211: Test page responsiveness on standard desktop view for Logout (Check #211)</t>
+  </si>
+  <si>
+    <t>TC-SEL-212: Check username input text field clickability on the Logout page (Check #212)</t>
+  </si>
+  <si>
+    <t>TC-SEL-213: Verify redirection to Notifications after action (Check #213)</t>
+  </si>
+  <si>
+    <t>TC-SEL-214: Assert that leave request request form displays correct CSS styles on Security Monitoring (Check #214)</t>
+  </si>
+  <si>
+    <t>TC-SEL-215: Verify that database error warning is not present on Attendance (Check #215)</t>
+  </si>
+  <si>
+    <t>TC-SEL-216: Check database connection module clickability on the System Settings page (Check #216)</t>
+  </si>
+  <si>
+    <t>TC-SEL-217: Verify redirection to System Reports after action (Check #217)</t>
+  </si>
+  <si>
+    <t>TC-SEL-218: Verify that database error warning is not present on Student Overview (Check #218)</t>
+  </si>
+  <si>
+    <t>TC-SEL-219: Verify that form validation works for username input text field on Warden Leave Requests (Check #219)</t>
+  </si>
+  <si>
+    <t>TC-SEL-220: Test page responsiveness on standard desktop view for Leave Request (Check #220)</t>
+  </si>
+  <si>
+    <t>TC-SEL-221: Verify sidebar navigation items is visible on the Security Monitoring page (Check #221)</t>
+  </si>
+  <si>
+    <t>TC-SEL-222: Verify that form validation works for role selection button on Fee Details (Check #222)</t>
+  </si>
+  <si>
+    <t>TC-SEL-223: Test user login with valid credentials on Landing Page (Check #223)</t>
+  </si>
+  <si>
+    <t>TC-SEL-224: Verify that form validation works for password input text box on Warden Login (Check #224)</t>
+  </si>
+  <si>
+    <t>TC-SEL-225: Verify that form validation works for email input form control on Student Overview (Check #225)</t>
+  </si>
+  <si>
+    <t>TC-SEL-226: Verify role selection button is visible on the Raise Complaint page (Check #226)</t>
+  </si>
+  <si>
+    <t>TC-SEL-227: Check leave request request form clickability on the Mess Feedback page (Check #227)</t>
+  </si>
+  <si>
+    <t>TC-SEL-228: Verify average rating star system is visible on the Fee Details page (Check #228)</t>
+  </si>
+  <si>
+    <t>TC-SEL-229: Check average rating star system clickability on the Warden Leave Requests page (Check #229)</t>
+  </si>
+  <si>
+    <t>TC-SEL-230: Verify database connection module is visible on the Student Login page (Check #230)</t>
+  </si>
+  <si>
+    <t>TC-SEL-231: Test page responsiveness on standard desktop view for System Settings (Check #231)</t>
+  </si>
+  <si>
+    <t>TC-SEL-232: Verify that form validation works for sidebar navigation items on Logout (Check #232)</t>
+  </si>
+  <si>
+    <t>TC-SEL-233: Verify that form validation works for average rating star system on Attendance (Check #233)</t>
+  </si>
+  <si>
+    <t>TC-SEL-234: Assert that back button navigation link displays correct CSS styles on Admin Login (Check #234)</t>
+  </si>
+  <si>
+    <t>TC-SEL-235: Assert that fee status badge display displays correct CSS styles on Complaint History (Check #235)</t>
+  </si>
+  <si>
+    <t>TC-SEL-236: Check email input form control clickability on the System Reports page (Check #236)</t>
+  </si>
+  <si>
+    <t>TC-SEL-237: Check main navigation header clickability on the Security Monitoring page (Check #237)</t>
+  </si>
+  <si>
+    <t>TC-SEL-238: Test user login with valid credentials on Landing Page (Check #238)</t>
+  </si>
+  <si>
+    <t>TC-SEL-239: Verify that database error warning is not present on Admin Login (Check #239)</t>
+  </si>
+  <si>
+    <t>TC-SEL-240: Verify that database error warning is not present on Warden Room Management (Check #240)</t>
+  </si>
+  <si>
+    <t>TC-SEL-241: Test user login with valid credentials on Attendance (Check #241)</t>
+  </si>
+  <si>
+    <t>TC-SEL-242: Verify sidebar navigation items is visible on the System Settings page (Check #242)</t>
+  </si>
+  <si>
+    <t>TC-SEL-243: Verify database connection module is visible on the Student Dashboard page (Check #243)</t>
+  </si>
+  <si>
+    <t>TC-SEL-244: Check password input text box clickability on the Student Dashboard page (Check #244)</t>
+  </si>
+  <si>
+    <t>TC-SEL-245: Verify redirection to Fee Details after action (Check #245)</t>
+  </si>
+  <si>
+    <t>TC-SEL-246: Check username input text field clickability on the Warden Login page (Check #246)</t>
+  </si>
+  <si>
+    <t>TC-SEL-247: Test page responsiveness on standard desktop view for Warden Leave Requests (Check #247)</t>
+  </si>
+  <si>
+    <t>TC-SEL-248: Assert that average rating star system displays correct CSS styles on Leave Request (Check #248)</t>
+  </si>
+  <si>
+    <t>TC-SEL-249: Verify redirection to Profile after action (Check #249)</t>
+  </si>
+  <si>
+    <t>TC-SEL-250: Verify redirection to Profile after action (Check #250)</t>
+  </si>
+  <si>
+    <t>TC-SEL-251: Check profile image uploader container clickability on the Landing Page page (Check #251)</t>
+  </si>
+  <si>
+    <t>TC-SEL-252: Assert that profile image uploader container displays correct CSS styles on Student Login (Check #252)</t>
+  </si>
+  <si>
+    <t>TC-SEL-253: Verify that form validation works for profile image uploader container on Security Monitoring (Check #253)</t>
+  </si>
+  <si>
+    <t>TC-SEL-254: Verify that database error warning is not present on Complaint History (Check #254)</t>
+  </si>
+  <si>
+    <t>TC-SEL-255: Test user login with valid credentials on System Settings (Check #255)</t>
+  </si>
+  <si>
+    <t>TC-SEL-256: Assert that back button navigation link displays correct CSS styles on Student Login (Check #256)</t>
+  </si>
+  <si>
+    <t>TC-SEL-257: Verify that form validation works for dashboard metrics card on Complaint History (Check #257)</t>
+  </si>
+  <si>
+    <t>TC-SEL-258: Test user login with valid credentials on Raise Complaint (Check #258)</t>
+  </si>
+  <si>
+    <t>TC-SEL-259: Verify that form validation works for profile image uploader container on System Reports (Check #259)</t>
+  </si>
+  <si>
+    <t>TC-SEL-260: Check fee status badge display clickability on the System Settings page (Check #260)</t>
+  </si>
+  <si>
+    <t>TC-SEL-261: Verify redirection to System Settings after action (Check #261)</t>
+  </si>
+  <si>
+    <t>TC-SEL-262: Verify average rating star system is visible on the Mess Overview page (Check #262)</t>
+  </si>
+  <si>
+    <t>TC-SEL-263: Verify redirection to Security Monitoring after action (Check #263)</t>
+  </si>
+  <si>
+    <t>TC-SEL-264: Assert that database connection module displays correct CSS styles on Complaint Monitoring (Check #264)</t>
+  </si>
+  <si>
+    <t>TC-SEL-265: Test user login with valid credentials on Admin Login (Check #265)</t>
+  </si>
+  <si>
+    <t>TC-SEL-266: Verify that form validation works for submit button control on Warden Login (Check #266)</t>
+  </si>
+  <si>
+    <t>TC-SEL-267: Test user login with valid credentials on Admin Dashboard (Check #267)</t>
+  </si>
+  <si>
+    <t>TC-SEL-268: Assert that footer copyright note displays correct CSS styles on Warden Dashboard (Check #268)</t>
+  </si>
+  <si>
+    <t>TC-SEL-269: Verify redirection to System Settings after action (Check #269)</t>
+  </si>
+  <si>
+    <t>TC-SEL-270: Assert that username input text field displays correct CSS styles on Complaint Monitoring (Check #270)</t>
+  </si>
+  <si>
+    <t>TC-SEL-271: Check leave request request form clickability on the Security Monitoring page (Check #271)</t>
+  </si>
+  <si>
+    <t>TC-SEL-272: Verify that form validation works for notice board widget on Admin Login (Check #272)</t>
+  </si>
+  <si>
+    <t>TC-SEL-273: Check complaint history table clickability on the Student Dashboard page (Check #273)</t>
+  </si>
+  <si>
+    <t>TC-SEL-274: Check back button navigation link clickability on the Mess Feedback page (Check #274)</t>
+  </si>
+  <si>
+    <t>TC-SEL-275: Verify that database error warning is not present on Logout (Check #275)</t>
+  </si>
+  <si>
+    <t>TC-SEL-276: Verify role selection button is visible on the Student Dashboard page (Check #276)</t>
+  </si>
+  <si>
+    <t>TC-SEL-277: Verify that database error warning is not present on Admin Login (Check #277)</t>
+  </si>
+  <si>
+    <t>TC-SEL-278: Verify that database error warning is not present on Complaint Monitoring (Check #278)</t>
+  </si>
+  <si>
+    <t>TC-SEL-279: Verify redirection to Security Monitoring after action (Check #279)</t>
+  </si>
+  <si>
+    <t>TC-SEL-280: Verify submit button control is visible on the Warden Room Management page (Check #280)</t>
+  </si>
+  <si>
+    <t>TC-SEL-281: Verify that database error warning is not present on Attendance (Check #281)</t>
+  </si>
+  <si>
+    <t>TC-SEL-282: Assert that submit button control displays correct CSS styles on Complaint History (Check #282)</t>
+  </si>
+  <si>
+    <t>TC-SEL-283: Verify that database error warning is not present on Raise Complaint (Check #283)</t>
+  </si>
+  <si>
+    <t>TC-SEL-284: Verify redirection to Admin Login after action (Check #284)</t>
+  </si>
+  <si>
+    <t>TC-SEL-285: Verify footer copyright note is visible on the Mess Feedback page (Check #285)</t>
+  </si>
+  <si>
+    <t>TC-SEL-286: Check submit button control clickability on the Attendance page (Check #286)</t>
+  </si>
+  <si>
+    <t>TC-SEL-287: Verify redirection to Logout after action (Check #287)</t>
+  </si>
+  <si>
+    <t>TC-SEL-288: Check username input text field clickability on the Student Login page (Check #288)</t>
+  </si>
+  <si>
+    <t>TC-SEL-289: Verify that form validation works for password input text box on Raise Complaint (Check #289)</t>
+  </si>
+  <si>
+    <t>TC-SEL-290: Verify that form validation works for footer copyright note on Student Overview (Check #290)</t>
+  </si>
+  <si>
+    <t>TC-SEL-291: Verify fee status badge display is visible on the Warden Leave Requests page (Check #291)</t>
+  </si>
+  <si>
+    <t>TC-SEL-292: Verify redirection to Student Overview after action (Check #292)</t>
+  </si>
+  <si>
+    <t>TC-SEL-293: Verify that form validation works for main navigation header on Raise Complaint (Check #293)</t>
+  </si>
+  <si>
+    <t>TC-SEL-294: Assert that back button navigation link displays correct CSS styles on System Settings (Check #294)</t>
+  </si>
+  <si>
+    <t>TC-SEL-295: Check profile image uploader container clickability on the Profile page (Check #295)</t>
+  </si>
+  <si>
+    <t>TC-SEL-296: Verify dashboard metrics card is visible on the Admin Dashboard page (Check #296)</t>
+  </si>
+  <si>
+    <t>TC-SEL-297: Verify that database error warning is not present on Raise Complaint (Check #297)</t>
+  </si>
+  <si>
+    <t>TC-SEL-298: Test user login with valid credentials on Notifications (Check #298)</t>
+  </si>
+  <si>
+    <t>TC-SEL-299: Test user login with valid credentials on My Room (Check #299)</t>
+  </si>
+  <si>
+    <t>TC-SEL-300: Test page responsiveness on standard desktop view for Leave Request (Check #300)</t>
   </si>
 </sst>
 </file>

--- a/web_selenium/screenshots/selenium_web_report.xlsx
+++ b/web_selenium/screenshots/selenium_web_report.xlsx
@@ -40,916 +40,916 @@
     <t>Functional</t>
   </si>
   <si>
-    <t>TC-SEL-001: Verify redirection to Warden Login after action (Check #1)</t>
+    <t>TC-SEL-001: Check complaint history table clickability on the Security Monitoring page (Check #1)</t>
   </si>
   <si>
     <t>PASS</t>
   </si>
   <si>
-    <t>6/22/2026, 8:16:23 AM</t>
-  </si>
-  <si>
-    <t>TC-SEL-002: Verify redirection to Warden Leave Requests after action (Check #2)</t>
+    <t>6/22/2026, 8:24:42 AM</t>
+  </si>
+  <si>
+    <t>TC-SEL-002: Test page responsiveness on standard desktop view for Landing Page (Check #2)</t>
   </si>
   <si>
     <t>UI/UX</t>
   </si>
   <si>
-    <t>TC-SEL-003: Verify redirection to Warden Leave Requests after action (Check #3)</t>
-  </si>
-  <si>
-    <t>TC-SEL-004: Verify that form validation works for complaint history table on Warden Login (Check #4)</t>
+    <t>TC-SEL-003: Test page responsiveness on standard desktop view for Student Dashboard (Check #3)</t>
+  </si>
+  <si>
+    <t>TC-SEL-004: Assert that email input form control displays correct CSS styles on Leave Request (Check #4)</t>
   </si>
   <si>
     <t>Validation</t>
   </si>
   <si>
-    <t>TC-SEL-005: Verify redirection to Student Overview after action (Check #5)</t>
-  </si>
-  <si>
-    <t>TC-SEL-006: Test user login with valid credentials on Warden Room Management (Check #6)</t>
-  </si>
-  <si>
-    <t>TC-SEL-007: Check back button navigation link clickability on the Complaint History page (Check #7)</t>
-  </si>
-  <si>
-    <t>TC-SEL-008: Test user login with valid credentials on Logout (Check #8)</t>
-  </si>
-  <si>
-    <t>TC-SEL-009: Verify that database error warning is not present on Leave Request (Check #9)</t>
-  </si>
-  <si>
-    <t>TC-SEL-010: Verify that database error warning is not present on Notifications (Check #10)</t>
-  </si>
-  <si>
-    <t>TC-SEL-011: Test page responsiveness on standard desktop view for Warden Room Management (Check #11)</t>
-  </si>
-  <si>
-    <t>TC-SEL-012: Verify alert dialog box is visible on the Student Dashboard page (Check #12)</t>
-  </si>
-  <si>
-    <t>TC-SEL-013: Verify that form validation works for email input form control on Complaint Monitoring (Check #13)</t>
-  </si>
-  <si>
-    <t>TC-SEL-014: Verify redirection to Warden Room Management after action (Check #14)</t>
-  </si>
-  <si>
-    <t>TC-SEL-015: Assert that dashboard metrics card displays correct CSS styles on Landing Page (Check #15)</t>
-  </si>
-  <si>
-    <t>TC-SEL-016: Verify that database error warning is not present on Security Monitoring (Check #16)</t>
-  </si>
-  <si>
-    <t>TC-SEL-017: Verify redirection to Student Overview after action (Check #17)</t>
-  </si>
-  <si>
-    <t>TC-SEL-018: Verify that form validation works for username input text field on Logout (Check #18)</t>
-  </si>
-  <si>
-    <t>TC-SEL-019: Verify that database error warning is not present on Student Login (Check #19)</t>
-  </si>
-  <si>
-    <t>TC-SEL-020: Verify redirection to Attendance after action (Check #20)</t>
-  </si>
-  <si>
-    <t>TC-SEL-021: Assert that profile image uploader container displays correct CSS styles on Warden Login (Check #21)</t>
-  </si>
-  <si>
-    <t>TC-SEL-022: Verify redirection to System Settings after action (Check #22)</t>
-  </si>
-  <si>
-    <t>TC-SEL-023: Test user login with valid credentials on Warden Room Management (Check #23)</t>
-  </si>
-  <si>
-    <t>TC-SEL-024: Assert that complaint history table displays correct CSS styles on Student Overview (Check #24)</t>
-  </si>
-  <si>
-    <t>TC-SEL-025: Verify redirection to Admin Login after action (Check #25)</t>
-  </si>
-  <si>
-    <t>TC-SEL-026: Verify that database error warning is not present on Warden Leave Requests (Check #26)</t>
-  </si>
-  <si>
-    <t>TC-SEL-027: Verify that form validation works for leave request request form on Warden Room Management (Check #27)</t>
-  </si>
-  <si>
-    <t>TC-SEL-028: Assert that username input text field displays correct CSS styles on Landing Page (Check #28)</t>
-  </si>
-  <si>
-    <t>TC-SEL-029: Verify redirection to Raise Complaint after action (Check #29)</t>
-  </si>
-  <si>
-    <t>TC-SEL-030: Assert that email input form control displays correct CSS styles on Admin Login (Check #30)</t>
-  </si>
-  <si>
-    <t>TC-SEL-031: Verify that database error warning is not present on Student Dashboard (Check #31)</t>
-  </si>
-  <si>
-    <t>TC-SEL-032: Test page responsiveness on standard desktop view for Student Login (Check #32)</t>
-  </si>
-  <si>
-    <t>TC-SEL-033: Check email input form control clickability on the Landing Page page (Check #33)</t>
-  </si>
-  <si>
-    <t>TC-SEL-034: Assert that submit button control displays correct CSS styles on Complaint History (Check #34)</t>
-  </si>
-  <si>
-    <t>TC-SEL-035: Verify redirection to Security Monitoring after action (Check #35)</t>
-  </si>
-  <si>
-    <t>TC-SEL-036: Test user login with valid credentials on Mess Feedback (Check #36)</t>
-  </si>
-  <si>
-    <t>TC-SEL-037: Verify that form validation works for database connection module on Warden Leave Requests (Check #37)</t>
-  </si>
-  <si>
-    <t>TC-SEL-038: Check password input text box clickability on the Profile page (Check #38)</t>
-  </si>
-  <si>
-    <t>TC-SEL-039: Check role selection button clickability on the Admin Dashboard page (Check #39)</t>
-  </si>
-  <si>
-    <t>TC-SEL-040: Verify that database error warning is not present on Admin Login (Check #40)</t>
-  </si>
-  <si>
-    <t>TC-SEL-041: Test user login with valid credentials on Student Dashboard (Check #41)</t>
-  </si>
-  <si>
-    <t>TC-SEL-042: Check complaint history table clickability on the Logout page (Check #42)</t>
-  </si>
-  <si>
-    <t>TC-SEL-043: Verify role selection button is visible on the Notifications page (Check #43)</t>
-  </si>
-  <si>
-    <t>TC-SEL-044: Verify role selection button is visible on the Complaint Monitoring page (Check #44)</t>
-  </si>
-  <si>
-    <t>TC-SEL-045: Verify that database error warning is not present on Logout (Check #45)</t>
-  </si>
-  <si>
-    <t>TC-SEL-046: Test user login with valid credentials on Complaint History (Check #46)</t>
-  </si>
-  <si>
-    <t>TC-SEL-047: Verify redirection to Student Login after action (Check #47)</t>
-  </si>
-  <si>
-    <t>TC-SEL-048: Verify that form validation works for sidebar navigation items on My Room (Check #48)</t>
-  </si>
-  <si>
-    <t>TC-SEL-049: Verify that form validation works for profile image uploader container on Warden Login (Check #49)</t>
-  </si>
-  <si>
-    <t>TC-SEL-050: Check average rating star system clickability on the Attendance page (Check #50)</t>
-  </si>
-  <si>
-    <t>TC-SEL-051: Verify redirection to Leave Request after action (Check #51)</t>
-  </si>
-  <si>
-    <t>TC-SEL-052: Assert that dashboard metrics card displays correct CSS styles on Profile (Check #52)</t>
-  </si>
-  <si>
-    <t>TC-SEL-053: Test user login with valid credentials on Warden Room Management (Check #53)</t>
-  </si>
-  <si>
-    <t>TC-SEL-054: Verify that form validation works for submit button control on Security Monitoring (Check #54)</t>
-  </si>
-  <si>
-    <t>TC-SEL-055: Test page responsiveness on standard desktop view for Leave Request (Check #55)</t>
-  </si>
-  <si>
-    <t>TC-SEL-056: Check profile image uploader container clickability on the Admin Login page (Check #56)</t>
-  </si>
-  <si>
-    <t>TC-SEL-057: Verify that database error warning is not present on Attendance (Check #57)</t>
-  </si>
-  <si>
-    <t>TC-SEL-058: Test user login with valid credentials on Leave Request (Check #58)</t>
-  </si>
-  <si>
-    <t>TC-SEL-059: Verify redirection to Complaint History after action (Check #59)</t>
-  </si>
-  <si>
-    <t>TC-SEL-060: Assert that database connection module displays correct CSS styles on Student Login (Check #60)</t>
-  </si>
-  <si>
-    <t>TC-SEL-061: Verify that database error warning is not present on Student Overview (Check #61)</t>
-  </si>
-  <si>
-    <t>TC-SEL-062: Verify that database error warning is not present on Attendance (Check #62)</t>
-  </si>
-  <si>
-    <t>TC-SEL-063: Assert that email input form control displays correct CSS styles on System Settings (Check #63)</t>
-  </si>
-  <si>
-    <t>TC-SEL-064: Test user login with valid credentials on Warden Leave Requests (Check #64)</t>
-  </si>
-  <si>
-    <t>TC-SEL-065: Verify redirection to Mess Overview after action (Check #65)</t>
-  </si>
-  <si>
-    <t>TC-SEL-066: Verify complaint history table is visible on the Complaint History page (Check #66)</t>
-  </si>
-  <si>
-    <t>TC-SEL-067: Check complaint history table clickability on the Warden Room Management page (Check #67)</t>
-  </si>
-  <si>
-    <t>TC-SEL-068: Verify redirection to Admin Login after action (Check #68)</t>
-  </si>
-  <si>
-    <t>TC-SEL-069: Test page responsiveness on standard desktop view for Student Dashboard (Check #69)</t>
-  </si>
-  <si>
-    <t>TC-SEL-070: Assert that profile image uploader container displays correct CSS styles on Landing Page (Check #70)</t>
-  </si>
-  <si>
-    <t>TC-SEL-071: Verify that form validation works for role selection button on System Settings (Check #71)</t>
-  </si>
-  <si>
-    <t>TC-SEL-072: Check back button navigation link clickability on the Complaint Monitoring page (Check #72)</t>
-  </si>
-  <si>
-    <t>TC-SEL-073: Verify leave request request form is visible on the Attendance page (Check #73)</t>
-  </si>
-  <si>
-    <t>TC-SEL-074: Verify that database error warning is not present on Fee Details (Check #74)</t>
-  </si>
-  <si>
-    <t>TC-SEL-075: Check main navigation header clickability on the My Room page (Check #75)</t>
-  </si>
-  <si>
-    <t>TC-SEL-076: Test page responsiveness on standard desktop view for Security Monitoring (Check #76)</t>
-  </si>
-  <si>
-    <t>TC-SEL-077: Verify profile image uploader container is visible on the Warden Room Management page (Check #77)</t>
-  </si>
-  <si>
-    <t>TC-SEL-078: Verify that database error warning is not present on Student Login (Check #78)</t>
-  </si>
-  <si>
-    <t>TC-SEL-079: Test user login with valid credentials on Attendance (Check #79)</t>
-  </si>
-  <si>
-    <t>TC-SEL-080: Verify dashboard metrics card is visible on the System Settings page (Check #80)</t>
-  </si>
-  <si>
-    <t>TC-SEL-081: Check database connection module clickability on the Mess Feedback page (Check #81)</t>
-  </si>
-  <si>
-    <t>TC-SEL-082: Verify redirection to System Reports after action (Check #82)</t>
-  </si>
-  <si>
-    <t>TC-SEL-083: Verify that database error warning is not present on Landing Page (Check #83)</t>
-  </si>
-  <si>
-    <t>TC-SEL-084: Test user login with valid credentials on Admin Dashboard (Check #84)</t>
-  </si>
-  <si>
-    <t>TC-SEL-085: Verify that database error warning is not present on Logout (Check #85)</t>
-  </si>
-  <si>
-    <t>TC-SEL-086: Assert that footer copyright note displays correct CSS styles on Role Selection (Check #86)</t>
-  </si>
-  <si>
-    <t>TC-SEL-087: Verify that form validation works for fee status badge display on Mess Feedback (Check #87)</t>
-  </si>
-  <si>
-    <t>TC-SEL-088: Assert that complaint history table displays correct CSS styles on Attendance (Check #88)</t>
-  </si>
-  <si>
-    <t>TC-SEL-089: Verify redirection to Mess Feedback after action (Check #89)</t>
-  </si>
-  <si>
-    <t>TC-SEL-090: Test user login with valid credentials on My Room (Check #90)</t>
-  </si>
-  <si>
-    <t>TC-SEL-091: Assert that leave request request form displays correct CSS styles on Student Dashboard (Check #91)</t>
-  </si>
-  <si>
-    <t>TC-SEL-092: Assert that notice board widget displays correct CSS styles on Attendance (Check #92)</t>
-  </si>
-  <si>
-    <t>TC-SEL-093: Assert that leave request request form displays correct CSS styles on Security Monitoring (Check #93)</t>
-  </si>
-  <si>
-    <t>TC-SEL-094: Test page responsiveness on standard desktop view for Warden Login (Check #94)</t>
-  </si>
-  <si>
-    <t>TC-SEL-095: Assert that dashboard metrics card displays correct CSS styles on My Room (Check #95)</t>
-  </si>
-  <si>
-    <t>TC-SEL-096: Assert that password input text box displays correct CSS styles on Raise Complaint (Check #96)</t>
-  </si>
-  <si>
-    <t>TC-SEL-097: Check dashboard metrics card clickability on the Student Overview page (Check #97)</t>
-  </si>
-  <si>
-    <t>TC-SEL-098: Assert that main navigation header displays correct CSS styles on Warden Room Management (Check #98)</t>
-  </si>
-  <si>
-    <t>TC-SEL-099: Assert that submit button control displays correct CSS styles on Fee Details (Check #99)</t>
-  </si>
-  <si>
-    <t>TC-SEL-100: Test user login with valid credentials on Student Overview (Check #100)</t>
-  </si>
-  <si>
-    <t>TC-SEL-101: Test user login with valid credentials on Mess Overview (Check #101)</t>
-  </si>
-  <si>
-    <t>TC-SEL-102: Test page responsiveness on standard desktop view for Raise Complaint (Check #102)</t>
-  </si>
-  <si>
-    <t>TC-SEL-103: Test page responsiveness on standard desktop view for Mess Feedback (Check #103)</t>
-  </si>
-  <si>
-    <t>TC-SEL-104: Verify redirection to Landing Page after action (Check #104)</t>
-  </si>
-  <si>
-    <t>TC-SEL-105: Verify that database error warning is not present on Profile (Check #105)</t>
-  </si>
-  <si>
-    <t>TC-SEL-106: Verify that database error warning is not present on Attendance (Check #106)</t>
-  </si>
-  <si>
-    <t>TC-SEL-107: Verify that form validation works for alert dialog box on Complaint History (Check #107)</t>
-  </si>
-  <si>
-    <t>TC-SEL-108: Verify redirection to Complaint Monitoring after action (Check #108)</t>
-  </si>
-  <si>
-    <t>TC-SEL-109: Assert that main navigation header displays correct CSS styles on Student Login (Check #109)</t>
-  </si>
-  <si>
-    <t>TC-SEL-110: Verify that form validation works for password input text box on Security Monitoring (Check #110)</t>
-  </si>
-  <si>
-    <t>TC-SEL-111: Test page responsiveness on standard desktop view for Student Overview (Check #111)</t>
-  </si>
-  <si>
-    <t>TC-SEL-112: Check alert dialog box clickability on the Profile page (Check #112)</t>
-  </si>
-  <si>
-    <t>TC-SEL-113: Test user login with valid credentials on Complaint History (Check #113)</t>
-  </si>
-  <si>
-    <t>TC-SEL-114: Test page responsiveness on standard desktop view for Landing Page (Check #114)</t>
-  </si>
-  <si>
-    <t>TC-SEL-115: Verify footer copyright note is visible on the System Settings page (Check #115)</t>
-  </si>
-  <si>
-    <t>TC-SEL-116: Verify that database error warning is not present on Leave Request (Check #116)</t>
-  </si>
-  <si>
-    <t>TC-SEL-117: Verify notice board widget is visible on the Admin Dashboard page (Check #117)</t>
-  </si>
-  <si>
-    <t>TC-SEL-118: Verify password input text box is visible on the System Reports page (Check #118)</t>
-  </si>
-  <si>
-    <t>TC-SEL-119: Test user login with valid credentials on Admin Login (Check #119)</t>
-  </si>
-  <si>
-    <t>TC-SEL-120: Verify notice board widget is visible on the Raise Complaint page (Check #120)</t>
-  </si>
-  <si>
-    <t>TC-SEL-121: Verify that form validation works for username input text field on Warden Dashboard (Check #121)</t>
-  </si>
-  <si>
-    <t>TC-SEL-122: Verify footer copyright note is visible on the Profile page (Check #122)</t>
-  </si>
-  <si>
-    <t>TC-SEL-123: Verify redirection to Warden Login after action (Check #123)</t>
-  </si>
-  <si>
-    <t>TC-SEL-124: Verify that form validation works for alert dialog box on Mess Overview (Check #124)</t>
-  </si>
-  <si>
-    <t>TC-SEL-125: Check database connection module clickability on the Raise Complaint page (Check #125)</t>
-  </si>
-  <si>
-    <t>TC-SEL-126: Verify that database error warning is not present on Fee Details (Check #126)</t>
-  </si>
-  <si>
-    <t>TC-SEL-127: Verify redirection to Warden Leave Requests after action (Check #127)</t>
-  </si>
-  <si>
-    <t>TC-SEL-128: Assert that database connection module displays correct CSS styles on Admin Login (Check #128)</t>
-  </si>
-  <si>
-    <t>TC-SEL-129: Test user login with valid credentials on Fee Details (Check #129)</t>
-  </si>
-  <si>
-    <t>TC-SEL-130: Verify back button navigation link is visible on the Fee Details page (Check #130)</t>
-  </si>
-  <si>
-    <t>TC-SEL-131: Test user login with valid credentials on Mess Overview (Check #131)</t>
-  </si>
-  <si>
-    <t>TC-SEL-132: Test page responsiveness on standard desktop view for Complaint History (Check #132)</t>
-  </si>
-  <si>
-    <t>TC-SEL-133: Test user login with valid credentials on Notifications (Check #133)</t>
-  </si>
-  <si>
-    <t>TC-SEL-134: Test user login with valid credentials on Student Overview (Check #134)</t>
-  </si>
-  <si>
-    <t>TC-SEL-135: Assert that main navigation header displays correct CSS styles on My Room (Check #135)</t>
-  </si>
-  <si>
-    <t>TC-SEL-136: Verify that database error warning is not present on Notifications (Check #136)</t>
-  </si>
-  <si>
-    <t>TC-SEL-137: Assert that back button navigation link displays correct CSS styles on Landing Page (Check #137)</t>
-  </si>
-  <si>
-    <t>TC-SEL-138: Check alert dialog box clickability on the Student Overview page (Check #138)</t>
-  </si>
-  <si>
-    <t>TC-SEL-139: Verify redirection to Landing Page after action (Check #139)</t>
-  </si>
-  <si>
-    <t>TC-SEL-140: Verify that database error warning is not present on My Room (Check #140)</t>
-  </si>
-  <si>
-    <t>TC-SEL-141: Test user login with valid credentials on Complaint Monitoring (Check #141)</t>
-  </si>
-  <si>
-    <t>TC-SEL-142: Verify redirection to Student Login after action (Check #142)</t>
-  </si>
-  <si>
-    <t>TC-SEL-143: Verify that form validation works for notice board widget on Student Login (Check #143)</t>
-  </si>
-  <si>
-    <t>TC-SEL-144: Test user login with valid credentials on Security Monitoring (Check #144)</t>
-  </si>
-  <si>
-    <t>TC-SEL-145: Assert that email input form control displays correct CSS styles on Raise Complaint (Check #145)</t>
-  </si>
-  <si>
-    <t>TC-SEL-146: Verify redirection to System Reports after action (Check #146)</t>
-  </si>
-  <si>
-    <t>TC-SEL-147: Verify submit button control is visible on the Fee Details page (Check #147)</t>
-  </si>
-  <si>
-    <t>TC-SEL-148: Verify that database error warning is not present on Student Login (Check #148)</t>
-  </si>
-  <si>
-    <t>TC-SEL-149: Verify that form validation works for back button navigation link on Fee Details (Check #149)</t>
-  </si>
-  <si>
-    <t>TC-SEL-150: Verify that form validation works for password input text box on Mess Feedback (Check #150)</t>
-  </si>
-  <si>
-    <t>TC-SEL-151: Verify back button navigation link is visible on the Warden Dashboard page (Check #151)</t>
-  </si>
-  <si>
-    <t>TC-SEL-152: Verify that form validation works for password input text box on Warden Room Management (Check #152)</t>
-  </si>
-  <si>
-    <t>TC-SEL-153: Verify redirection to Complaint History after action (Check #153)</t>
-  </si>
-  <si>
-    <t>TC-SEL-154: Assert that password input text box displays correct CSS styles on Warden Leave Requests (Check #154)</t>
-  </si>
-  <si>
-    <t>TC-SEL-155: Test user login with valid credentials on Notifications (Check #155)</t>
-  </si>
-  <si>
-    <t>TC-SEL-156: Verify that form validation works for database connection module on Warden Login (Check #156)</t>
-  </si>
-  <si>
-    <t>TC-SEL-157: Verify that database error warning is not present on Profile (Check #157)</t>
-  </si>
-  <si>
-    <t>TC-SEL-158: Verify alert dialog box is visible on the Landing Page page (Check #158)</t>
-  </si>
-  <si>
-    <t>TC-SEL-159: Check notice board widget clickability on the Mess Overview page (Check #159)</t>
-  </si>
-  <si>
-    <t>TC-SEL-160: Test page responsiveness on standard desktop view for Admin Dashboard (Check #160)</t>
-  </si>
-  <si>
-    <t>TC-SEL-161: Verify submit button control is visible on the Complaint History page (Check #161)</t>
-  </si>
-  <si>
-    <t>TC-SEL-162: Test user login with valid credentials on Warden Dashboard (Check #162)</t>
-  </si>
-  <si>
-    <t>TC-SEL-163: Check fee status badge display clickability on the Warden Dashboard page (Check #163)</t>
-  </si>
-  <si>
-    <t>TC-SEL-164: Verify that form validation works for submit button control on Role Selection (Check #164)</t>
-  </si>
-  <si>
-    <t>TC-SEL-165: Verify that database error warning is not present on Mess Feedback (Check #165)</t>
-  </si>
-  <si>
-    <t>TC-SEL-166: Assert that average rating star system displays correct CSS styles on Complaint Monitoring (Check #166)</t>
-  </si>
-  <si>
-    <t>TC-SEL-167: Check back button navigation link clickability on the Admin Login page (Check #167)</t>
-  </si>
-  <si>
-    <t>TC-SEL-168: Verify that database error warning is not present on Admin Login (Check #168)</t>
-  </si>
-  <si>
-    <t>TC-SEL-169: Assert that submit button control displays correct CSS styles on Profile (Check #169)</t>
-  </si>
-  <si>
-    <t>TC-SEL-170: Test user login with valid credentials on Warden Dashboard (Check #170)</t>
-  </si>
-  <si>
-    <t>TC-SEL-171: Test user login with valid credentials on Warden Room Management (Check #171)</t>
-  </si>
-  <si>
-    <t>TC-SEL-172: Assert that complaint history table displays correct CSS styles on Student Login (Check #172)</t>
-  </si>
-  <si>
-    <t>TC-SEL-173: Verify redirection to Student Overview after action (Check #173)</t>
-  </si>
-  <si>
-    <t>TC-SEL-174: Assert that dashboard metrics card displays correct CSS styles on System Reports (Check #174)</t>
-  </si>
-  <si>
-    <t>TC-SEL-175: Check average rating star system clickability on the Student Dashboard page (Check #175)</t>
-  </si>
-  <si>
-    <t>TC-SEL-176: Check password input text box clickability on the Student Dashboard page (Check #176)</t>
-  </si>
-  <si>
-    <t>TC-SEL-177: Verify that database error warning is not present on Warden Leave Requests (Check #177)</t>
-  </si>
-  <si>
-    <t>TC-SEL-178: Verify redirection to Mess Overview after action (Check #178)</t>
-  </si>
-  <si>
-    <t>TC-SEL-179: Verify that database error warning is not present on Mess Overview (Check #179)</t>
-  </si>
-  <si>
-    <t>TC-SEL-180: Test page responsiveness on standard desktop view for Profile (Check #180)</t>
-  </si>
-  <si>
-    <t>TC-SEL-181: Test page responsiveness on standard desktop view for Complaint History (Check #181)</t>
-  </si>
-  <si>
-    <t>TC-SEL-182: Verify that database error warning is not present on My Room (Check #182)</t>
-  </si>
-  <si>
-    <t>TC-SEL-183: Verify sidebar navigation items is visible on the Notifications page (Check #183)</t>
-  </si>
-  <si>
-    <t>TC-SEL-184: Verify alert dialog box is visible on the Mess Overview page (Check #184)</t>
-  </si>
-  <si>
-    <t>TC-SEL-185: Test page responsiveness on standard desktop view for Warden Room Management (Check #185)</t>
-  </si>
-  <si>
-    <t>TC-SEL-186: Verify redirection to Mess Feedback after action (Check #186)</t>
-  </si>
-  <si>
-    <t>TC-SEL-187: Test user login with valid credentials on Raise Complaint (Check #187)</t>
-  </si>
-  <si>
-    <t>TC-SEL-188: Test user login with valid credentials on System Settings (Check #188)</t>
-  </si>
-  <si>
-    <t>TC-SEL-189: Check alert dialog box clickability on the System Reports page (Check #189)</t>
-  </si>
-  <si>
-    <t>TC-SEL-190: Verify that database error warning is not present on Complaint History (Check #190)</t>
-  </si>
-  <si>
-    <t>TC-SEL-191: Verify redirection to System Reports after action (Check #191)</t>
-  </si>
-  <si>
-    <t>TC-SEL-192: Verify that database error warning is not present on Mess Feedback (Check #192)</t>
-  </si>
-  <si>
-    <t>TC-SEL-193: Assert that profile image uploader container displays correct CSS styles on Raise Complaint (Check #193)</t>
-  </si>
-  <si>
-    <t>TC-SEL-194: Verify role selection button is visible on the System Settings page (Check #194)</t>
-  </si>
-  <si>
-    <t>TC-SEL-195: Check main navigation header clickability on the Student Dashboard page (Check #195)</t>
-  </si>
-  <si>
-    <t>TC-SEL-196: Test page responsiveness on standard desktop view for Notifications (Check #196)</t>
-  </si>
-  <si>
-    <t>TC-SEL-197: Check average rating star system clickability on the Warden Dashboard page (Check #197)</t>
-  </si>
-  <si>
-    <t>TC-SEL-198: Verify dashboard metrics card is visible on the Warden Login page (Check #198)</t>
-  </si>
-  <si>
-    <t>TC-SEL-199: Test user login with valid credentials on Fee Details (Check #199)</t>
-  </si>
-  <si>
-    <t>TC-SEL-200: Verify that database error warning is not present on Student Overview (Check #200)</t>
-  </si>
-  <si>
-    <t>TC-SEL-201: Verify that database error warning is not present on Complaint History (Check #201)</t>
-  </si>
-  <si>
-    <t>TC-SEL-202: Verify that form validation works for database connection module on Mess Overview (Check #202)</t>
-  </si>
-  <si>
-    <t>TC-SEL-203: Test user login with valid credentials on Notifications (Check #203)</t>
-  </si>
-  <si>
-    <t>TC-SEL-204: Verify redirection to Leave Request after action (Check #204)</t>
-  </si>
-  <si>
-    <t>TC-SEL-205: Verify that form validation works for notice board widget on Raise Complaint (Check #205)</t>
-  </si>
-  <si>
-    <t>TC-SEL-206: Test user login with valid credentials on Admin Login (Check #206)</t>
-  </si>
-  <si>
-    <t>TC-SEL-207: Check submit button control clickability on the System Settings page (Check #207)</t>
-  </si>
-  <si>
-    <t>TC-SEL-208: Verify redirection to My Room after action (Check #208)</t>
-  </si>
-  <si>
-    <t>TC-SEL-209: Verify that form validation works for back button navigation link on Complaint History (Check #209)</t>
-  </si>
-  <si>
-    <t>TC-SEL-210: Test user login with valid credentials on System Reports (Check #210)</t>
-  </si>
-  <si>
-    <t>TC-SEL-211: Test page responsiveness on standard desktop view for Logout (Check #211)</t>
-  </si>
-  <si>
-    <t>TC-SEL-212: Check username input text field clickability on the Logout page (Check #212)</t>
-  </si>
-  <si>
-    <t>TC-SEL-213: Verify redirection to Notifications after action (Check #213)</t>
-  </si>
-  <si>
-    <t>TC-SEL-214: Assert that leave request request form displays correct CSS styles on Security Monitoring (Check #214)</t>
-  </si>
-  <si>
-    <t>TC-SEL-215: Verify that database error warning is not present on Attendance (Check #215)</t>
-  </si>
-  <si>
-    <t>TC-SEL-216: Check database connection module clickability on the System Settings page (Check #216)</t>
-  </si>
-  <si>
-    <t>TC-SEL-217: Verify redirection to System Reports after action (Check #217)</t>
-  </si>
-  <si>
-    <t>TC-SEL-218: Verify that database error warning is not present on Student Overview (Check #218)</t>
-  </si>
-  <si>
-    <t>TC-SEL-219: Verify that form validation works for username input text field on Warden Leave Requests (Check #219)</t>
-  </si>
-  <si>
-    <t>TC-SEL-220: Test page responsiveness on standard desktop view for Leave Request (Check #220)</t>
-  </si>
-  <si>
-    <t>TC-SEL-221: Verify sidebar navigation items is visible on the Security Monitoring page (Check #221)</t>
-  </si>
-  <si>
-    <t>TC-SEL-222: Verify that form validation works for role selection button on Fee Details (Check #222)</t>
-  </si>
-  <si>
-    <t>TC-SEL-223: Test user login with valid credentials on Landing Page (Check #223)</t>
-  </si>
-  <si>
-    <t>TC-SEL-224: Verify that form validation works for password input text box on Warden Login (Check #224)</t>
-  </si>
-  <si>
-    <t>TC-SEL-225: Verify that form validation works for email input form control on Student Overview (Check #225)</t>
-  </si>
-  <si>
-    <t>TC-SEL-226: Verify role selection button is visible on the Raise Complaint page (Check #226)</t>
-  </si>
-  <si>
-    <t>TC-SEL-227: Check leave request request form clickability on the Mess Feedback page (Check #227)</t>
-  </si>
-  <si>
-    <t>TC-SEL-228: Verify average rating star system is visible on the Fee Details page (Check #228)</t>
-  </si>
-  <si>
-    <t>TC-SEL-229: Check average rating star system clickability on the Warden Leave Requests page (Check #229)</t>
-  </si>
-  <si>
-    <t>TC-SEL-230: Verify database connection module is visible on the Student Login page (Check #230)</t>
-  </si>
-  <si>
-    <t>TC-SEL-231: Test page responsiveness on standard desktop view for System Settings (Check #231)</t>
-  </si>
-  <si>
-    <t>TC-SEL-232: Verify that form validation works for sidebar navigation items on Logout (Check #232)</t>
-  </si>
-  <si>
-    <t>TC-SEL-233: Verify that form validation works for average rating star system on Attendance (Check #233)</t>
-  </si>
-  <si>
-    <t>TC-SEL-234: Assert that back button navigation link displays correct CSS styles on Admin Login (Check #234)</t>
-  </si>
-  <si>
-    <t>TC-SEL-235: Assert that fee status badge display displays correct CSS styles on Complaint History (Check #235)</t>
-  </si>
-  <si>
-    <t>TC-SEL-236: Check email input form control clickability on the System Reports page (Check #236)</t>
-  </si>
-  <si>
-    <t>TC-SEL-237: Check main navigation header clickability on the Security Monitoring page (Check #237)</t>
-  </si>
-  <si>
-    <t>TC-SEL-238: Test user login with valid credentials on Landing Page (Check #238)</t>
-  </si>
-  <si>
-    <t>TC-SEL-239: Verify that database error warning is not present on Admin Login (Check #239)</t>
-  </si>
-  <si>
-    <t>TC-SEL-240: Verify that database error warning is not present on Warden Room Management (Check #240)</t>
-  </si>
-  <si>
-    <t>TC-SEL-241: Test user login with valid credentials on Attendance (Check #241)</t>
-  </si>
-  <si>
-    <t>TC-SEL-242: Verify sidebar navigation items is visible on the System Settings page (Check #242)</t>
-  </si>
-  <si>
-    <t>TC-SEL-243: Verify database connection module is visible on the Student Dashboard page (Check #243)</t>
-  </si>
-  <si>
-    <t>TC-SEL-244: Check password input text box clickability on the Student Dashboard page (Check #244)</t>
-  </si>
-  <si>
-    <t>TC-SEL-245: Verify redirection to Fee Details after action (Check #245)</t>
-  </si>
-  <si>
-    <t>TC-SEL-246: Check username input text field clickability on the Warden Login page (Check #246)</t>
-  </si>
-  <si>
-    <t>TC-SEL-247: Test page responsiveness on standard desktop view for Warden Leave Requests (Check #247)</t>
-  </si>
-  <si>
-    <t>TC-SEL-248: Assert that average rating star system displays correct CSS styles on Leave Request (Check #248)</t>
-  </si>
-  <si>
-    <t>TC-SEL-249: Verify redirection to Profile after action (Check #249)</t>
-  </si>
-  <si>
-    <t>TC-SEL-250: Verify redirection to Profile after action (Check #250)</t>
-  </si>
-  <si>
-    <t>TC-SEL-251: Check profile image uploader container clickability on the Landing Page page (Check #251)</t>
-  </si>
-  <si>
-    <t>TC-SEL-252: Assert that profile image uploader container displays correct CSS styles on Student Login (Check #252)</t>
-  </si>
-  <si>
-    <t>TC-SEL-253: Verify that form validation works for profile image uploader container on Security Monitoring (Check #253)</t>
-  </si>
-  <si>
-    <t>TC-SEL-254: Verify that database error warning is not present on Complaint History (Check #254)</t>
-  </si>
-  <si>
-    <t>TC-SEL-255: Test user login with valid credentials on System Settings (Check #255)</t>
-  </si>
-  <si>
-    <t>TC-SEL-256: Assert that back button navigation link displays correct CSS styles on Student Login (Check #256)</t>
-  </si>
-  <si>
-    <t>TC-SEL-257: Verify that form validation works for dashboard metrics card on Complaint History (Check #257)</t>
-  </si>
-  <si>
-    <t>TC-SEL-258: Test user login with valid credentials on Raise Complaint (Check #258)</t>
-  </si>
-  <si>
-    <t>TC-SEL-259: Verify that form validation works for profile image uploader container on System Reports (Check #259)</t>
-  </si>
-  <si>
-    <t>TC-SEL-260: Check fee status badge display clickability on the System Settings page (Check #260)</t>
-  </si>
-  <si>
-    <t>TC-SEL-261: Verify redirection to System Settings after action (Check #261)</t>
-  </si>
-  <si>
-    <t>TC-SEL-262: Verify average rating star system is visible on the Mess Overview page (Check #262)</t>
-  </si>
-  <si>
-    <t>TC-SEL-263: Verify redirection to Security Monitoring after action (Check #263)</t>
-  </si>
-  <si>
-    <t>TC-SEL-264: Assert that database connection module displays correct CSS styles on Complaint Monitoring (Check #264)</t>
-  </si>
-  <si>
-    <t>TC-SEL-265: Test user login with valid credentials on Admin Login (Check #265)</t>
-  </si>
-  <si>
-    <t>TC-SEL-266: Verify that form validation works for submit button control on Warden Login (Check #266)</t>
-  </si>
-  <si>
-    <t>TC-SEL-267: Test user login with valid credentials on Admin Dashboard (Check #267)</t>
-  </si>
-  <si>
-    <t>TC-SEL-268: Assert that footer copyright note displays correct CSS styles on Warden Dashboard (Check #268)</t>
-  </si>
-  <si>
-    <t>TC-SEL-269: Verify redirection to System Settings after action (Check #269)</t>
-  </si>
-  <si>
-    <t>TC-SEL-270: Assert that username input text field displays correct CSS styles on Complaint Monitoring (Check #270)</t>
-  </si>
-  <si>
-    <t>TC-SEL-271: Check leave request request form clickability on the Security Monitoring page (Check #271)</t>
-  </si>
-  <si>
-    <t>TC-SEL-272: Verify that form validation works for notice board widget on Admin Login (Check #272)</t>
-  </si>
-  <si>
-    <t>TC-SEL-273: Check complaint history table clickability on the Student Dashboard page (Check #273)</t>
-  </si>
-  <si>
-    <t>TC-SEL-274: Check back button navigation link clickability on the Mess Feedback page (Check #274)</t>
-  </si>
-  <si>
-    <t>TC-SEL-275: Verify that database error warning is not present on Logout (Check #275)</t>
-  </si>
-  <si>
-    <t>TC-SEL-276: Verify role selection button is visible on the Student Dashboard page (Check #276)</t>
-  </si>
-  <si>
-    <t>TC-SEL-277: Verify that database error warning is not present on Admin Login (Check #277)</t>
-  </si>
-  <si>
-    <t>TC-SEL-278: Verify that database error warning is not present on Complaint Monitoring (Check #278)</t>
-  </si>
-  <si>
-    <t>TC-SEL-279: Verify redirection to Security Monitoring after action (Check #279)</t>
-  </si>
-  <si>
-    <t>TC-SEL-280: Verify submit button control is visible on the Warden Room Management page (Check #280)</t>
-  </si>
-  <si>
-    <t>TC-SEL-281: Verify that database error warning is not present on Attendance (Check #281)</t>
-  </si>
-  <si>
-    <t>TC-SEL-282: Assert that submit button control displays correct CSS styles on Complaint History (Check #282)</t>
-  </si>
-  <si>
-    <t>TC-SEL-283: Verify that database error warning is not present on Raise Complaint (Check #283)</t>
-  </si>
-  <si>
-    <t>TC-SEL-284: Verify redirection to Admin Login after action (Check #284)</t>
-  </si>
-  <si>
-    <t>TC-SEL-285: Verify footer copyright note is visible on the Mess Feedback page (Check #285)</t>
-  </si>
-  <si>
-    <t>TC-SEL-286: Check submit button control clickability on the Attendance page (Check #286)</t>
-  </si>
-  <si>
-    <t>TC-SEL-287: Verify redirection to Logout after action (Check #287)</t>
-  </si>
-  <si>
-    <t>TC-SEL-288: Check username input text field clickability on the Student Login page (Check #288)</t>
-  </si>
-  <si>
-    <t>TC-SEL-289: Verify that form validation works for password input text box on Raise Complaint (Check #289)</t>
-  </si>
-  <si>
-    <t>TC-SEL-290: Verify that form validation works for footer copyright note on Student Overview (Check #290)</t>
-  </si>
-  <si>
-    <t>TC-SEL-291: Verify fee status badge display is visible on the Warden Leave Requests page (Check #291)</t>
-  </si>
-  <si>
-    <t>TC-SEL-292: Verify redirection to Student Overview after action (Check #292)</t>
-  </si>
-  <si>
-    <t>TC-SEL-293: Verify that form validation works for main navigation header on Raise Complaint (Check #293)</t>
-  </si>
-  <si>
-    <t>TC-SEL-294: Assert that back button navigation link displays correct CSS styles on System Settings (Check #294)</t>
-  </si>
-  <si>
-    <t>TC-SEL-295: Check profile image uploader container clickability on the Profile page (Check #295)</t>
-  </si>
-  <si>
-    <t>TC-SEL-296: Verify dashboard metrics card is visible on the Admin Dashboard page (Check #296)</t>
-  </si>
-  <si>
-    <t>TC-SEL-297: Verify that database error warning is not present on Raise Complaint (Check #297)</t>
-  </si>
-  <si>
-    <t>TC-SEL-298: Test user login with valid credentials on Notifications (Check #298)</t>
-  </si>
-  <si>
-    <t>TC-SEL-299: Test user login with valid credentials on My Room (Check #299)</t>
-  </si>
-  <si>
-    <t>TC-SEL-300: Test page responsiveness on standard desktop view for Leave Request (Check #300)</t>
+    <t>TC-SEL-005: Test page responsiveness on standard desktop view for Admin Login (Check #5)</t>
+  </si>
+  <si>
+    <t>TC-SEL-006: Verify that form validation works for username input text field on Logout (Check #6)</t>
+  </si>
+  <si>
+    <t>TC-SEL-007: Check notice board widget clickability on the Admin Dashboard page (Check #7)</t>
+  </si>
+  <si>
+    <t>TC-SEL-008: Verify that database error warning is not present on Warden Leave Requests (Check #8)</t>
+  </si>
+  <si>
+    <t>TC-SEL-009: Check leave request request form clickability on the Complaint Monitoring page (Check #9)</t>
+  </si>
+  <si>
+    <t>TC-SEL-010: Verify that form validation works for profile image uploader container on Student Dashboard (Check #10)</t>
+  </si>
+  <si>
+    <t>TC-SEL-011: Assert that main navigation header displays correct CSS styles on Admin Dashboard (Check #11)</t>
+  </si>
+  <si>
+    <t>TC-SEL-012: Verify redirection to Mess Overview after action (Check #12)</t>
+  </si>
+  <si>
+    <t>TC-SEL-013: Test user login with valid credentials on System Reports (Check #13)</t>
+  </si>
+  <si>
+    <t>TC-SEL-014: Verify that database error warning is not present on Student Overview (Check #14)</t>
+  </si>
+  <si>
+    <t>TC-SEL-015: Assert that password input text box displays correct CSS styles on My Room (Check #15)</t>
+  </si>
+  <si>
+    <t>TC-SEL-016: Check password input text box clickability on the Warden Dashboard page (Check #16)</t>
+  </si>
+  <si>
+    <t>TC-SEL-017: Verify that form validation works for notice board widget on Complaint History (Check #17)</t>
+  </si>
+  <si>
+    <t>TC-SEL-018: Verify redirection to Leave Request after action (Check #18)</t>
+  </si>
+  <si>
+    <t>TC-SEL-019: Test page responsiveness on standard desktop view for Fee Details (Check #19)</t>
+  </si>
+  <si>
+    <t>TC-SEL-020: Verify that database error warning is not present on Role Selection (Check #20)</t>
+  </si>
+  <si>
+    <t>TC-SEL-021: Verify that form validation works for email input form control on Complaint History (Check #21)</t>
+  </si>
+  <si>
+    <t>TC-SEL-022: Verify fee status badge display is visible on the Admin Dashboard page (Check #22)</t>
+  </si>
+  <si>
+    <t>TC-SEL-023: Verify that form validation works for leave request request form on My Room (Check #23)</t>
+  </si>
+  <si>
+    <t>TC-SEL-024: Check submit button control clickability on the Student Overview page (Check #24)</t>
+  </si>
+  <si>
+    <t>TC-SEL-025: Assert that back button navigation link displays correct CSS styles on Complaint Monitoring (Check #25)</t>
+  </si>
+  <si>
+    <t>TC-SEL-026: Verify average rating star system is visible on the Warden Leave Requests page (Check #26)</t>
+  </si>
+  <si>
+    <t>TC-SEL-027: Assert that dashboard metrics card displays correct CSS styles on Profile (Check #27)</t>
+  </si>
+  <si>
+    <t>TC-SEL-028: Verify footer copyright note is visible on the Mess Overview page (Check #28)</t>
+  </si>
+  <si>
+    <t>TC-SEL-029: Assert that leave request request form displays correct CSS styles on Logout (Check #29)</t>
+  </si>
+  <si>
+    <t>TC-SEL-030: Verify redirection to Raise Complaint after action (Check #30)</t>
+  </si>
+  <si>
+    <t>TC-SEL-031: Test user login with valid credentials on Leave Request (Check #31)</t>
+  </si>
+  <si>
+    <t>TC-SEL-032: Verify complaint history table is visible on the Raise Complaint page (Check #32)</t>
+  </si>
+  <si>
+    <t>TC-SEL-033: Verify that database error warning is not present on Warden Room Management (Check #33)</t>
+  </si>
+  <si>
+    <t>TC-SEL-034: Test page responsiveness on standard desktop view for Warden Room Management (Check #34)</t>
+  </si>
+  <si>
+    <t>TC-SEL-035: Verify that database error warning is not present on Fee Details (Check #35)</t>
+  </si>
+  <si>
+    <t>TC-SEL-036: Test page responsiveness on standard desktop view for Notifications (Check #36)</t>
+  </si>
+  <si>
+    <t>TC-SEL-037: Check database connection module clickability on the System Settings page (Check #37)</t>
+  </si>
+  <si>
+    <t>TC-SEL-038: Test user login with valid credentials on Security Monitoring (Check #38)</t>
+  </si>
+  <si>
+    <t>TC-SEL-039: Assert that password input text box displays correct CSS styles on My Room (Check #39)</t>
+  </si>
+  <si>
+    <t>TC-SEL-040: Assert that back button navigation link displays correct CSS styles on Notifications (Check #40)</t>
+  </si>
+  <si>
+    <t>TC-SEL-041: Assert that profile image uploader container displays correct CSS styles on Raise Complaint (Check #41)</t>
+  </si>
+  <si>
+    <t>TC-SEL-042: Test user login with valid credentials on Warden Leave Requests (Check #42)</t>
+  </si>
+  <si>
+    <t>TC-SEL-043: Verify that database error warning is not present on Admin Login (Check #43)</t>
+  </si>
+  <si>
+    <t>TC-SEL-044: Check profile image uploader container clickability on the Mess Overview page (Check #44)</t>
+  </si>
+  <si>
+    <t>TC-SEL-045: Test user login with valid credentials on Student Login (Check #45)</t>
+  </si>
+  <si>
+    <t>TC-SEL-046: Check back button navigation link clickability on the Landing Page page (Check #46)</t>
+  </si>
+  <si>
+    <t>TC-SEL-047: Verify that form validation works for username input text field on Warden Room Management (Check #47)</t>
+  </si>
+  <si>
+    <t>TC-SEL-048: Verify redirection to Warden Dashboard after action (Check #48)</t>
+  </si>
+  <si>
+    <t>TC-SEL-049: Verify that database error warning is not present on Student Overview (Check #49)</t>
+  </si>
+  <si>
+    <t>TC-SEL-050: Verify that form validation works for notice board widget on Mess Overview (Check #50)</t>
+  </si>
+  <si>
+    <t>TC-SEL-051: Verify that form validation works for database connection module on Warden Leave Requests (Check #51)</t>
+  </si>
+  <si>
+    <t>TC-SEL-052: Verify that form validation works for email input form control on Admin Dashboard (Check #52)</t>
+  </si>
+  <si>
+    <t>TC-SEL-053: Test page responsiveness on standard desktop view for Warden Dashboard (Check #53)</t>
+  </si>
+  <si>
+    <t>TC-SEL-054: Check submit button control clickability on the Logout page (Check #54)</t>
+  </si>
+  <si>
+    <t>TC-SEL-055: Verify redirection to Security Monitoring after action (Check #55)</t>
+  </si>
+  <si>
+    <t>TC-SEL-056: Verify that database error warning is not present on Mess Feedback (Check #56)</t>
+  </si>
+  <si>
+    <t>TC-SEL-057: Test user login with valid credentials on Raise Complaint (Check #57)</t>
+  </si>
+  <si>
+    <t>TC-SEL-058: Assert that sidebar navigation items displays correct CSS styles on Attendance (Check #58)</t>
+  </si>
+  <si>
+    <t>TC-SEL-059: Check fee status badge display clickability on the System Reports page (Check #59)</t>
+  </si>
+  <si>
+    <t>TC-SEL-060: Check email input form control clickability on the Student Overview page (Check #60)</t>
+  </si>
+  <si>
+    <t>TC-SEL-061: Verify that form validation works for password input text box on Student Login (Check #61)</t>
+  </si>
+  <si>
+    <t>TC-SEL-062: Verify that database error warning is not present on Complaint History (Check #62)</t>
+  </si>
+  <si>
+    <t>TC-SEL-063: Check submit button control clickability on the Student Overview page (Check #63)</t>
+  </si>
+  <si>
+    <t>TC-SEL-064: Verify that database error warning is not present on Complaint History (Check #64)</t>
+  </si>
+  <si>
+    <t>TC-SEL-065: Verify email input form control is visible on the Role Selection page (Check #65)</t>
+  </si>
+  <si>
+    <t>TC-SEL-066: Check complaint history table clickability on the Leave Request page (Check #66)</t>
+  </si>
+  <si>
+    <t>TC-SEL-067: Test page responsiveness on standard desktop view for Complaint History (Check #67)</t>
+  </si>
+  <si>
+    <t>TC-SEL-068: Check email input form control clickability on the Admin Dashboard page (Check #68)</t>
+  </si>
+  <si>
+    <t>TC-SEL-069: Test page responsiveness on standard desktop view for Student Login (Check #69)</t>
+  </si>
+  <si>
+    <t>TC-SEL-070: Check profile image uploader container clickability on the Profile page (Check #70)</t>
+  </si>
+  <si>
+    <t>TC-SEL-071: Test page responsiveness on standard desktop view for Warden Login (Check #71)</t>
+  </si>
+  <si>
+    <t>TC-SEL-072: Test user login with valid credentials on Mess Feedback (Check #72)</t>
+  </si>
+  <si>
+    <t>TC-SEL-073: Verify alert dialog box is visible on the Student Overview page (Check #73)</t>
+  </si>
+  <si>
+    <t>TC-SEL-074: Verify that form validation works for username input text field on Student Overview (Check #74)</t>
+  </si>
+  <si>
+    <t>TC-SEL-075: Test user login with valid credentials on Role Selection (Check #75)</t>
+  </si>
+  <si>
+    <t>TC-SEL-076: Verify that database error warning is not present on Profile (Check #76)</t>
+  </si>
+  <si>
+    <t>TC-SEL-077: Verify that database error warning is not present on Landing Page (Check #77)</t>
+  </si>
+  <si>
+    <t>TC-SEL-078: Verify that database error warning is not present on Admin Dashboard (Check #78)</t>
+  </si>
+  <si>
+    <t>TC-SEL-079: Verify that database error warning is not present on Complaint Monitoring (Check #79)</t>
+  </si>
+  <si>
+    <t>TC-SEL-080: Test page responsiveness on standard desktop view for Admin Dashboard (Check #80)</t>
+  </si>
+  <si>
+    <t>TC-SEL-081: Verify redirection to Landing Page after action (Check #81)</t>
+  </si>
+  <si>
+    <t>TC-SEL-082: Verify redirection to Notifications after action (Check #82)</t>
+  </si>
+  <si>
+    <t>TC-SEL-083: Test page responsiveness on standard desktop view for Fee Details (Check #83)</t>
+  </si>
+  <si>
+    <t>TC-SEL-084: Check dashboard metrics card clickability on the System Settings page (Check #84)</t>
+  </si>
+  <si>
+    <t>TC-SEL-085: Verify that database error warning is not present on Warden Leave Requests (Check #85)</t>
+  </si>
+  <si>
+    <t>TC-SEL-086: Verify footer copyright note is visible on the Admin Dashboard page (Check #86)</t>
+  </si>
+  <si>
+    <t>TC-SEL-087: Assert that role selection button displays correct CSS styles on Warden Leave Requests (Check #87)</t>
+  </si>
+  <si>
+    <t>TC-SEL-088: Test user login with valid credentials on Complaint History (Check #88)</t>
+  </si>
+  <si>
+    <t>TC-SEL-089: Verify that database error warning is not present on Raise Complaint (Check #89)</t>
+  </si>
+  <si>
+    <t>TC-SEL-090: Verify that form validation works for back button navigation link on Role Selection (Check #90)</t>
+  </si>
+  <si>
+    <t>TC-SEL-091: Verify that database error warning is not present on Complaint Monitoring (Check #91)</t>
+  </si>
+  <si>
+    <t>TC-SEL-092: Test page responsiveness on standard desktop view for Role Selection (Check #92)</t>
+  </si>
+  <si>
+    <t>TC-SEL-093: Assert that main navigation header displays correct CSS styles on Mess Feedback (Check #93)</t>
+  </si>
+  <si>
+    <t>TC-SEL-094: Verify that database error warning is not present on Warden Leave Requests (Check #94)</t>
+  </si>
+  <si>
+    <t>TC-SEL-095: Test page responsiveness on standard desktop view for Admin Dashboard (Check #95)</t>
+  </si>
+  <si>
+    <t>TC-SEL-096: Verify that form validation works for leave request request form on Landing Page (Check #96)</t>
+  </si>
+  <si>
+    <t>TC-SEL-097: Assert that profile image uploader container displays correct CSS styles on Notifications (Check #97)</t>
+  </si>
+  <si>
+    <t>TC-SEL-098: Test user login with valid credentials on Fee Details (Check #98)</t>
+  </si>
+  <si>
+    <t>TC-SEL-099: Assert that alert dialog box displays correct CSS styles on Warden Dashboard (Check #99)</t>
+  </si>
+  <si>
+    <t>TC-SEL-100: Verify that form validation works for database connection module on Admin Login (Check #100)</t>
+  </si>
+  <si>
+    <t>TC-SEL-101: Test user login with valid credentials on System Reports (Check #101)</t>
+  </si>
+  <si>
+    <t>TC-SEL-102: Check username input text field clickability on the Warden Dashboard page (Check #102)</t>
+  </si>
+  <si>
+    <t>TC-SEL-103: Verify that form validation works for alert dialog box on Landing Page (Check #103)</t>
+  </si>
+  <si>
+    <t>TC-SEL-104: Verify dashboard metrics card is visible on the Student Login page (Check #104)</t>
+  </si>
+  <si>
+    <t>TC-SEL-105: Assert that username input text field displays correct CSS styles on Mess Overview (Check #105)</t>
+  </si>
+  <si>
+    <t>TC-SEL-106: Assert that submit button control displays correct CSS styles on Student Dashboard (Check #106)</t>
+  </si>
+  <si>
+    <t>TC-SEL-107: Verify fee status badge display is visible on the Logout page (Check #107)</t>
+  </si>
+  <si>
+    <t>TC-SEL-108: Assert that leave request request form displays correct CSS styles on Warden Room Management (Check #108)</t>
+  </si>
+  <si>
+    <t>TC-SEL-109: Test page responsiveness on standard desktop view for Security Monitoring (Check #109)</t>
+  </si>
+  <si>
+    <t>TC-SEL-110: Check back button navigation link clickability on the Warden Room Management page (Check #110)</t>
+  </si>
+  <si>
+    <t>TC-SEL-111: Verify that database error warning is not present on Fee Details (Check #111)</t>
+  </si>
+  <si>
+    <t>TC-SEL-112: Check submit button control clickability on the Attendance page (Check #112)</t>
+  </si>
+  <si>
+    <t>TC-SEL-113: Verify that database error warning is not present on System Settings (Check #113)</t>
+  </si>
+  <si>
+    <t>TC-SEL-114: Check submit button control clickability on the Landing Page page (Check #114)</t>
+  </si>
+  <si>
+    <t>TC-SEL-115: Assert that submit button control displays correct CSS styles on System Reports (Check #115)</t>
+  </si>
+  <si>
+    <t>TC-SEL-116: Verify redirection to Mess Feedback after action (Check #116)</t>
+  </si>
+  <si>
+    <t>TC-SEL-117: Check fee status badge display clickability on the Role Selection page (Check #117)</t>
+  </si>
+  <si>
+    <t>TC-SEL-118: Verify complaint history table is visible on the Warden Room Management page (Check #118)</t>
+  </si>
+  <si>
+    <t>TC-SEL-119: Verify that form validation works for average rating star system on Fee Details (Check #119)</t>
+  </si>
+  <si>
+    <t>TC-SEL-120: Verify redirection to Warden Leave Requests after action (Check #120)</t>
+  </si>
+  <si>
+    <t>TC-SEL-121: Verify that database error warning is not present on Warden Dashboard (Check #121)</t>
+  </si>
+  <si>
+    <t>TC-SEL-122: Verify redirection to Warden Dashboard after action (Check #122)</t>
+  </si>
+  <si>
+    <t>TC-SEL-123: Verify that form validation works for dashboard metrics card on Warden Room Management (Check #123)</t>
+  </si>
+  <si>
+    <t>TC-SEL-124: Verify redirection to Student Dashboard after action (Check #124)</t>
+  </si>
+  <si>
+    <t>TC-SEL-125: Test page responsiveness on standard desktop view for Logout (Check #125)</t>
+  </si>
+  <si>
+    <t>TC-SEL-126: Check dashboard metrics card clickability on the Profile page (Check #126)</t>
+  </si>
+  <si>
+    <t>TC-SEL-127: Check notice board widget clickability on the System Reports page (Check #127)</t>
+  </si>
+  <si>
+    <t>TC-SEL-128: Check main navigation header clickability on the Admin Login page (Check #128)</t>
+  </si>
+  <si>
+    <t>TC-SEL-129: Check submit button control clickability on the Warden Login page (Check #129)</t>
+  </si>
+  <si>
+    <t>TC-SEL-130: Test page responsiveness on standard desktop view for Security Monitoring (Check #130)</t>
+  </si>
+  <si>
+    <t>TC-SEL-131: Verify redirection to Profile after action (Check #131)</t>
+  </si>
+  <si>
+    <t>TC-SEL-132: Verify that database error warning is not present on Mess Feedback (Check #132)</t>
+  </si>
+  <si>
+    <t>TC-SEL-133: Verify that database error warning is not present on Student Overview (Check #133)</t>
+  </si>
+  <si>
+    <t>TC-SEL-134: Test user login with valid credentials on Role Selection (Check #134)</t>
+  </si>
+  <si>
+    <t>TC-SEL-135: Check notice board widget clickability on the Role Selection page (Check #135)</t>
+  </si>
+  <si>
+    <t>TC-SEL-136: Test page responsiveness on standard desktop view for Warden Login (Check #136)</t>
+  </si>
+  <si>
+    <t>TC-SEL-137: Verify redirection to Attendance after action (Check #137)</t>
+  </si>
+  <si>
+    <t>TC-SEL-138: Verify average rating star system is visible on the Profile page (Check #138)</t>
+  </si>
+  <si>
+    <t>TC-SEL-139: Verify that form validation works for back button navigation link on Logout (Check #139)</t>
+  </si>
+  <si>
+    <t>TC-SEL-140: Verify redirection to My Room after action (Check #140)</t>
+  </si>
+  <si>
+    <t>TC-SEL-141: Check password input text box clickability on the Admin Dashboard page (Check #141)</t>
+  </si>
+  <si>
+    <t>TC-SEL-142: Test page responsiveness on standard desktop view for Raise Complaint (Check #142)</t>
+  </si>
+  <si>
+    <t>TC-SEL-143: Assert that alert dialog box displays correct CSS styles on Profile (Check #143)</t>
+  </si>
+  <si>
+    <t>TC-SEL-144: Test page responsiveness on standard desktop view for Mess Overview (Check #144)</t>
+  </si>
+  <si>
+    <t>TC-SEL-145: Verify that form validation works for fee status badge display on Warden Leave Requests (Check #145)</t>
+  </si>
+  <si>
+    <t>TC-SEL-146: Assert that back button navigation link displays correct CSS styles on Warden Room Management (Check #146)</t>
+  </si>
+  <si>
+    <t>TC-SEL-147: Verify submit button control is visible on the Student Dashboard page (Check #147)</t>
+  </si>
+  <si>
+    <t>TC-SEL-148: Verify that database error warning is not present on System Settings (Check #148)</t>
+  </si>
+  <si>
+    <t>TC-SEL-149: Verify dashboard metrics card is visible on the Mess Feedback page (Check #149)</t>
+  </si>
+  <si>
+    <t>TC-SEL-150: Verify that database error warning is not present on Notifications (Check #150)</t>
+  </si>
+  <si>
+    <t>TC-SEL-151: Verify redirection to Role Selection after action (Check #151)</t>
+  </si>
+  <si>
+    <t>TC-SEL-152: Test user login with valid credentials on Student Dashboard (Check #152)</t>
+  </si>
+  <si>
+    <t>TC-SEL-153: Assert that profile image uploader container displays correct CSS styles on System Settings (Check #153)</t>
+  </si>
+  <si>
+    <t>TC-SEL-154: Test page responsiveness on standard desktop view for Role Selection (Check #154)</t>
+  </si>
+  <si>
+    <t>TC-SEL-155: Check profile image uploader container clickability on the My Room page (Check #155)</t>
+  </si>
+  <si>
+    <t>TC-SEL-156: Check alert dialog box clickability on the Role Selection page (Check #156)</t>
+  </si>
+  <si>
+    <t>TC-SEL-157: Test user login with valid credentials on Landing Page (Check #157)</t>
+  </si>
+  <si>
+    <t>TC-SEL-158: Test page responsiveness on standard desktop view for Student Login (Check #158)</t>
+  </si>
+  <si>
+    <t>TC-SEL-159: Test user login with valid credentials on Complaint Monitoring (Check #159)</t>
+  </si>
+  <si>
+    <t>TC-SEL-160: Verify that database error warning is not present on Raise Complaint (Check #160)</t>
+  </si>
+  <si>
+    <t>TC-SEL-161: Verify that database error warning is not present on Leave Request (Check #161)</t>
+  </si>
+  <si>
+    <t>TC-SEL-162: Verify that database error warning is not present on Security Monitoring (Check #162)</t>
+  </si>
+  <si>
+    <t>TC-SEL-163: Verify redirection to My Room after action (Check #163)</t>
+  </si>
+  <si>
+    <t>TC-SEL-164: Verify notice board widget is visible on the System Settings page (Check #164)</t>
+  </si>
+  <si>
+    <t>TC-SEL-165: Verify database connection module is visible on the Warden Room Management page (Check #165)</t>
+  </si>
+  <si>
+    <t>TC-SEL-166: Assert that email input form control displays correct CSS styles on System Settings (Check #166)</t>
+  </si>
+  <si>
+    <t>TC-SEL-167: Verify redirection to Complaint History after action (Check #167)</t>
+  </si>
+  <si>
+    <t>TC-SEL-168: Test user login with valid credentials on Student Login (Check #168)</t>
+  </si>
+  <si>
+    <t>TC-SEL-169: Assert that notice board widget displays correct CSS styles on Admin Login (Check #169)</t>
+  </si>
+  <si>
+    <t>TC-SEL-170: Test user login with valid credentials on Warden Room Management (Check #170)</t>
+  </si>
+  <si>
+    <t>TC-SEL-171: Test page responsiveness on standard desktop view for Complaint Monitoring (Check #171)</t>
+  </si>
+  <si>
+    <t>TC-SEL-172: Verify that form validation works for back button navigation link on Fee Details (Check #172)</t>
+  </si>
+  <si>
+    <t>TC-SEL-173: Assert that fee status badge display displays correct CSS styles on Role Selection (Check #173)</t>
+  </si>
+  <si>
+    <t>TC-SEL-174: Verify sidebar navigation items is visible on the Student Dashboard page (Check #174)</t>
+  </si>
+  <si>
+    <t>TC-SEL-175: Verify complaint history table is visible on the Admin Login page (Check #175)</t>
+  </si>
+  <si>
+    <t>TC-SEL-176: Verify main navigation header is visible on the Student Login page (Check #176)</t>
+  </si>
+  <si>
+    <t>TC-SEL-177: Check email input form control clickability on the Student Login page (Check #177)</t>
+  </si>
+  <si>
+    <t>TC-SEL-178: Verify that form validation works for database connection module on Warden Dashboard (Check #178)</t>
+  </si>
+  <si>
+    <t>TC-SEL-179: Assert that main navigation header displays correct CSS styles on Complaint Monitoring (Check #179)</t>
+  </si>
+  <si>
+    <t>TC-SEL-180: Test user login with valid credentials on Admin Login (Check #180)</t>
+  </si>
+  <si>
+    <t>TC-SEL-181: Verify profile image uploader container is visible on the Admin Dashboard page (Check #181)</t>
+  </si>
+  <si>
+    <t>TC-SEL-182: Verify that form validation works for email input form control on Fee Details (Check #182)</t>
+  </si>
+  <si>
+    <t>TC-SEL-183: Assert that footer copyright note displays correct CSS styles on System Reports (Check #183)</t>
+  </si>
+  <si>
+    <t>TC-SEL-184: Verify that form validation works for alert dialog box on Mess Overview (Check #184)</t>
+  </si>
+  <si>
+    <t>TC-SEL-185: Verify that form validation works for submit button control on Warden Dashboard (Check #185)</t>
+  </si>
+  <si>
+    <t>TC-SEL-186: Check role selection button clickability on the Warden Room Management page (Check #186)</t>
+  </si>
+  <si>
+    <t>TC-SEL-187: Check dashboard metrics card clickability on the Warden Login page (Check #187)</t>
+  </si>
+  <si>
+    <t>TC-SEL-188: Test page responsiveness on standard desktop view for Warden Room Management (Check #188)</t>
+  </si>
+  <si>
+    <t>TC-SEL-189: Test user login with valid credentials on Notifications (Check #189)</t>
+  </si>
+  <si>
+    <t>TC-SEL-190: Verify that database error warning is not present on System Reports (Check #190)</t>
+  </si>
+  <si>
+    <t>TC-SEL-191: Test user login with valid credentials on Logout (Check #191)</t>
+  </si>
+  <si>
+    <t>TC-SEL-192: Assert that email input form control displays correct CSS styles on My Room (Check #192)</t>
+  </si>
+  <si>
+    <t>TC-SEL-193: Verify redirection to System Reports after action (Check #193)</t>
+  </si>
+  <si>
+    <t>TC-SEL-194: Verify that form validation works for footer copyright note on Notifications (Check #194)</t>
+  </si>
+  <si>
+    <t>TC-SEL-195: Verify that form validation works for role selection button on Security Monitoring (Check #195)</t>
+  </si>
+  <si>
+    <t>TC-SEL-196: Verify database connection module is visible on the Student Login page (Check #196)</t>
+  </si>
+  <si>
+    <t>TC-SEL-197: Check main navigation header clickability on the Landing Page page (Check #197)</t>
+  </si>
+  <si>
+    <t>TC-SEL-198: Verify that form validation works for dashboard metrics card on Leave Request (Check #198)</t>
+  </si>
+  <si>
+    <t>TC-SEL-199: Assert that sidebar navigation items displays correct CSS styles on Profile (Check #199)</t>
+  </si>
+  <si>
+    <t>TC-SEL-200: Verify database connection module is visible on the Warden Login page (Check #200)</t>
+  </si>
+  <si>
+    <t>TC-SEL-201: Verify redirection to Student Dashboard after action (Check #201)</t>
+  </si>
+  <si>
+    <t>TC-SEL-202: Test user login with valid credentials on Admin Login (Check #202)</t>
+  </si>
+  <si>
+    <t>TC-SEL-203: Verify that form validation works for username input text field on Fee Details (Check #203)</t>
+  </si>
+  <si>
+    <t>TC-SEL-204: Verify that form validation works for dashboard metrics card on Admin Login (Check #204)</t>
+  </si>
+  <si>
+    <t>TC-SEL-205: Verify database connection module is visible on the Security Monitoring page (Check #205)</t>
+  </si>
+  <si>
+    <t>TC-SEL-206: Assert that fee status badge display displays correct CSS styles on Logout (Check #206)</t>
+  </si>
+  <si>
+    <t>TC-SEL-207: Verify redirection to Warden Leave Requests after action (Check #207)</t>
+  </si>
+  <si>
+    <t>TC-SEL-208: Verify that database error warning is not present on Admin Dashboard (Check #208)</t>
+  </si>
+  <si>
+    <t>TC-SEL-209: Verify that form validation works for back button navigation link on Student Login (Check #209)</t>
+  </si>
+  <si>
+    <t>TC-SEL-210: Verify complaint history table is visible on the Warden Leave Requests page (Check #210)</t>
+  </si>
+  <si>
+    <t>TC-SEL-211: Verify that form validation works for fee status badge display on Mess Feedback (Check #211)</t>
+  </si>
+  <si>
+    <t>TC-SEL-212: Assert that email input form control displays correct CSS styles on Warden Leave Requests (Check #212)</t>
+  </si>
+  <si>
+    <t>TC-SEL-213: Verify alert dialog box is visible on the Complaint Monitoring page (Check #213)</t>
+  </si>
+  <si>
+    <t>TC-SEL-214: Assert that back button navigation link displays correct CSS styles on Fee Details (Check #214)</t>
+  </si>
+  <si>
+    <t>TC-SEL-215: Check database connection module clickability on the Warden Room Management page (Check #215)</t>
+  </si>
+  <si>
+    <t>TC-SEL-216: Assert that database connection module displays correct CSS styles on Role Selection (Check #216)</t>
+  </si>
+  <si>
+    <t>TC-SEL-217: Verify that database error warning is not present on Raise Complaint (Check #217)</t>
+  </si>
+  <si>
+    <t>TC-SEL-218: Verify that form validation works for alert dialog box on Student Dashboard (Check #218)</t>
+  </si>
+  <si>
+    <t>TC-SEL-219: Verify that database error warning is not present on Warden Room Management (Check #219)</t>
+  </si>
+  <si>
+    <t>TC-SEL-220: Verify redirection to Role Selection after action (Check #220)</t>
+  </si>
+  <si>
+    <t>TC-SEL-221: Test user login with valid credentials on Student Login (Check #221)</t>
+  </si>
+  <si>
+    <t>TC-SEL-222: Verify dashboard metrics card is visible on the Mess Overview page (Check #222)</t>
+  </si>
+  <si>
+    <t>TC-SEL-223: Check notice board widget clickability on the Warden Login page (Check #223)</t>
+  </si>
+  <si>
+    <t>TC-SEL-224: Verify that database error warning is not present on Logout (Check #224)</t>
+  </si>
+  <si>
+    <t>TC-SEL-225: Verify redirection to Leave Request after action (Check #225)</t>
+  </si>
+  <si>
+    <t>TC-SEL-226: Verify that form validation works for dashboard metrics card on Mess Feedback (Check #226)</t>
+  </si>
+  <si>
+    <t>TC-SEL-227: Verify that database error warning is not present on Notifications (Check #227)</t>
+  </si>
+  <si>
+    <t>TC-SEL-228: Verify redirection to Landing Page after action (Check #228)</t>
+  </si>
+  <si>
+    <t>TC-SEL-229: Verify redirection to Profile after action (Check #229)</t>
+  </si>
+  <si>
+    <t>TC-SEL-230: Check email input form control clickability on the Attendance page (Check #230)</t>
+  </si>
+  <si>
+    <t>TC-SEL-231: Test user login with valid credentials on Logout (Check #231)</t>
+  </si>
+  <si>
+    <t>TC-SEL-232: Verify complaint history table is visible on the Logout page (Check #232)</t>
+  </si>
+  <si>
+    <t>TC-SEL-233: Verify alert dialog box is visible on the Attendance page (Check #233)</t>
+  </si>
+  <si>
+    <t>TC-SEL-234: Verify that database error warning is not present on System Settings (Check #234)</t>
+  </si>
+  <si>
+    <t>TC-SEL-235: Verify that database error warning is not present on Warden Leave Requests (Check #235)</t>
+  </si>
+  <si>
+    <t>TC-SEL-236: Check database connection module clickability on the System Reports page (Check #236)</t>
+  </si>
+  <si>
+    <t>TC-SEL-237: Verify that form validation works for username input text field on Warden Room Management (Check #237)</t>
+  </si>
+  <si>
+    <t>TC-SEL-238: Verify that database error warning is not present on Warden Leave Requests (Check #238)</t>
+  </si>
+  <si>
+    <t>TC-SEL-239: Verify redirection to Security Monitoring after action (Check #239)</t>
+  </si>
+  <si>
+    <t>TC-SEL-240: Verify that form validation works for leave request request form on Security Monitoring (Check #240)</t>
+  </si>
+  <si>
+    <t>TC-SEL-241: Verify that form validation works for main navigation header on Student Dashboard (Check #241)</t>
+  </si>
+  <si>
+    <t>TC-SEL-242: Verify that form validation works for database connection module on Warden Dashboard (Check #242)</t>
+  </si>
+  <si>
+    <t>TC-SEL-243: Verify that database error warning is not present on Notifications (Check #243)</t>
+  </si>
+  <si>
+    <t>TC-SEL-244: Assert that alert dialog box displays correct CSS styles on Landing Page (Check #244)</t>
+  </si>
+  <si>
+    <t>TC-SEL-245: Verify back button navigation link is visible on the Raise Complaint page (Check #245)</t>
+  </si>
+  <si>
+    <t>TC-SEL-246: Verify redirection to Student Overview after action (Check #246)</t>
+  </si>
+  <si>
+    <t>TC-SEL-247: Assert that main navigation header displays correct CSS styles on Student Dashboard (Check #247)</t>
+  </si>
+  <si>
+    <t>TC-SEL-248: Verify that form validation works for submit button control on Admin Dashboard (Check #248)</t>
+  </si>
+  <si>
+    <t>TC-SEL-249: Verify that database error warning is not present on Security Monitoring (Check #249)</t>
+  </si>
+  <si>
+    <t>TC-SEL-250: Verify username input text field is visible on the System Reports page (Check #250)</t>
+  </si>
+  <si>
+    <t>TC-SEL-251: Test page responsiveness on standard desktop view for My Room (Check #251)</t>
+  </si>
+  <si>
+    <t>TC-SEL-252: Verify sidebar navigation items is visible on the System Reports page (Check #252)</t>
+  </si>
+  <si>
+    <t>TC-SEL-253: Check alert dialog box clickability on the Warden Leave Requests page (Check #253)</t>
+  </si>
+  <si>
+    <t>TC-SEL-254: Verify that database error warning is not present on Leave Request (Check #254)</t>
+  </si>
+  <si>
+    <t>TC-SEL-255: Verify redirection to Warden Dashboard after action (Check #255)</t>
+  </si>
+  <si>
+    <t>TC-SEL-256: Check footer copyright note clickability on the Leave Request page (Check #256)</t>
+  </si>
+  <si>
+    <t>TC-SEL-257: Verify fee status badge display is visible on the Warden Login page (Check #257)</t>
+  </si>
+  <si>
+    <t>TC-SEL-258: Verify that form validation works for fee status badge display on Landing Page (Check #258)</t>
+  </si>
+  <si>
+    <t>TC-SEL-259: Verify that database error warning is not present on Mess Overview (Check #259)</t>
+  </si>
+  <si>
+    <t>TC-SEL-260: Verify that form validation works for profile image uploader container on Leave Request (Check #260)</t>
+  </si>
+  <si>
+    <t>TC-SEL-261: Verify role selection button is visible on the Warden Dashboard page (Check #261)</t>
+  </si>
+  <si>
+    <t>TC-SEL-262: Verify redirection to Attendance after action (Check #262)</t>
+  </si>
+  <si>
+    <t>TC-SEL-263: Test user login with valid credentials on System Reports (Check #263)</t>
+  </si>
+  <si>
+    <t>TC-SEL-264: Verify username input text field is visible on the Role Selection page (Check #264)</t>
+  </si>
+  <si>
+    <t>TC-SEL-265: Verify password input text box is visible on the Mess Feedback page (Check #265)</t>
+  </si>
+  <si>
+    <t>TC-SEL-266: Test page responsiveness on standard desktop view for Warden Leave Requests (Check #266)</t>
+  </si>
+  <si>
+    <t>TC-SEL-267: Verify that database error warning is not present on Profile (Check #267)</t>
+  </si>
+  <si>
+    <t>TC-SEL-268: Verify that database error warning is not present on Attendance (Check #268)</t>
+  </si>
+  <si>
+    <t>TC-SEL-269: Verify redirection to Student Login after action (Check #269)</t>
+  </si>
+  <si>
+    <t>TC-SEL-270: Verify footer copyright note is visible on the Warden Room Management page (Check #270)</t>
+  </si>
+  <si>
+    <t>TC-SEL-271: Verify that form validation works for alert dialog box on System Reports (Check #271)</t>
+  </si>
+  <si>
+    <t>TC-SEL-272: Test page responsiveness on standard desktop view for Complaint Monitoring (Check #272)</t>
+  </si>
+  <si>
+    <t>TC-SEL-273: Check username input text field clickability on the Logout page (Check #273)</t>
+  </si>
+  <si>
+    <t>TC-SEL-274: Verify that database error warning is not present on Warden Login (Check #274)</t>
+  </si>
+  <si>
+    <t>TC-SEL-275: Test page responsiveness on standard desktop view for System Settings (Check #275)</t>
+  </si>
+  <si>
+    <t>TC-SEL-276: Verify redirection to Security Monitoring after action (Check #276)</t>
+  </si>
+  <si>
+    <t>TC-SEL-277: Verify redirection to System Reports after action (Check #277)</t>
+  </si>
+  <si>
+    <t>TC-SEL-278: Test user login with valid credentials on System Settings (Check #278)</t>
+  </si>
+  <si>
+    <t>TC-SEL-279: Verify that database error warning is not present on Student Login (Check #279)</t>
+  </si>
+  <si>
+    <t>TC-SEL-280: Verify that form validation works for footer copyright note on Admin Login (Check #280)</t>
+  </si>
+  <si>
+    <t>TC-SEL-281: Verify that database error warning is not present on Student Overview (Check #281)</t>
+  </si>
+  <si>
+    <t>TC-SEL-282: Assert that sidebar navigation items displays correct CSS styles on Warden Login (Check #282)</t>
+  </si>
+  <si>
+    <t>TC-SEL-283: Test user login with valid credentials on Warden Login (Check #283)</t>
+  </si>
+  <si>
+    <t>TC-SEL-284: Verify that database error warning is not present on Landing Page (Check #284)</t>
+  </si>
+  <si>
+    <t>TC-SEL-285: Assert that average rating star system displays correct CSS styles on Security Monitoring (Check #285)</t>
+  </si>
+  <si>
+    <t>TC-SEL-286: Test user login with valid credentials on Warden Dashboard (Check #286)</t>
+  </si>
+  <si>
+    <t>TC-SEL-287: Verify email input form control is visible on the Security Monitoring page (Check #287)</t>
+  </si>
+  <si>
+    <t>TC-SEL-288: Verify that database error warning is not present on Profile (Check #288)</t>
+  </si>
+  <si>
+    <t>TC-SEL-289: Verify redirection to Admin Dashboard after action (Check #289)</t>
+  </si>
+  <si>
+    <t>TC-SEL-290: Check notice board widget clickability on the Warden Leave Requests page (Check #290)</t>
+  </si>
+  <si>
+    <t>TC-SEL-291: Verify alert dialog box is visible on the Admin Login page (Check #291)</t>
+  </si>
+  <si>
+    <t>TC-SEL-292: Test user login with valid credentials on Notifications (Check #292)</t>
+  </si>
+  <si>
+    <t>TC-SEL-293: Verify redirection to System Reports after action (Check #293)</t>
+  </si>
+  <si>
+    <t>TC-SEL-294: Test user login with valid credentials on Leave Request (Check #294)</t>
+  </si>
+  <si>
+    <t>TC-SEL-295: Assert that profile image uploader container displays correct CSS styles on Mess Overview (Check #295)</t>
+  </si>
+  <si>
+    <t>TC-SEL-296: Verify password input text box is visible on the Raise Complaint page (Check #296)</t>
+  </si>
+  <si>
+    <t>TC-SEL-297: Check fee status badge display clickability on the Fee Details page (Check #297)</t>
+  </si>
+  <si>
+    <t>TC-SEL-298: Verify redirection to Student Overview after action (Check #298)</t>
+  </si>
+  <si>
+    <t>TC-SEL-299: Verify that form validation works for alert dialog box on Student Dashboard (Check #299)</t>
+  </si>
+  <si>
+    <t>TC-SEL-300: Test page responsiveness on standard desktop view for Security Monitoring (Check #300)</t>
   </si>
 </sst>
 </file>
